--- a/doc/notes.xlsx
+++ b/doc/notes.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10531"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10726"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/renzosala/Develop/personal/tokeniko/doc/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{968B2943-EE54-E149-BA60-3239CC634F6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FBAF464E-8D0F-5545-B872-50397C7AB13C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="780" windowWidth="36000" windowHeight="22600" activeTab="10" xr2:uid="{ED098269-B10A-E440-BCE3-AF4955707036}"/>
+    <workbookView xWindow="0" yWindow="780" windowWidth="36000" windowHeight="22600" activeTab="11" xr2:uid="{ED098269-B10A-E440-BCE3-AF4955707036}"/>
   </bookViews>
   <sheets>
     <sheet name="General schema" sheetId="1" r:id="rId1"/>
@@ -24,6 +24,7 @@
     <sheet name="Problems" sheetId="10" r:id="rId9"/>
     <sheet name="Next step" sheetId="11" r:id="rId10"/>
     <sheet name="Inconsistencies" sheetId="12" r:id="rId11"/>
+    <sheet name="TKZIP2" sheetId="13" r:id="rId12"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -46,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="857" uniqueCount="513">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1169" uniqueCount="579">
   <si>
     <t>essere</t>
   </si>
@@ -1786,12 +1787,210 @@
     <t>So we can simplify: wheter we know or we don't know the values of the vector, we endup discovering that the expression violates logic (a eq b imply a noteq b) 
 because we have HARDWIRED the logic operations (because we consider the logic tokeniko first truth)</t>
   </si>
+  <si>
+    <t>cat</t>
+  </si>
+  <si>
+    <t>orange</t>
+  </si>
+  <si>
+    <t>feline</t>
+  </si>
+  <si>
+    <t>mammal</t>
+  </si>
+  <si>
+    <t>cute</t>
+  </si>
+  <si>
+    <t>*</t>
+  </si>
+  <si>
+    <t>point of view</t>
+  </si>
+  <si>
+    <t>original</t>
+  </si>
+  <si>
+    <t>predicate</t>
+  </si>
+  <si>
+    <t>my cat is cute</t>
+  </si>
+  <si>
+    <t>felines are mammals</t>
+  </si>
+  <si>
+    <t>all</t>
+  </si>
+  <si>
+    <t>a wire is ligament made of metal</t>
+  </si>
+  <si>
+    <t>wire</t>
+  </si>
+  <si>
+    <t>ligament</t>
+  </si>
+  <si>
+    <t>material</t>
+  </si>
+  <si>
+    <t>direct</t>
+  </si>
+  <si>
+    <t>indirects</t>
+  </si>
+  <si>
+    <t>part</t>
+  </si>
+  <si>
+    <t>destination</t>
+  </si>
+  <si>
+    <t>I gave my sister a book</t>
+  </si>
+  <si>
+    <t>me</t>
+  </si>
+  <si>
+    <t>give</t>
+  </si>
+  <si>
+    <t>t-1</t>
+  </si>
+  <si>
+    <t>st</t>
+  </si>
+  <si>
+    <t>I went from Rome to Genoa to see the ligurian sea</t>
+  </si>
+  <si>
+    <t>theatre (stm)</t>
+  </si>
+  <si>
+    <t>[t-1,t-1][*,*][*,*][*,*]</t>
+  </si>
+  <si>
+    <t>go</t>
+  </si>
+  <si>
+    <t>see</t>
+  </si>
+  <si>
+    <t>sea</t>
+  </si>
+  <si>
+    <t>t-2</t>
+  </si>
+  <si>
+    <t>[t-2,t-1][r(x),g(x)][r(y),g(y)][r(z),g(z)]</t>
+  </si>
+  <si>
+    <t>liguria</t>
+  </si>
+  <si>
+    <t>advantage</t>
+  </si>
+  <si>
+    <t>she works for her family</t>
+  </si>
+  <si>
+    <t>she</t>
+  </si>
+  <si>
+    <t>work</t>
+  </si>
+  <si>
+    <t>(me)sister</t>
+  </si>
+  <si>
+    <t>(she)faimily</t>
+  </si>
+  <si>
+    <t>my cats are orange</t>
+  </si>
+  <si>
+    <t>many</t>
+  </si>
+  <si>
+    <t>rel</t>
+  </si>
+  <si>
+    <t>with</t>
+  </si>
+  <si>
+    <t>tool</t>
+  </si>
+  <si>
+    <t>goal</t>
+  </si>
+  <si>
+    <t>agent</t>
+  </si>
+  <si>
+    <t>the hammer is made of titanium</t>
+  </si>
+  <si>
+    <t>one</t>
+  </si>
+  <si>
+    <t>book</t>
+  </si>
+  <si>
+    <t>titanium</t>
+  </si>
+  <si>
+    <t>AND</t>
+  </si>
+  <si>
+    <t>the mail was written by John</t>
+  </si>
+  <si>
+    <t>mail</t>
+  </si>
+  <si>
+    <t>write</t>
+  </si>
+  <si>
+    <t>John</t>
+  </si>
+  <si>
+    <t>I study for the exam</t>
+  </si>
+  <si>
+    <t>study</t>
+  </si>
+  <si>
+    <t>exam</t>
+  </si>
+  <si>
+    <t>my house was destroyed by the tornado</t>
+  </si>
+  <si>
+    <t>house</t>
+  </si>
+  <si>
+    <t>destroyed</t>
+  </si>
+  <si>
+    <t>tornado</t>
+  </si>
+  <si>
+    <t>build</t>
+  </si>
+  <si>
+    <t>contraption</t>
+  </si>
+  <si>
+    <t>I build my contraption with my hammer</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="22">
+  <fonts count="24">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -1923,8 +2122,22 @@
       <name val="Aptos Narrow"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <color theme="0"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="0"/>
+      <name val="Aptos Narrow"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="7">
+  <fills count="18">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1955,6 +2168,72 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="3"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="3" tint="9.9978637043366805E-2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC00000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF0000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="-0.499984740745262"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="-0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2" tint="-0.749992370372631"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2" tint="-0.499984740745262"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2125,7 +2404,7 @@
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="94">
+  <cellXfs count="112">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
@@ -2302,8 +2581,32 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2323,16 +2626,7 @@
     <xf numFmtId="0" fontId="15" fillId="3" borderId="9" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="6" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2347,15 +2641,6 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="6" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2368,11 +2653,57 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
+    <xf numFmtId="0" fontId="22" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="5">
@@ -3042,12 +3373,12 @@
       <c r="D30" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="E30" s="70" t="s">
+      <c r="E30" s="72" t="s">
         <v>127</v>
       </c>
-      <c r="F30" s="70"/>
-      <c r="G30" s="70"/>
-      <c r="H30" s="70"/>
+      <c r="F30" s="72"/>
+      <c r="G30" s="72"/>
+      <c r="H30" s="72"/>
       <c r="I30" s="4" t="s">
         <v>340</v>
       </c>
@@ -3110,12 +3441,12 @@
       <c r="D36" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="E36" s="70" t="s">
+      <c r="E36" s="72" t="s">
         <v>127</v>
       </c>
-      <c r="F36" s="70"/>
-      <c r="G36" s="70"/>
-      <c r="H36" s="70"/>
+      <c r="F36" s="72"/>
+      <c r="G36" s="72"/>
+      <c r="H36" s="72"/>
     </row>
     <row r="37" spans="2:10">
       <c r="B37" s="4"/>
@@ -3491,7 +3822,7 @@
       <c r="B7" t="s">
         <v>502</v>
       </c>
-      <c r="C7" s="92" t="s">
+      <c r="C7" s="70" t="s">
         <v>505</v>
       </c>
       <c r="D7" s="63"/>
@@ -3621,7 +3952,7 @@
       </c>
     </row>
     <row r="20" spans="3:8">
-      <c r="C20" s="92" t="s">
+      <c r="C20" s="70" t="s">
         <v>510</v>
       </c>
       <c r="D20" s="63"/>
@@ -3663,27 +3994,1075 @@
       </c>
     </row>
     <row r="24" spans="3:8" ht="43" customHeight="1">
-      <c r="C24" s="93" t="s">
+      <c r="C24" s="71" t="s">
         <v>511</v>
       </c>
-      <c r="D24" s="93"/>
-      <c r="E24" s="93"/>
-      <c r="F24" s="93"/>
-      <c r="G24" s="93"/>
+      <c r="D24" s="71"/>
+      <c r="E24" s="71"/>
+      <c r="F24" s="71"/>
+      <c r="G24" s="71"/>
     </row>
     <row r="25" spans="3:8" ht="80" customHeight="1">
-      <c r="C25" s="93" t="s">
+      <c r="C25" s="71" t="s">
         <v>512</v>
       </c>
-      <c r="D25" s="93"/>
-      <c r="E25" s="93"/>
-      <c r="F25" s="93"/>
-      <c r="G25" s="93"/>
+      <c r="D25" s="71"/>
+      <c r="E25" s="71"/>
+      <c r="F25" s="71"/>
+      <c r="G25" s="71"/>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="C25:G25"/>
     <mergeCell ref="C24:G24"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A8FFB43E-77B2-C342-86C5-6A72B72B7B3C}">
+  <dimension ref="A3:V19"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
+  <cols>
+    <col min="1" max="1" width="51.6640625" customWidth="1"/>
+    <col min="2" max="2" width="6.1640625" customWidth="1"/>
+    <col min="3" max="3" width="7.33203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="29.83203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="5.5" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="4.1640625" customWidth="1"/>
+    <col min="10" max="10" width="3.5" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="4.5" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="6.1640625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="11" customWidth="1"/>
+    <col min="17" max="17" width="9.1640625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="1:22">
+      <c r="A3" s="94" t="s">
+        <v>520</v>
+      </c>
+      <c r="B3" s="103" t="s">
+        <v>220</v>
+      </c>
+      <c r="C3" s="95" t="s">
+        <v>519</v>
+      </c>
+      <c r="D3" s="95"/>
+      <c r="E3" s="96" t="s">
+        <v>191</v>
+      </c>
+      <c r="F3" s="96"/>
+      <c r="G3" s="96"/>
+      <c r="H3" s="96"/>
+      <c r="I3" s="96"/>
+      <c r="J3" s="96"/>
+      <c r="K3" s="96"/>
+      <c r="L3" s="99"/>
+      <c r="M3" s="99"/>
+      <c r="N3" s="97"/>
+      <c r="O3" s="97"/>
+      <c r="P3" s="97"/>
+      <c r="Q3" s="97"/>
+      <c r="R3" s="97"/>
+      <c r="S3" s="97"/>
+      <c r="T3" s="97"/>
+      <c r="U3" s="97"/>
+      <c r="V3" s="97"/>
+    </row>
+    <row r="4" spans="1:22" s="67" customFormat="1">
+      <c r="C4" s="98" t="s">
+        <v>140</v>
+      </c>
+      <c r="D4" s="98" t="s">
+        <v>521</v>
+      </c>
+      <c r="E4" s="98" t="s">
+        <v>539</v>
+      </c>
+      <c r="F4" s="104" t="s">
+        <v>140</v>
+      </c>
+      <c r="G4" s="104"/>
+      <c r="H4" s="104"/>
+      <c r="I4" s="106" t="s">
+        <v>521</v>
+      </c>
+      <c r="J4" s="106"/>
+      <c r="K4" s="108" t="s">
+        <v>529</v>
+      </c>
+      <c r="L4" s="108"/>
+      <c r="M4" s="108"/>
+      <c r="N4" s="110" t="s">
+        <v>530</v>
+      </c>
+      <c r="O4" s="110"/>
+      <c r="P4" s="110"/>
+      <c r="Q4" s="110"/>
+      <c r="R4" s="110"/>
+      <c r="S4" s="110"/>
+      <c r="T4" s="110"/>
+      <c r="U4" s="110"/>
+      <c r="V4" s="110"/>
+    </row>
+    <row r="5" spans="1:22" s="67" customFormat="1">
+      <c r="C5" s="98"/>
+      <c r="D5" s="98"/>
+      <c r="F5" s="105" t="s">
+        <v>531</v>
+      </c>
+      <c r="G5" s="105" t="s">
+        <v>555</v>
+      </c>
+      <c r="H5" s="105" t="s">
+        <v>140</v>
+      </c>
+      <c r="I5" s="107" t="s">
+        <v>521</v>
+      </c>
+      <c r="J5" s="107" t="s">
+        <v>537</v>
+      </c>
+      <c r="K5" s="109" t="s">
+        <v>531</v>
+      </c>
+      <c r="L5" s="109" t="s">
+        <v>555</v>
+      </c>
+      <c r="M5" s="109" t="s">
+        <v>529</v>
+      </c>
+      <c r="N5" s="111" t="s">
+        <v>528</v>
+      </c>
+      <c r="O5" s="111" t="s">
+        <v>532</v>
+      </c>
+      <c r="P5" s="111" t="s">
+        <v>547</v>
+      </c>
+      <c r="Q5" s="111" t="s">
+        <v>369</v>
+      </c>
+      <c r="R5" s="111" t="s">
+        <v>556</v>
+      </c>
+      <c r="S5" s="111" t="s">
+        <v>557</v>
+      </c>
+      <c r="T5" s="111" t="s">
+        <v>559</v>
+      </c>
+      <c r="U5" s="111" t="s">
+        <v>558</v>
+      </c>
+      <c r="V5" s="111" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="6" spans="1:22">
+      <c r="C6" s="69"/>
+      <c r="D6" s="69"/>
+      <c r="F6" s="69"/>
+      <c r="G6" s="69"/>
+      <c r="H6" s="69"/>
+      <c r="I6" s="69"/>
+      <c r="J6" s="69"/>
+      <c r="K6" s="69"/>
+      <c r="L6" s="69"/>
+      <c r="M6" s="69"/>
+    </row>
+    <row r="7" spans="1:22">
+      <c r="A7" t="s">
+        <v>522</v>
+      </c>
+      <c r="B7" t="s">
+        <v>564</v>
+      </c>
+      <c r="C7" t="s">
+        <v>534</v>
+      </c>
+      <c r="D7" t="s">
+        <v>470</v>
+      </c>
+      <c r="E7" t="s">
+        <v>518</v>
+      </c>
+      <c r="F7" t="s">
+        <v>518</v>
+      </c>
+      <c r="G7" t="s">
+        <v>534</v>
+      </c>
+      <c r="H7" t="s">
+        <v>513</v>
+      </c>
+      <c r="I7" t="s">
+        <v>517</v>
+      </c>
+      <c r="J7" t="s">
+        <v>518</v>
+      </c>
+      <c r="K7" t="s">
+        <v>518</v>
+      </c>
+      <c r="L7" t="s">
+        <v>518</v>
+      </c>
+      <c r="M7" t="s">
+        <v>518</v>
+      </c>
+      <c r="N7" t="s">
+        <v>518</v>
+      </c>
+      <c r="O7" t="s">
+        <v>518</v>
+      </c>
+      <c r="P7" t="s">
+        <v>518</v>
+      </c>
+      <c r="Q7" t="s">
+        <v>518</v>
+      </c>
+      <c r="R7" t="s">
+        <v>518</v>
+      </c>
+      <c r="S7" t="s">
+        <v>518</v>
+      </c>
+      <c r="T7" t="s">
+        <v>518</v>
+      </c>
+      <c r="U7" t="s">
+        <v>518</v>
+      </c>
+      <c r="V7" t="s">
+        <v>518</v>
+      </c>
+    </row>
+    <row r="8" spans="1:22">
+      <c r="A8" t="s">
+        <v>523</v>
+      </c>
+      <c r="B8" t="s">
+        <v>564</v>
+      </c>
+      <c r="C8" t="s">
+        <v>518</v>
+      </c>
+      <c r="D8" t="s">
+        <v>518</v>
+      </c>
+      <c r="E8" t="s">
+        <v>518</v>
+      </c>
+      <c r="F8" t="s">
+        <v>524</v>
+      </c>
+      <c r="G8" t="s">
+        <v>518</v>
+      </c>
+      <c r="H8" t="s">
+        <v>515</v>
+      </c>
+      <c r="I8" t="s">
+        <v>516</v>
+      </c>
+      <c r="J8" t="s">
+        <v>518</v>
+      </c>
+      <c r="K8" t="s">
+        <v>518</v>
+      </c>
+      <c r="L8" t="s">
+        <v>518</v>
+      </c>
+      <c r="M8" t="s">
+        <v>518</v>
+      </c>
+      <c r="N8" t="s">
+        <v>518</v>
+      </c>
+      <c r="O8" t="s">
+        <v>518</v>
+      </c>
+      <c r="P8" t="s">
+        <v>518</v>
+      </c>
+      <c r="Q8" t="s">
+        <v>518</v>
+      </c>
+      <c r="R8" t="s">
+        <v>518</v>
+      </c>
+      <c r="S8" t="s">
+        <v>518</v>
+      </c>
+      <c r="T8" t="s">
+        <v>518</v>
+      </c>
+      <c r="U8" t="s">
+        <v>518</v>
+      </c>
+      <c r="V8" t="s">
+        <v>518</v>
+      </c>
+    </row>
+    <row r="9" spans="1:22">
+      <c r="A9" t="s">
+        <v>525</v>
+      </c>
+      <c r="B9" t="s">
+        <v>564</v>
+      </c>
+      <c r="C9" t="s">
+        <v>518</v>
+      </c>
+      <c r="D9" t="s">
+        <v>518</v>
+      </c>
+      <c r="E9" t="s">
+        <v>518</v>
+      </c>
+      <c r="F9" t="s">
+        <v>524</v>
+      </c>
+      <c r="G9" t="s">
+        <v>518</v>
+      </c>
+      <c r="H9" t="s">
+        <v>526</v>
+      </c>
+      <c r="I9" t="s">
+        <v>527</v>
+      </c>
+      <c r="J9" t="s">
+        <v>518</v>
+      </c>
+      <c r="K9" t="s">
+        <v>518</v>
+      </c>
+      <c r="L9" t="s">
+        <v>518</v>
+      </c>
+      <c r="M9" t="s">
+        <v>518</v>
+      </c>
+      <c r="N9" t="s">
+        <v>518</v>
+      </c>
+      <c r="O9" t="s">
+        <v>518</v>
+      </c>
+      <c r="P9" t="s">
+        <v>518</v>
+      </c>
+      <c r="Q9" t="s">
+        <v>518</v>
+      </c>
+      <c r="R9" t="s">
+        <v>518</v>
+      </c>
+      <c r="S9" t="s">
+        <v>518</v>
+      </c>
+      <c r="T9" t="s">
+        <v>518</v>
+      </c>
+      <c r="U9" t="s">
+        <v>518</v>
+      </c>
+      <c r="V9" t="s">
+        <v>518</v>
+      </c>
+    </row>
+    <row r="10" spans="1:22">
+      <c r="A10" t="s">
+        <v>533</v>
+      </c>
+      <c r="B10" t="s">
+        <v>564</v>
+      </c>
+      <c r="C10" t="s">
+        <v>518</v>
+      </c>
+      <c r="D10" t="s">
+        <v>518</v>
+      </c>
+      <c r="E10" t="s">
+        <v>540</v>
+      </c>
+      <c r="F10" t="s">
+        <v>518</v>
+      </c>
+      <c r="G10" t="s">
+        <v>518</v>
+      </c>
+      <c r="H10" t="s">
+        <v>534</v>
+      </c>
+      <c r="I10" t="s">
+        <v>535</v>
+      </c>
+      <c r="J10" t="s">
+        <v>536</v>
+      </c>
+      <c r="K10" t="s">
+        <v>518</v>
+      </c>
+      <c r="L10" t="s">
+        <v>518</v>
+      </c>
+      <c r="M10" t="s">
+        <v>518</v>
+      </c>
+      <c r="N10" t="s">
+        <v>518</v>
+      </c>
+      <c r="O10" t="s">
+        <v>551</v>
+      </c>
+      <c r="P10" t="s">
+        <v>518</v>
+      </c>
+      <c r="Q10" t="s">
+        <v>518</v>
+      </c>
+      <c r="R10" t="s">
+        <v>518</v>
+      </c>
+      <c r="S10" t="s">
+        <v>518</v>
+      </c>
+      <c r="T10" t="s">
+        <v>518</v>
+      </c>
+      <c r="U10" t="s">
+        <v>518</v>
+      </c>
+      <c r="V10" t="s">
+        <v>518</v>
+      </c>
+    </row>
+    <row r="11" spans="1:22">
+      <c r="A11" s="100" t="s">
+        <v>538</v>
+      </c>
+      <c r="B11" t="s">
+        <v>564</v>
+      </c>
+      <c r="C11" t="s">
+        <v>518</v>
+      </c>
+      <c r="D11" t="s">
+        <v>518</v>
+      </c>
+      <c r="E11" s="101" t="s">
+        <v>545</v>
+      </c>
+      <c r="F11" t="s">
+        <v>518</v>
+      </c>
+      <c r="G11" t="s">
+        <v>518</v>
+      </c>
+      <c r="H11" t="s">
+        <v>534</v>
+      </c>
+      <c r="I11" t="s">
+        <v>541</v>
+      </c>
+      <c r="J11" t="s">
+        <v>544</v>
+      </c>
+      <c r="K11" t="s">
+        <v>518</v>
+      </c>
+      <c r="L11" t="s">
+        <v>518</v>
+      </c>
+      <c r="M11" t="s">
+        <v>518</v>
+      </c>
+      <c r="N11" t="s">
+        <v>518</v>
+      </c>
+      <c r="O11" t="s">
+        <v>518</v>
+      </c>
+      <c r="P11" t="s">
+        <v>518</v>
+      </c>
+      <c r="Q11" t="s">
+        <v>518</v>
+      </c>
+      <c r="R11" t="s">
+        <v>518</v>
+      </c>
+      <c r="S11" t="s">
+        <v>518</v>
+      </c>
+      <c r="T11" t="s">
+        <v>518</v>
+      </c>
+      <c r="U11" t="s">
+        <v>518</v>
+      </c>
+      <c r="V11" t="s">
+        <v>518</v>
+      </c>
+    </row>
+    <row r="12" spans="1:22">
+      <c r="A12" s="100"/>
+      <c r="B12" s="102" t="s">
+        <v>218</v>
+      </c>
+      <c r="C12" t="s">
+        <v>518</v>
+      </c>
+      <c r="D12" t="s">
+        <v>518</v>
+      </c>
+      <c r="E12" s="101"/>
+      <c r="F12" t="s">
+        <v>518</v>
+      </c>
+      <c r="G12" t="s">
+        <v>518</v>
+      </c>
+      <c r="H12" t="s">
+        <v>534</v>
+      </c>
+      <c r="I12" t="s">
+        <v>542</v>
+      </c>
+      <c r="J12" t="s">
+        <v>536</v>
+      </c>
+      <c r="K12" t="s">
+        <v>561</v>
+      </c>
+      <c r="L12" t="s">
+        <v>546</v>
+      </c>
+      <c r="M12" t="s">
+        <v>543</v>
+      </c>
+      <c r="N12" t="s">
+        <v>518</v>
+      </c>
+      <c r="O12" t="s">
+        <v>518</v>
+      </c>
+      <c r="P12" t="s">
+        <v>518</v>
+      </c>
+      <c r="Q12" t="s">
+        <v>518</v>
+      </c>
+      <c r="R12" t="s">
+        <v>518</v>
+      </c>
+      <c r="S12" t="s">
+        <v>518</v>
+      </c>
+      <c r="T12" t="s">
+        <v>518</v>
+      </c>
+      <c r="U12" t="s">
+        <v>518</v>
+      </c>
+      <c r="V12" t="s">
+        <v>518</v>
+      </c>
+    </row>
+    <row r="13" spans="1:22">
+      <c r="A13" t="s">
+        <v>548</v>
+      </c>
+      <c r="B13" t="s">
+        <v>564</v>
+      </c>
+      <c r="C13" t="s">
+        <v>518</v>
+      </c>
+      <c r="D13" t="s">
+        <v>518</v>
+      </c>
+      <c r="E13" t="s">
+        <v>518</v>
+      </c>
+      <c r="F13" t="s">
+        <v>518</v>
+      </c>
+      <c r="G13" t="s">
+        <v>518</v>
+      </c>
+      <c r="H13" t="s">
+        <v>549</v>
+      </c>
+      <c r="I13" t="s">
+        <v>550</v>
+      </c>
+      <c r="J13" t="s">
+        <v>518</v>
+      </c>
+      <c r="K13" t="s">
+        <v>518</v>
+      </c>
+      <c r="L13" t="s">
+        <v>518</v>
+      </c>
+      <c r="M13" t="s">
+        <v>518</v>
+      </c>
+      <c r="N13" t="s">
+        <v>518</v>
+      </c>
+      <c r="O13" t="s">
+        <v>518</v>
+      </c>
+      <c r="P13" t="s">
+        <v>552</v>
+      </c>
+      <c r="Q13" t="s">
+        <v>518</v>
+      </c>
+      <c r="R13" t="s">
+        <v>518</v>
+      </c>
+      <c r="S13" t="s">
+        <v>518</v>
+      </c>
+      <c r="T13" t="s">
+        <v>518</v>
+      </c>
+      <c r="U13" t="s">
+        <v>518</v>
+      </c>
+      <c r="V13" t="s">
+        <v>518</v>
+      </c>
+    </row>
+    <row r="14" spans="1:22">
+      <c r="A14" t="s">
+        <v>553</v>
+      </c>
+      <c r="B14" t="s">
+        <v>564</v>
+      </c>
+      <c r="C14" t="s">
+        <v>518</v>
+      </c>
+      <c r="D14" t="s">
+        <v>518</v>
+      </c>
+      <c r="E14" t="s">
+        <v>518</v>
+      </c>
+      <c r="F14" t="s">
+        <v>554</v>
+      </c>
+      <c r="G14" t="s">
+        <v>534</v>
+      </c>
+      <c r="H14" t="s">
+        <v>513</v>
+      </c>
+      <c r="I14" t="s">
+        <v>514</v>
+      </c>
+      <c r="J14" t="s">
+        <v>518</v>
+      </c>
+      <c r="K14" t="s">
+        <v>518</v>
+      </c>
+      <c r="L14" t="s">
+        <v>518</v>
+      </c>
+      <c r="M14" t="s">
+        <v>518</v>
+      </c>
+      <c r="N14" t="s">
+        <v>518</v>
+      </c>
+      <c r="O14" t="s">
+        <v>518</v>
+      </c>
+      <c r="P14" t="s">
+        <v>518</v>
+      </c>
+      <c r="Q14" t="s">
+        <v>518</v>
+      </c>
+      <c r="R14" t="s">
+        <v>518</v>
+      </c>
+      <c r="S14" t="s">
+        <v>518</v>
+      </c>
+      <c r="T14" t="s">
+        <v>518</v>
+      </c>
+      <c r="U14" t="s">
+        <v>518</v>
+      </c>
+      <c r="V14" t="s">
+        <v>518</v>
+      </c>
+    </row>
+    <row r="15" spans="1:22">
+      <c r="A15" t="s">
+        <v>560</v>
+      </c>
+      <c r="B15" t="s">
+        <v>564</v>
+      </c>
+      <c r="C15" t="s">
+        <v>518</v>
+      </c>
+      <c r="D15" t="s">
+        <v>518</v>
+      </c>
+      <c r="E15" t="s">
+        <v>518</v>
+      </c>
+      <c r="F15" t="s">
+        <v>561</v>
+      </c>
+      <c r="G15" t="s">
+        <v>518</v>
+      </c>
+      <c r="H15" t="s">
+        <v>562</v>
+      </c>
+      <c r="I15" t="s">
+        <v>518</v>
+      </c>
+      <c r="J15" t="s">
+        <v>518</v>
+      </c>
+      <c r="K15" t="s">
+        <v>518</v>
+      </c>
+      <c r="L15" t="s">
+        <v>518</v>
+      </c>
+      <c r="M15" t="s">
+        <v>518</v>
+      </c>
+      <c r="N15" t="s">
+        <v>563</v>
+      </c>
+      <c r="O15" t="s">
+        <v>518</v>
+      </c>
+      <c r="P15" t="s">
+        <v>518</v>
+      </c>
+      <c r="Q15" t="s">
+        <v>518</v>
+      </c>
+      <c r="R15" t="s">
+        <v>518</v>
+      </c>
+      <c r="S15" t="s">
+        <v>518</v>
+      </c>
+      <c r="T15" t="s">
+        <v>518</v>
+      </c>
+      <c r="U15" t="s">
+        <v>518</v>
+      </c>
+      <c r="V15" t="s">
+        <v>518</v>
+      </c>
+    </row>
+    <row r="16" spans="1:22">
+      <c r="A16" t="s">
+        <v>565</v>
+      </c>
+      <c r="B16" t="s">
+        <v>564</v>
+      </c>
+      <c r="C16" t="s">
+        <v>518</v>
+      </c>
+      <c r="D16" t="s">
+        <v>518</v>
+      </c>
+      <c r="E16" t="s">
+        <v>540</v>
+      </c>
+      <c r="F16" t="s">
+        <v>561</v>
+      </c>
+      <c r="G16" t="s">
+        <v>518</v>
+      </c>
+      <c r="H16" t="s">
+        <v>566</v>
+      </c>
+      <c r="I16" t="s">
+        <v>567</v>
+      </c>
+      <c r="J16" t="s">
+        <v>518</v>
+      </c>
+      <c r="K16" t="s">
+        <v>518</v>
+      </c>
+      <c r="L16" t="s">
+        <v>518</v>
+      </c>
+      <c r="M16" t="s">
+        <v>518</v>
+      </c>
+      <c r="N16" t="s">
+        <v>518</v>
+      </c>
+      <c r="O16" t="s">
+        <v>518</v>
+      </c>
+      <c r="P16" t="s">
+        <v>518</v>
+      </c>
+      <c r="Q16" t="s">
+        <v>518</v>
+      </c>
+      <c r="R16" t="s">
+        <v>518</v>
+      </c>
+      <c r="S16" t="s">
+        <v>518</v>
+      </c>
+      <c r="T16" t="s">
+        <v>568</v>
+      </c>
+      <c r="U16" t="s">
+        <v>518</v>
+      </c>
+      <c r="V16" t="s">
+        <v>518</v>
+      </c>
+    </row>
+    <row r="17" spans="1:22">
+      <c r="A17" t="s">
+        <v>569</v>
+      </c>
+      <c r="B17" t="s">
+        <v>564</v>
+      </c>
+      <c r="C17" t="s">
+        <v>518</v>
+      </c>
+      <c r="D17" t="s">
+        <v>518</v>
+      </c>
+      <c r="E17" t="s">
+        <v>518</v>
+      </c>
+      <c r="F17" t="s">
+        <v>518</v>
+      </c>
+      <c r="G17" t="s">
+        <v>518</v>
+      </c>
+      <c r="H17" t="s">
+        <v>534</v>
+      </c>
+      <c r="I17" t="s">
+        <v>570</v>
+      </c>
+      <c r="J17" t="s">
+        <v>518</v>
+      </c>
+      <c r="K17" t="s">
+        <v>518</v>
+      </c>
+      <c r="L17" t="s">
+        <v>518</v>
+      </c>
+      <c r="M17" t="s">
+        <v>518</v>
+      </c>
+      <c r="N17" t="s">
+        <v>518</v>
+      </c>
+      <c r="O17" t="s">
+        <v>518</v>
+      </c>
+      <c r="P17" t="s">
+        <v>518</v>
+      </c>
+      <c r="Q17" t="s">
+        <v>518</v>
+      </c>
+      <c r="R17" t="s">
+        <v>518</v>
+      </c>
+      <c r="S17" t="s">
+        <v>518</v>
+      </c>
+      <c r="T17" t="s">
+        <v>518</v>
+      </c>
+      <c r="U17" t="s">
+        <v>571</v>
+      </c>
+      <c r="V17" t="s">
+        <v>518</v>
+      </c>
+    </row>
+    <row r="18" spans="1:22">
+      <c r="A18" t="s">
+        <v>572</v>
+      </c>
+      <c r="B18" t="s">
+        <v>564</v>
+      </c>
+      <c r="C18" t="s">
+        <v>518</v>
+      </c>
+      <c r="D18" t="s">
+        <v>518</v>
+      </c>
+      <c r="E18" t="s">
+        <v>518</v>
+      </c>
+      <c r="F18" t="s">
+        <v>561</v>
+      </c>
+      <c r="G18" t="s">
+        <v>534</v>
+      </c>
+      <c r="H18" t="s">
+        <v>573</v>
+      </c>
+      <c r="I18" t="s">
+        <v>574</v>
+      </c>
+      <c r="J18" t="s">
+        <v>518</v>
+      </c>
+      <c r="K18" t="s">
+        <v>518</v>
+      </c>
+      <c r="L18" t="s">
+        <v>518</v>
+      </c>
+      <c r="M18" t="s">
+        <v>518</v>
+      </c>
+      <c r="N18" t="s">
+        <v>518</v>
+      </c>
+      <c r="O18" t="s">
+        <v>518</v>
+      </c>
+      <c r="P18" t="s">
+        <v>518</v>
+      </c>
+      <c r="Q18" t="s">
+        <v>518</v>
+      </c>
+      <c r="R18" t="s">
+        <v>518</v>
+      </c>
+      <c r="S18" t="s">
+        <v>518</v>
+      </c>
+      <c r="T18" t="s">
+        <v>518</v>
+      </c>
+      <c r="U18" t="s">
+        <v>518</v>
+      </c>
+      <c r="V18" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="19" spans="1:22">
+      <c r="A19" t="s">
+        <v>578</v>
+      </c>
+      <c r="B19" t="s">
+        <v>564</v>
+      </c>
+      <c r="C19" t="s">
+        <v>518</v>
+      </c>
+      <c r="D19" t="s">
+        <v>518</v>
+      </c>
+      <c r="E19" t="s">
+        <v>518</v>
+      </c>
+      <c r="F19" t="s">
+        <v>518</v>
+      </c>
+      <c r="G19" t="s">
+        <v>518</v>
+      </c>
+      <c r="H19" t="s">
+        <v>534</v>
+      </c>
+      <c r="I19" t="s">
+        <v>576</v>
+      </c>
+      <c r="J19" t="s">
+        <v>518</v>
+      </c>
+      <c r="K19" t="s">
+        <v>561</v>
+      </c>
+      <c r="L19" t="s">
+        <v>534</v>
+      </c>
+      <c r="M19" t="s">
+        <v>577</v>
+      </c>
+      <c r="N19" t="s">
+        <v>518</v>
+      </c>
+      <c r="O19" t="s">
+        <v>518</v>
+      </c>
+      <c r="P19" t="s">
+        <v>518</v>
+      </c>
+      <c r="Q19" t="s">
+        <v>518</v>
+      </c>
+      <c r="R19" t="s">
+        <v>518</v>
+      </c>
+      <c r="S19" t="s">
+        <v>518</v>
+      </c>
+      <c r="T19" t="s">
+        <v>518</v>
+      </c>
+      <c r="U19" t="s">
+        <v>518</v>
+      </c>
+      <c r="V19" t="s">
+        <v>518</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="8">
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="E3:K3"/>
+    <mergeCell ref="N4:V4"/>
+    <mergeCell ref="F4:H4"/>
+    <mergeCell ref="I4:J4"/>
+    <mergeCell ref="A11:A12"/>
+    <mergeCell ref="E11:E12"/>
+    <mergeCell ref="K4:M4"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -4156,22 +5535,22 @@
       <c r="R5" s="19"/>
     </row>
     <row r="6" spans="3:21">
-      <c r="C6" s="77" t="s">
+      <c r="C6" s="75" t="s">
         <v>343</v>
       </c>
-      <c r="D6" s="78"/>
-      <c r="E6" s="78"/>
-      <c r="F6" s="78"/>
-      <c r="G6" s="78"/>
-      <c r="H6" s="78"/>
-      <c r="I6" s="78"/>
-      <c r="J6" s="78"/>
-      <c r="K6" s="78"/>
-      <c r="L6" s="78"/>
-      <c r="M6" s="78"/>
-      <c r="N6" s="78"/>
-      <c r="O6" s="78"/>
-      <c r="P6" s="79"/>
+      <c r="D6" s="76"/>
+      <c r="E6" s="76"/>
+      <c r="F6" s="76"/>
+      <c r="G6" s="76"/>
+      <c r="H6" s="76"/>
+      <c r="I6" s="76"/>
+      <c r="J6" s="76"/>
+      <c r="K6" s="76"/>
+      <c r="L6" s="76"/>
+      <c r="M6" s="76"/>
+      <c r="N6" s="76"/>
+      <c r="O6" s="76"/>
+      <c r="P6" s="77"/>
       <c r="Q6" s="22"/>
       <c r="R6" s="22" t="s">
         <v>218</v>
@@ -4179,24 +5558,24 @@
       <c r="U6" s="2"/>
     </row>
     <row r="7" spans="3:21">
-      <c r="C7" s="71" t="s">
+      <c r="C7" s="79" t="s">
         <v>227</v>
       </c>
-      <c r="D7" s="72"/>
-      <c r="E7" s="72"/>
-      <c r="F7" s="72"/>
-      <c r="G7" s="72"/>
-      <c r="H7" s="72"/>
-      <c r="I7" s="73"/>
-      <c r="J7" s="71" t="s">
+      <c r="D7" s="80"/>
+      <c r="E7" s="80"/>
+      <c r="F7" s="80"/>
+      <c r="G7" s="80"/>
+      <c r="H7" s="80"/>
+      <c r="I7" s="81"/>
+      <c r="J7" s="79" t="s">
         <v>230</v>
       </c>
-      <c r="K7" s="72"/>
-      <c r="L7" s="72"/>
-      <c r="M7" s="72"/>
-      <c r="N7" s="72"/>
-      <c r="O7" s="72"/>
-      <c r="P7" s="73"/>
+      <c r="K7" s="80"/>
+      <c r="L7" s="80"/>
+      <c r="M7" s="80"/>
+      <c r="N7" s="80"/>
+      <c r="O7" s="80"/>
+      <c r="P7" s="81"/>
       <c r="Q7" s="19"/>
       <c r="R7" s="19"/>
       <c r="U7" s="2"/>
@@ -4249,28 +5628,28 @@
       <c r="U8" s="2"/>
     </row>
     <row r="9" spans="3:21">
-      <c r="C9" s="81" t="s">
+      <c r="C9" s="86" t="s">
         <v>234</v>
       </c>
-      <c r="D9" s="77" t="b">
-        <v>1</v>
-      </c>
-      <c r="E9" s="78"/>
-      <c r="F9" s="78"/>
-      <c r="G9" s="78"/>
-      <c r="H9" s="78"/>
-      <c r="I9" s="79"/>
-      <c r="J9" s="81" t="s">
+      <c r="D9" s="75" t="b">
+        <v>1</v>
+      </c>
+      <c r="E9" s="76"/>
+      <c r="F9" s="76"/>
+      <c r="G9" s="76"/>
+      <c r="H9" s="76"/>
+      <c r="I9" s="77"/>
+      <c r="J9" s="86" t="s">
         <v>218</v>
       </c>
-      <c r="K9" s="80" t="b">
-        <v>1</v>
-      </c>
-      <c r="L9" s="80"/>
-      <c r="M9" s="80"/>
-      <c r="N9" s="80"/>
-      <c r="O9" s="80"/>
-      <c r="P9" s="80"/>
+      <c r="K9" s="74" t="b">
+        <v>1</v>
+      </c>
+      <c r="L9" s="74"/>
+      <c r="M9" s="74"/>
+      <c r="N9" s="74"/>
+      <c r="O9" s="74"/>
+      <c r="P9" s="74"/>
       <c r="Q9" s="24" t="b">
         <v>1</v>
       </c>
@@ -4286,16 +5665,16 @@
       </c>
     </row>
     <row r="10" spans="3:21">
-      <c r="C10" s="82"/>
-      <c r="D10" s="74" t="b">
-        <v>1</v>
-      </c>
-      <c r="E10" s="75"/>
-      <c r="F10" s="75"/>
-      <c r="G10" s="75"/>
-      <c r="H10" s="75"/>
-      <c r="I10" s="76"/>
-      <c r="J10" s="82"/>
+      <c r="C10" s="87"/>
+      <c r="D10" s="82" t="b">
+        <v>1</v>
+      </c>
+      <c r="E10" s="83"/>
+      <c r="F10" s="83"/>
+      <c r="G10" s="83"/>
+      <c r="H10" s="83"/>
+      <c r="I10" s="84"/>
+      <c r="J10" s="87"/>
       <c r="K10" s="85" t="b">
         <v>0</v>
       </c>
@@ -4319,24 +5698,24 @@
       </c>
     </row>
     <row r="11" spans="3:21">
-      <c r="C11" s="82"/>
-      <c r="D11" s="77" t="b">
+      <c r="C11" s="87"/>
+      <c r="D11" s="75" t="b">
         <v>0</v>
       </c>
-      <c r="E11" s="78"/>
-      <c r="F11" s="78"/>
-      <c r="G11" s="78"/>
-      <c r="H11" s="78"/>
-      <c r="I11" s="79"/>
-      <c r="J11" s="82"/>
-      <c r="K11" s="80" t="b">
-        <v>1</v>
-      </c>
-      <c r="L11" s="80"/>
-      <c r="M11" s="80"/>
-      <c r="N11" s="80"/>
-      <c r="O11" s="80"/>
-      <c r="P11" s="80"/>
+      <c r="E11" s="76"/>
+      <c r="F11" s="76"/>
+      <c r="G11" s="76"/>
+      <c r="H11" s="76"/>
+      <c r="I11" s="77"/>
+      <c r="J11" s="87"/>
+      <c r="K11" s="74" t="b">
+        <v>1</v>
+      </c>
+      <c r="L11" s="74"/>
+      <c r="M11" s="74"/>
+      <c r="N11" s="74"/>
+      <c r="O11" s="74"/>
+      <c r="P11" s="74"/>
       <c r="Q11" s="24" t="b">
         <v>1</v>
       </c>
@@ -4352,24 +5731,24 @@
       </c>
     </row>
     <row r="12" spans="3:21">
-      <c r="C12" s="83"/>
-      <c r="D12" s="77" t="b">
+      <c r="C12" s="88"/>
+      <c r="D12" s="75" t="b">
         <v>0</v>
       </c>
-      <c r="E12" s="78"/>
-      <c r="F12" s="78"/>
-      <c r="G12" s="78"/>
-      <c r="H12" s="78"/>
-      <c r="I12" s="79"/>
-      <c r="J12" s="83"/>
-      <c r="K12" s="80" t="b">
+      <c r="E12" s="76"/>
+      <c r="F12" s="76"/>
+      <c r="G12" s="76"/>
+      <c r="H12" s="76"/>
+      <c r="I12" s="77"/>
+      <c r="J12" s="88"/>
+      <c r="K12" s="74" t="b">
         <v>0</v>
       </c>
-      <c r="L12" s="80"/>
-      <c r="M12" s="80"/>
-      <c r="N12" s="80"/>
-      <c r="O12" s="80"/>
-      <c r="P12" s="80"/>
+      <c r="L12" s="74"/>
+      <c r="M12" s="74"/>
+      <c r="N12" s="74"/>
+      <c r="O12" s="74"/>
+      <c r="P12" s="74"/>
       <c r="Q12" s="24" t="b">
         <v>1</v>
       </c>
@@ -4390,22 +5769,22 @@
       <c r="U13" s="2"/>
     </row>
     <row r="14" spans="3:21">
-      <c r="C14" s="77" t="s">
+      <c r="C14" s="75" t="s">
         <v>344</v>
       </c>
-      <c r="D14" s="78"/>
-      <c r="E14" s="78"/>
-      <c r="F14" s="78"/>
-      <c r="G14" s="78"/>
-      <c r="H14" s="78"/>
-      <c r="I14" s="78"/>
-      <c r="J14" s="78"/>
-      <c r="K14" s="78"/>
-      <c r="L14" s="78"/>
-      <c r="M14" s="78"/>
-      <c r="N14" s="78"/>
-      <c r="O14" s="78"/>
-      <c r="P14" s="79"/>
+      <c r="D14" s="76"/>
+      <c r="E14" s="76"/>
+      <c r="F14" s="76"/>
+      <c r="G14" s="76"/>
+      <c r="H14" s="76"/>
+      <c r="I14" s="76"/>
+      <c r="J14" s="76"/>
+      <c r="K14" s="76"/>
+      <c r="L14" s="76"/>
+      <c r="M14" s="76"/>
+      <c r="N14" s="76"/>
+      <c r="O14" s="76"/>
+      <c r="P14" s="77"/>
       <c r="Q14" s="19"/>
       <c r="R14" s="22" t="s">
         <v>219</v>
@@ -4413,24 +5792,24 @@
       <c r="U14" s="2"/>
     </row>
     <row r="15" spans="3:21">
-      <c r="C15" s="71" t="s">
+      <c r="C15" s="79" t="s">
         <v>228</v>
       </c>
-      <c r="D15" s="72"/>
-      <c r="E15" s="72"/>
-      <c r="F15" s="72"/>
-      <c r="G15" s="72"/>
-      <c r="H15" s="72"/>
-      <c r="I15" s="73"/>
-      <c r="J15" s="71" t="s">
+      <c r="D15" s="80"/>
+      <c r="E15" s="80"/>
+      <c r="F15" s="80"/>
+      <c r="G15" s="80"/>
+      <c r="H15" s="80"/>
+      <c r="I15" s="81"/>
+      <c r="J15" s="79" t="s">
         <v>230</v>
       </c>
-      <c r="K15" s="72"/>
-      <c r="L15" s="72"/>
-      <c r="M15" s="72"/>
-      <c r="N15" s="72"/>
-      <c r="O15" s="72"/>
-      <c r="P15" s="73"/>
+      <c r="K15" s="80"/>
+      <c r="L15" s="80"/>
+      <c r="M15" s="80"/>
+      <c r="N15" s="80"/>
+      <c r="O15" s="80"/>
+      <c r="P15" s="81"/>
       <c r="Q15" s="19"/>
       <c r="R15" s="19"/>
       <c r="U15" s="2"/>
@@ -4483,28 +5862,28 @@
       <c r="U16" s="2"/>
     </row>
     <row r="17" spans="3:21">
-      <c r="C17" s="81" t="s">
+      <c r="C17" s="86" t="s">
         <v>234</v>
       </c>
-      <c r="D17" s="77" t="b">
-        <v>1</v>
-      </c>
-      <c r="E17" s="78"/>
-      <c r="F17" s="78"/>
-      <c r="G17" s="78"/>
-      <c r="H17" s="78"/>
-      <c r="I17" s="79"/>
-      <c r="J17" s="81" t="s">
+      <c r="D17" s="75" t="b">
+        <v>1</v>
+      </c>
+      <c r="E17" s="76"/>
+      <c r="F17" s="76"/>
+      <c r="G17" s="76"/>
+      <c r="H17" s="76"/>
+      <c r="I17" s="77"/>
+      <c r="J17" s="86" t="s">
         <v>219</v>
       </c>
-      <c r="K17" s="80" t="b">
-        <v>1</v>
-      </c>
-      <c r="L17" s="80"/>
-      <c r="M17" s="80"/>
-      <c r="N17" s="80"/>
-      <c r="O17" s="80"/>
-      <c r="P17" s="80"/>
+      <c r="K17" s="74" t="b">
+        <v>1</v>
+      </c>
+      <c r="L17" s="74"/>
+      <c r="M17" s="74"/>
+      <c r="N17" s="74"/>
+      <c r="O17" s="74"/>
+      <c r="P17" s="74"/>
       <c r="Q17" s="24" t="b">
         <v>1</v>
       </c>
@@ -4512,24 +5891,24 @@
       <c r="U17" s="2"/>
     </row>
     <row r="18" spans="3:21">
-      <c r="C18" s="82"/>
-      <c r="D18" s="77" t="b">
-        <v>1</v>
-      </c>
-      <c r="E18" s="78"/>
-      <c r="F18" s="78"/>
-      <c r="G18" s="78"/>
-      <c r="H18" s="78"/>
-      <c r="I18" s="79"/>
-      <c r="J18" s="82"/>
-      <c r="K18" s="80" t="b">
+      <c r="C18" s="87"/>
+      <c r="D18" s="75" t="b">
+        <v>1</v>
+      </c>
+      <c r="E18" s="76"/>
+      <c r="F18" s="76"/>
+      <c r="G18" s="76"/>
+      <c r="H18" s="76"/>
+      <c r="I18" s="77"/>
+      <c r="J18" s="87"/>
+      <c r="K18" s="74" t="b">
         <v>0</v>
       </c>
-      <c r="L18" s="80"/>
-      <c r="M18" s="80"/>
-      <c r="N18" s="80"/>
-      <c r="O18" s="80"/>
-      <c r="P18" s="80"/>
+      <c r="L18" s="74"/>
+      <c r="M18" s="74"/>
+      <c r="N18" s="74"/>
+      <c r="O18" s="74"/>
+      <c r="P18" s="74"/>
       <c r="Q18" s="24" t="b">
         <v>1</v>
       </c>
@@ -4537,16 +5916,16 @@
       <c r="U18" s="2"/>
     </row>
     <row r="19" spans="3:21">
-      <c r="C19" s="82"/>
-      <c r="D19" s="74" t="b">
+      <c r="C19" s="87"/>
+      <c r="D19" s="82" t="b">
         <v>0</v>
       </c>
-      <c r="E19" s="75"/>
-      <c r="F19" s="75"/>
-      <c r="G19" s="75"/>
-      <c r="H19" s="75"/>
-      <c r="I19" s="76"/>
-      <c r="J19" s="82"/>
+      <c r="E19" s="83"/>
+      <c r="F19" s="83"/>
+      <c r="G19" s="83"/>
+      <c r="H19" s="83"/>
+      <c r="I19" s="84"/>
+      <c r="J19" s="87"/>
       <c r="K19" s="85" t="b">
         <v>1</v>
       </c>
@@ -4562,24 +5941,24 @@
       <c r="U19" s="2"/>
     </row>
     <row r="20" spans="3:21">
-      <c r="C20" s="83"/>
-      <c r="D20" s="77" t="b">
+      <c r="C20" s="88"/>
+      <c r="D20" s="75" t="b">
         <v>0</v>
       </c>
-      <c r="E20" s="78"/>
-      <c r="F20" s="78"/>
-      <c r="G20" s="78"/>
-      <c r="H20" s="78"/>
-      <c r="I20" s="79"/>
-      <c r="J20" s="83"/>
-      <c r="K20" s="80" t="b">
+      <c r="E20" s="76"/>
+      <c r="F20" s="76"/>
+      <c r="G20" s="76"/>
+      <c r="H20" s="76"/>
+      <c r="I20" s="77"/>
+      <c r="J20" s="88"/>
+      <c r="K20" s="74" t="b">
         <v>0</v>
       </c>
-      <c r="L20" s="80"/>
-      <c r="M20" s="80"/>
-      <c r="N20" s="80"/>
-      <c r="O20" s="80"/>
-      <c r="P20" s="80"/>
+      <c r="L20" s="74"/>
+      <c r="M20" s="74"/>
+      <c r="N20" s="74"/>
+      <c r="O20" s="74"/>
+      <c r="P20" s="74"/>
       <c r="Q20" s="27" t="b">
         <v>1</v>
       </c>
@@ -4590,46 +5969,46 @@
       <c r="R21" s="19"/>
     </row>
     <row r="22" spans="3:21">
-      <c r="C22" s="77" t="s">
+      <c r="C22" s="75" t="s">
         <v>345</v>
       </c>
-      <c r="D22" s="78"/>
-      <c r="E22" s="78"/>
-      <c r="F22" s="78"/>
-      <c r="G22" s="78"/>
-      <c r="H22" s="78"/>
-      <c r="I22" s="78"/>
-      <c r="J22" s="78"/>
-      <c r="K22" s="78"/>
-      <c r="L22" s="78"/>
-      <c r="M22" s="78"/>
-      <c r="N22" s="78"/>
-      <c r="O22" s="78"/>
-      <c r="P22" s="79"/>
+      <c r="D22" s="76"/>
+      <c r="E22" s="76"/>
+      <c r="F22" s="76"/>
+      <c r="G22" s="76"/>
+      <c r="H22" s="76"/>
+      <c r="I22" s="76"/>
+      <c r="J22" s="76"/>
+      <c r="K22" s="76"/>
+      <c r="L22" s="76"/>
+      <c r="M22" s="76"/>
+      <c r="N22" s="76"/>
+      <c r="O22" s="76"/>
+      <c r="P22" s="77"/>
       <c r="Q22" s="19"/>
       <c r="R22" s="22" t="s">
         <v>217</v>
       </c>
     </row>
     <row r="23" spans="3:21">
-      <c r="C23" s="71" t="s">
+      <c r="C23" s="79" t="s">
         <v>229</v>
       </c>
-      <c r="D23" s="72"/>
-      <c r="E23" s="72"/>
-      <c r="F23" s="72"/>
-      <c r="G23" s="72"/>
-      <c r="H23" s="72"/>
-      <c r="I23" s="73"/>
-      <c r="J23" s="71" t="s">
+      <c r="D23" s="80"/>
+      <c r="E23" s="80"/>
+      <c r="F23" s="80"/>
+      <c r="G23" s="80"/>
+      <c r="H23" s="80"/>
+      <c r="I23" s="81"/>
+      <c r="J23" s="79" t="s">
         <v>231</v>
       </c>
-      <c r="K23" s="72"/>
-      <c r="L23" s="72"/>
-      <c r="M23" s="72"/>
-      <c r="N23" s="72"/>
-      <c r="O23" s="72"/>
-      <c r="P23" s="73"/>
+      <c r="K23" s="80"/>
+      <c r="L23" s="80"/>
+      <c r="M23" s="80"/>
+      <c r="N23" s="80"/>
+      <c r="O23" s="80"/>
+      <c r="P23" s="81"/>
       <c r="Q23" s="19"/>
       <c r="R23" s="19"/>
     </row>
@@ -4680,44 +6059,44 @@
       <c r="R24" s="19"/>
     </row>
     <row r="25" spans="3:21">
-      <c r="C25" s="81" t="s">
+      <c r="C25" s="86" t="s">
         <v>234</v>
       </c>
-      <c r="D25" s="77" t="b">
-        <v>1</v>
-      </c>
-      <c r="E25" s="78"/>
-      <c r="F25" s="78"/>
-      <c r="G25" s="78"/>
-      <c r="H25" s="78"/>
-      <c r="I25" s="79"/>
-      <c r="J25" s="84" t="s">
+      <c r="D25" s="75" t="b">
+        <v>1</v>
+      </c>
+      <c r="E25" s="76"/>
+      <c r="F25" s="76"/>
+      <c r="G25" s="76"/>
+      <c r="H25" s="76"/>
+      <c r="I25" s="77"/>
+      <c r="J25" s="89" t="s">
         <v>233</v>
       </c>
-      <c r="K25" s="80" t="b">
-        <v>1</v>
-      </c>
-      <c r="L25" s="80"/>
-      <c r="M25" s="80"/>
-      <c r="N25" s="80"/>
-      <c r="O25" s="80"/>
-      <c r="P25" s="80"/>
+      <c r="K25" s="74" t="b">
+        <v>1</v>
+      </c>
+      <c r="L25" s="74"/>
+      <c r="M25" s="74"/>
+      <c r="N25" s="74"/>
+      <c r="O25" s="74"/>
+      <c r="P25" s="74"/>
       <c r="Q25" s="24" t="b">
         <v>1</v>
       </c>
       <c r="R25" s="19"/>
     </row>
     <row r="26" spans="3:21">
-      <c r="C26" s="82"/>
-      <c r="D26" s="74" t="b">
-        <v>1</v>
-      </c>
-      <c r="E26" s="75"/>
-      <c r="F26" s="75"/>
-      <c r="G26" s="75"/>
-      <c r="H26" s="75"/>
-      <c r="I26" s="76"/>
-      <c r="J26" s="82"/>
+      <c r="C26" s="87"/>
+      <c r="D26" s="82" t="b">
+        <v>1</v>
+      </c>
+      <c r="E26" s="83"/>
+      <c r="F26" s="83"/>
+      <c r="G26" s="83"/>
+      <c r="H26" s="83"/>
+      <c r="I26" s="84"/>
+      <c r="J26" s="87"/>
       <c r="K26" s="85" t="b">
         <v>0</v>
       </c>
@@ -4732,16 +6111,16 @@
       <c r="R26" s="19"/>
     </row>
     <row r="27" spans="3:21">
-      <c r="C27" s="82"/>
-      <c r="D27" s="74" t="b">
+      <c r="C27" s="87"/>
+      <c r="D27" s="82" t="b">
         <v>0</v>
       </c>
-      <c r="E27" s="75"/>
-      <c r="F27" s="75"/>
-      <c r="G27" s="75"/>
-      <c r="H27" s="75"/>
-      <c r="I27" s="76"/>
-      <c r="J27" s="82"/>
+      <c r="E27" s="83"/>
+      <c r="F27" s="83"/>
+      <c r="G27" s="83"/>
+      <c r="H27" s="83"/>
+      <c r="I27" s="84"/>
+      <c r="J27" s="87"/>
       <c r="K27" s="85" t="b">
         <v>1</v>
       </c>
@@ -4756,24 +6135,24 @@
       <c r="R27" s="19"/>
     </row>
     <row r="28" spans="3:21">
-      <c r="C28" s="83"/>
-      <c r="D28" s="77" t="b">
+      <c r="C28" s="88"/>
+      <c r="D28" s="75" t="b">
         <v>0</v>
       </c>
-      <c r="E28" s="78"/>
-      <c r="F28" s="78"/>
-      <c r="G28" s="78"/>
-      <c r="H28" s="78"/>
-      <c r="I28" s="79"/>
-      <c r="J28" s="83"/>
-      <c r="K28" s="80" t="b">
+      <c r="E28" s="76"/>
+      <c r="F28" s="76"/>
+      <c r="G28" s="76"/>
+      <c r="H28" s="76"/>
+      <c r="I28" s="77"/>
+      <c r="J28" s="88"/>
+      <c r="K28" s="74" t="b">
         <v>0</v>
       </c>
-      <c r="L28" s="80"/>
-      <c r="M28" s="80"/>
-      <c r="N28" s="80"/>
-      <c r="O28" s="80"/>
-      <c r="P28" s="80"/>
+      <c r="L28" s="74"/>
+      <c r="M28" s="74"/>
+      <c r="N28" s="74"/>
+      <c r="O28" s="74"/>
+      <c r="P28" s="74"/>
       <c r="Q28" s="27" t="b">
         <v>1</v>
       </c>
@@ -4783,46 +6162,46 @@
       <c r="R29" s="19"/>
     </row>
     <row r="30" spans="3:21">
-      <c r="C30" s="77" t="s">
+      <c r="C30" s="75" t="s">
         <v>346</v>
       </c>
-      <c r="D30" s="78"/>
-      <c r="E30" s="78"/>
-      <c r="F30" s="78"/>
-      <c r="G30" s="78"/>
-      <c r="H30" s="78"/>
-      <c r="I30" s="78"/>
-      <c r="J30" s="78"/>
-      <c r="K30" s="78"/>
-      <c r="L30" s="78"/>
-      <c r="M30" s="78"/>
-      <c r="N30" s="78"/>
-      <c r="O30" s="78"/>
-      <c r="P30" s="79"/>
+      <c r="D30" s="76"/>
+      <c r="E30" s="76"/>
+      <c r="F30" s="76"/>
+      <c r="G30" s="76"/>
+      <c r="H30" s="76"/>
+      <c r="I30" s="76"/>
+      <c r="J30" s="76"/>
+      <c r="K30" s="76"/>
+      <c r="L30" s="76"/>
+      <c r="M30" s="76"/>
+      <c r="N30" s="76"/>
+      <c r="O30" s="76"/>
+      <c r="P30" s="77"/>
       <c r="Q30" s="19"/>
       <c r="R30" s="22" t="s">
         <v>220</v>
       </c>
     </row>
     <row r="31" spans="3:21">
-      <c r="C31" s="71" t="s">
+      <c r="C31" s="79" t="s">
         <v>237</v>
       </c>
-      <c r="D31" s="72"/>
-      <c r="E31" s="72"/>
-      <c r="F31" s="72"/>
-      <c r="G31" s="72"/>
-      <c r="H31" s="72"/>
-      <c r="I31" s="73"/>
-      <c r="J31" s="71" t="s">
+      <c r="D31" s="80"/>
+      <c r="E31" s="80"/>
+      <c r="F31" s="80"/>
+      <c r="G31" s="80"/>
+      <c r="H31" s="80"/>
+      <c r="I31" s="81"/>
+      <c r="J31" s="79" t="s">
         <v>238</v>
       </c>
-      <c r="K31" s="72"/>
-      <c r="L31" s="72"/>
-      <c r="M31" s="72"/>
-      <c r="N31" s="72"/>
-      <c r="O31" s="72"/>
-      <c r="P31" s="73"/>
+      <c r="K31" s="80"/>
+      <c r="L31" s="80"/>
+      <c r="M31" s="80"/>
+      <c r="N31" s="80"/>
+      <c r="O31" s="80"/>
+      <c r="P31" s="81"/>
       <c r="Q31" s="19"/>
       <c r="R31" s="19"/>
     </row>
@@ -4876,25 +6255,25 @@
       <c r="C33" s="24" t="s">
         <v>236</v>
       </c>
-      <c r="D33" s="77" t="s">
+      <c r="D33" s="75" t="s">
         <v>216</v>
       </c>
-      <c r="E33" s="78"/>
-      <c r="F33" s="78"/>
-      <c r="G33" s="78"/>
-      <c r="H33" s="78"/>
-      <c r="I33" s="79"/>
+      <c r="E33" s="76"/>
+      <c r="F33" s="76"/>
+      <c r="G33" s="76"/>
+      <c r="H33" s="76"/>
+      <c r="I33" s="77"/>
       <c r="J33" s="24" t="s">
         <v>235</v>
       </c>
-      <c r="K33" s="80" t="s">
+      <c r="K33" s="74" t="s">
         <v>221</v>
       </c>
-      <c r="L33" s="80"/>
-      <c r="M33" s="80"/>
-      <c r="N33" s="80"/>
-      <c r="O33" s="80"/>
-      <c r="P33" s="80"/>
+      <c r="L33" s="74"/>
+      <c r="M33" s="74"/>
+      <c r="N33" s="74"/>
+      <c r="O33" s="74"/>
+      <c r="P33" s="74"/>
       <c r="Q33" s="24" t="s">
         <v>239</v>
       </c>
@@ -4908,19 +6287,19 @@
     <row r="36" spans="3:21" ht="26">
       <c r="C36" s="20"/>
       <c r="D36" s="20"/>
-      <c r="F36" s="87" t="s">
+      <c r="F36" s="78" t="s">
         <v>253</v>
       </c>
-      <c r="G36" s="87"/>
-      <c r="H36" s="87"/>
-      <c r="I36" s="87"/>
-      <c r="J36" s="87"/>
-      <c r="K36" s="87"/>
-      <c r="L36" s="87"/>
-      <c r="M36" s="87"/>
-      <c r="N36" s="87"/>
-      <c r="O36" s="87"/>
-      <c r="P36" s="87"/>
+      <c r="G36" s="78"/>
+      <c r="H36" s="78"/>
+      <c r="I36" s="78"/>
+      <c r="J36" s="78"/>
+      <c r="K36" s="78"/>
+      <c r="L36" s="78"/>
+      <c r="M36" s="78"/>
+      <c r="N36" s="78"/>
+      <c r="O36" s="78"/>
+      <c r="P36" s="78"/>
     </row>
     <row r="37" spans="3:21">
       <c r="C37" s="30" t="s">
@@ -5216,18 +6595,18 @@
       </c>
     </row>
     <row r="65" spans="3:12">
-      <c r="C65" s="86" t="s">
+      <c r="C65" s="73" t="s">
         <v>286</v>
       </c>
-      <c r="D65" s="86"/>
-      <c r="E65" s="86"/>
-      <c r="F65" s="86"/>
-      <c r="G65" s="86"/>
-      <c r="H65" s="86"/>
-      <c r="I65" s="86"/>
-      <c r="J65" s="86"/>
-      <c r="K65" s="86"/>
-      <c r="L65" s="86"/>
+      <c r="D65" s="73"/>
+      <c r="E65" s="73"/>
+      <c r="F65" s="73"/>
+      <c r="G65" s="73"/>
+      <c r="H65" s="73"/>
+      <c r="I65" s="73"/>
+      <c r="J65" s="73"/>
+      <c r="K65" s="73"/>
+      <c r="L65" s="73"/>
     </row>
     <row r="66" spans="3:12">
       <c r="C66" s="19" t="b">
@@ -5385,18 +6764,18 @@
       <c r="G70" s="19"/>
     </row>
     <row r="71" spans="3:12">
-      <c r="C71" s="86" t="s">
+      <c r="C71" s="73" t="s">
         <v>287</v>
       </c>
-      <c r="D71" s="86"/>
-      <c r="E71" s="86"/>
-      <c r="F71" s="86"/>
-      <c r="G71" s="86"/>
-      <c r="H71" s="86"/>
-      <c r="I71" s="86"/>
-      <c r="J71" s="86"/>
-      <c r="K71" s="86"/>
-      <c r="L71" s="86"/>
+      <c r="D71" s="73"/>
+      <c r="E71" s="73"/>
+      <c r="F71" s="73"/>
+      <c r="G71" s="73"/>
+      <c r="H71" s="73"/>
+      <c r="I71" s="73"/>
+      <c r="J71" s="73"/>
+      <c r="K71" s="73"/>
+      <c r="L71" s="73"/>
     </row>
     <row r="72" spans="3:12">
       <c r="C72" s="19">
@@ -5719,18 +7098,18 @@
       </c>
     </row>
     <row r="81" spans="3:12">
-      <c r="C81" s="86" t="s">
+      <c r="C81" s="73" t="s">
         <v>298</v>
       </c>
-      <c r="D81" s="86"/>
-      <c r="E81" s="86"/>
-      <c r="F81" s="86"/>
-      <c r="G81" s="86"/>
-      <c r="H81" s="86"/>
-      <c r="I81" s="86"/>
-      <c r="J81" s="86"/>
-      <c r="K81" s="86"/>
-      <c r="L81" s="86"/>
+      <c r="D81" s="73"/>
+      <c r="E81" s="73"/>
+      <c r="F81" s="73"/>
+      <c r="G81" s="73"/>
+      <c r="H81" s="73"/>
+      <c r="I81" s="73"/>
+      <c r="J81" s="73"/>
+      <c r="K81" s="73"/>
+      <c r="L81" s="73"/>
     </row>
     <row r="82" spans="3:12">
       <c r="C82" s="19">
@@ -6244,22 +7623,22 @@
     </row>
   </sheetData>
   <mergeCells count="48">
-    <mergeCell ref="C81:L81"/>
-    <mergeCell ref="C65:L65"/>
-    <mergeCell ref="C71:L71"/>
-    <mergeCell ref="K33:P33"/>
-    <mergeCell ref="D33:I33"/>
-    <mergeCell ref="F36:P36"/>
-    <mergeCell ref="C7:I7"/>
-    <mergeCell ref="D12:I12"/>
-    <mergeCell ref="D11:I11"/>
-    <mergeCell ref="D10:I10"/>
-    <mergeCell ref="D9:I9"/>
-    <mergeCell ref="C22:P22"/>
-    <mergeCell ref="K9:P9"/>
-    <mergeCell ref="K10:P10"/>
-    <mergeCell ref="K11:P11"/>
-    <mergeCell ref="K12:P12"/>
+    <mergeCell ref="J31:P31"/>
+    <mergeCell ref="J23:P23"/>
+    <mergeCell ref="J7:P7"/>
+    <mergeCell ref="J15:P15"/>
+    <mergeCell ref="D26:I26"/>
+    <mergeCell ref="D27:I27"/>
+    <mergeCell ref="D28:I28"/>
+    <mergeCell ref="D20:I20"/>
+    <mergeCell ref="D19:I19"/>
+    <mergeCell ref="D18:I18"/>
+    <mergeCell ref="K20:P20"/>
+    <mergeCell ref="D17:I17"/>
+    <mergeCell ref="C15:I15"/>
+    <mergeCell ref="C23:I23"/>
+    <mergeCell ref="C31:I31"/>
+    <mergeCell ref="C30:P30"/>
     <mergeCell ref="C6:P6"/>
     <mergeCell ref="J9:J12"/>
     <mergeCell ref="J25:J28"/>
@@ -6276,22 +7655,22 @@
     <mergeCell ref="K17:P17"/>
     <mergeCell ref="K18:P18"/>
     <mergeCell ref="K19:P19"/>
-    <mergeCell ref="J31:P31"/>
-    <mergeCell ref="J23:P23"/>
-    <mergeCell ref="J7:P7"/>
-    <mergeCell ref="J15:P15"/>
-    <mergeCell ref="D26:I26"/>
-    <mergeCell ref="D27:I27"/>
-    <mergeCell ref="D28:I28"/>
-    <mergeCell ref="D20:I20"/>
-    <mergeCell ref="D19:I19"/>
-    <mergeCell ref="D18:I18"/>
-    <mergeCell ref="K20:P20"/>
-    <mergeCell ref="D17:I17"/>
-    <mergeCell ref="C15:I15"/>
-    <mergeCell ref="C23:I23"/>
-    <mergeCell ref="C31:I31"/>
-    <mergeCell ref="C30:P30"/>
+    <mergeCell ref="C22:P22"/>
+    <mergeCell ref="K9:P9"/>
+    <mergeCell ref="K10:P10"/>
+    <mergeCell ref="K11:P11"/>
+    <mergeCell ref="K12:P12"/>
+    <mergeCell ref="C7:I7"/>
+    <mergeCell ref="D12:I12"/>
+    <mergeCell ref="D11:I11"/>
+    <mergeCell ref="D10:I10"/>
+    <mergeCell ref="D9:I9"/>
+    <mergeCell ref="C81:L81"/>
+    <mergeCell ref="C65:L65"/>
+    <mergeCell ref="C71:L71"/>
+    <mergeCell ref="K33:P33"/>
+    <mergeCell ref="D33:I33"/>
+    <mergeCell ref="F36:P36"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -6385,62 +7764,62 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:33">
-      <c r="B2" s="88" t="s">
+      <c r="B2" s="90" t="s">
         <v>68</v>
       </c>
-      <c r="C2" s="88"/>
-      <c r="D2" s="88"/>
-      <c r="E2" s="88"/>
+      <c r="C2" s="90"/>
+      <c r="D2" s="90"/>
+      <c r="E2" s="90"/>
     </row>
     <row r="3" spans="2:33">
-      <c r="B3" s="88"/>
-      <c r="C3" s="88"/>
-      <c r="D3" s="88"/>
-      <c r="E3" s="88"/>
+      <c r="B3" s="90"/>
+      <c r="C3" s="90"/>
+      <c r="D3" s="90"/>
+      <c r="E3" s="90"/>
       <c r="M3" s="31"/>
     </row>
     <row r="4" spans="2:33">
-      <c r="B4" s="88"/>
-      <c r="C4" s="88"/>
-      <c r="D4" s="88"/>
-      <c r="E4" s="88"/>
+      <c r="B4" s="90"/>
+      <c r="C4" s="90"/>
+      <c r="D4" s="90"/>
+      <c r="E4" s="90"/>
     </row>
     <row r="5" spans="2:33">
-      <c r="B5" s="88"/>
-      <c r="C5" s="88"/>
-      <c r="D5" s="88"/>
-      <c r="E5" s="88"/>
+      <c r="B5" s="90"/>
+      <c r="C5" s="90"/>
+      <c r="D5" s="90"/>
+      <c r="E5" s="90"/>
     </row>
     <row r="6" spans="2:33">
-      <c r="B6" s="88"/>
-      <c r="C6" s="88"/>
-      <c r="D6" s="88"/>
-      <c r="E6" s="88"/>
-      <c r="O6" s="88" t="s">
+      <c r="B6" s="90"/>
+      <c r="C6" s="90"/>
+      <c r="D6" s="90"/>
+      <c r="E6" s="90"/>
+      <c r="O6" s="90" t="s">
         <v>33</v>
       </c>
-      <c r="P6" s="88"/>
-      <c r="Q6" s="88"/>
-      <c r="R6" s="88"/>
+      <c r="P6" s="90"/>
+      <c r="Q6" s="90"/>
+      <c r="R6" s="90"/>
     </row>
     <row r="7" spans="2:33">
-      <c r="O7" s="88"/>
-      <c r="P7" s="88"/>
-      <c r="Q7" s="88"/>
-      <c r="R7" s="88"/>
+      <c r="O7" s="90"/>
+      <c r="P7" s="90"/>
+      <c r="Q7" s="90"/>
+      <c r="R7" s="90"/>
     </row>
     <row r="8" spans="2:33">
-      <c r="C8" s="89" t="s">
+      <c r="C8" s="91" t="s">
         <v>8</v>
       </c>
-      <c r="D8" s="89"/>
-      <c r="E8" s="89"/>
-      <c r="F8" s="89"/>
-      <c r="G8" s="89"/>
-      <c r="O8" s="88"/>
-      <c r="P8" s="88"/>
-      <c r="Q8" s="88"/>
-      <c r="R8" s="88"/>
+      <c r="D8" s="91"/>
+      <c r="E8" s="91"/>
+      <c r="F8" s="91"/>
+      <c r="G8" s="91"/>
+      <c r="O8" s="90"/>
+      <c r="P8" s="90"/>
+      <c r="Q8" s="90"/>
+      <c r="R8" s="90"/>
     </row>
     <row r="9" spans="2:33">
       <c r="B9" s="33" t="s">
@@ -6471,10 +7850,10 @@
         <v>6</v>
       </c>
       <c r="L9" s="31"/>
-      <c r="O9" s="88"/>
-      <c r="P9" s="88"/>
-      <c r="Q9" s="88"/>
-      <c r="R9" s="88"/>
+      <c r="O9" s="90"/>
+      <c r="P9" s="90"/>
+      <c r="Q9" s="90"/>
+      <c r="R9" s="90"/>
     </row>
     <row r="10" spans="2:33">
       <c r="B10" s="31" t="s">
@@ -6504,10 +7883,10 @@
       <c r="J10" s="2">
         <v>0</v>
       </c>
-      <c r="O10" s="88"/>
-      <c r="P10" s="88"/>
-      <c r="Q10" s="88"/>
-      <c r="R10" s="88"/>
+      <c r="O10" s="90"/>
+      <c r="P10" s="90"/>
+      <c r="Q10" s="90"/>
+      <c r="R10" s="90"/>
     </row>
     <row r="11" spans="2:33">
       <c r="B11" s="31" t="s">
@@ -7376,12 +8755,12 @@
       </c>
     </row>
     <row r="25" spans="2:33">
-      <c r="B25" s="88" t="s">
+      <c r="B25" s="90" t="s">
         <v>69</v>
       </c>
-      <c r="C25" s="88"/>
-      <c r="D25" s="88"/>
-      <c r="E25" s="88"/>
+      <c r="C25" s="90"/>
+      <c r="D25" s="90"/>
+      <c r="E25" s="90"/>
       <c r="O25" s="2" t="s">
         <v>23</v>
       </c>
@@ -7450,10 +8829,10 @@
       </c>
     </row>
     <row r="26" spans="2:33" ht="16" customHeight="1">
-      <c r="B26" s="88"/>
-      <c r="C26" s="88"/>
-      <c r="D26" s="88"/>
-      <c r="E26" s="88"/>
+      <c r="B26" s="90"/>
+      <c r="C26" s="90"/>
+      <c r="D26" s="90"/>
+      <c r="E26" s="90"/>
       <c r="N26" s="34" t="s">
         <v>23</v>
       </c>
@@ -7524,10 +8903,10 @@
       </c>
     </row>
     <row r="27" spans="2:33" ht="16" customHeight="1">
-      <c r="B27" s="88"/>
-      <c r="C27" s="88"/>
-      <c r="D27" s="88"/>
-      <c r="E27" s="88"/>
+      <c r="B27" s="90"/>
+      <c r="C27" s="90"/>
+      <c r="D27" s="90"/>
+      <c r="E27" s="90"/>
       <c r="N27" s="34" t="s">
         <v>24</v>
       </c>
@@ -7598,10 +8977,10 @@
       </c>
     </row>
     <row r="28" spans="2:33" ht="16" customHeight="1">
-      <c r="B28" s="88"/>
-      <c r="C28" s="88"/>
-      <c r="D28" s="88"/>
-      <c r="E28" s="88"/>
+      <c r="B28" s="90"/>
+      <c r="C28" s="90"/>
+      <c r="D28" s="90"/>
+      <c r="E28" s="90"/>
       <c r="N28" s="34" t="s">
         <v>25</v>
       </c>
@@ -7672,10 +9051,10 @@
       </c>
     </row>
     <row r="29" spans="2:33" ht="16" customHeight="1">
-      <c r="B29" s="88"/>
-      <c r="C29" s="88"/>
-      <c r="D29" s="88"/>
-      <c r="E29" s="88"/>
+      <c r="B29" s="90"/>
+      <c r="C29" s="90"/>
+      <c r="D29" s="90"/>
+      <c r="E29" s="90"/>
       <c r="N29" s="34" t="s">
         <v>27</v>
       </c>
@@ -9159,7 +10538,7 @@
       <c r="M18" s="6"/>
     </row>
     <row r="19" spans="1:15" ht="39" customHeight="1">
-      <c r="A19" s="90">
+      <c r="A19" s="92">
         <v>2</v>
       </c>
       <c r="B19" s="6" t="s">
@@ -9203,7 +10582,7 @@
       </c>
     </row>
     <row r="20" spans="1:15" ht="39" customHeight="1">
-      <c r="A20" s="90"/>
+      <c r="A20" s="92"/>
       <c r="B20" s="6" t="s">
         <v>98</v>
       </c>
@@ -9422,12 +10801,12 @@
       <c r="F29" s="6"/>
       <c r="G29" s="6"/>
       <c r="H29" s="6"/>
-      <c r="I29" s="91" t="s">
+      <c r="I29" s="93" t="s">
         <v>418</v>
       </c>
-      <c r="J29" s="91"/>
-      <c r="K29" s="91"/>
-      <c r="L29" s="91"/>
+      <c r="J29" s="93"/>
+      <c r="K29" s="93"/>
+      <c r="L29" s="93"/>
     </row>
     <row r="30" spans="1:15" ht="39" customHeight="1">
       <c r="A30" s="6"/>
@@ -9792,12 +11171,12 @@
       <c r="F47" s="6"/>
       <c r="G47" s="6"/>
       <c r="H47" s="6"/>
-      <c r="I47" s="91" t="s">
+      <c r="I47" s="93" t="s">
         <v>419</v>
       </c>
-      <c r="J47" s="91"/>
-      <c r="K47" s="91"/>
-      <c r="L47" s="91"/>
+      <c r="J47" s="93"/>
+      <c r="K47" s="93"/>
+      <c r="L47" s="93"/>
       <c r="M47" s="6"/>
       <c r="N47" s="6"/>
     </row>

--- a/doc/notes.xlsx
+++ b/doc/notes.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10726"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10810"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/renzosala/Develop/personal/tokeniko/doc/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FBAF464E-8D0F-5545-B872-50397C7AB13C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F33213D4-EA41-9545-A451-03B58471E31B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="780" windowWidth="36000" windowHeight="22600" activeTab="11" xr2:uid="{ED098269-B10A-E440-BCE3-AF4955707036}"/>
+    <workbookView xWindow="0" yWindow="780" windowWidth="36000" windowHeight="22600" activeTab="12" xr2:uid="{ED098269-B10A-E440-BCE3-AF4955707036}"/>
   </bookViews>
   <sheets>
     <sheet name="General schema" sheetId="1" r:id="rId1"/>
@@ -25,6 +25,7 @@
     <sheet name="Next step" sheetId="11" r:id="rId10"/>
     <sheet name="Inconsistencies" sheetId="12" r:id="rId11"/>
     <sheet name="TKZIP2" sheetId="13" r:id="rId12"/>
+    <sheet name="Sheet1" sheetId="14" r:id="rId13"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -47,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1169" uniqueCount="579">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2179" uniqueCount="997">
   <si>
     <t>essere</t>
   </si>
@@ -1985,12 +1986,1266 @@
   <si>
     <t>I build my contraption with my hammer</t>
   </si>
+  <si>
+    <t>thing</t>
+  </si>
+  <si>
+    <t>Verb</t>
+  </si>
+  <si>
+    <t>is</t>
+  </si>
+  <si>
+    <t>object = object</t>
+  </si>
+  <si>
+    <t>Adj</t>
+  </si>
+  <si>
+    <t>NOT true</t>
+  </si>
+  <si>
+    <t>Noun</t>
+  </si>
+  <si>
+    <t>has property AND is true</t>
+  </si>
+  <si>
+    <t>property</t>
+  </si>
+  <si>
+    <t>object AND is true OR false</t>
+  </si>
+  <si>
+    <t>has</t>
+  </si>
+  <si>
+    <t>object AND property = true</t>
+  </si>
+  <si>
+    <t>Adv</t>
+  </si>
+  <si>
+    <t>now</t>
+  </si>
+  <si>
+    <t>is true</t>
+  </si>
+  <si>
+    <t>Cat</t>
+  </si>
+  <si>
+    <t>Word</t>
+  </si>
+  <si>
+    <t>Definition</t>
+  </si>
+  <si>
+    <t>EX.1</t>
+  </si>
+  <si>
+    <t>thing = thing</t>
+  </si>
+  <si>
+    <t>thing AND state = true</t>
+  </si>
+  <si>
+    <t>is true AND has state</t>
+  </si>
+  <si>
+    <t>state</t>
+  </si>
+  <si>
+    <t>thing AND is true OR false</t>
+  </si>
+  <si>
+    <t>thing = true</t>
+  </si>
+  <si>
+    <t>none</t>
+  </si>
+  <si>
+    <t>NOT all</t>
+  </si>
+  <si>
+    <t>some</t>
+  </si>
+  <si>
+    <t>NOT all AND NOT none</t>
+  </si>
+  <si>
+    <t>state != state</t>
+  </si>
+  <si>
+    <t>change</t>
+  </si>
+  <si>
+    <t>has time</t>
+  </si>
+  <si>
+    <t>time AND is true</t>
+  </si>
+  <si>
+    <t>before</t>
+  </si>
+  <si>
+    <t>time AND NOT now</t>
+  </si>
+  <si>
+    <t>after</t>
+  </si>
+  <si>
+    <t>NOT before AND NOT now</t>
+  </si>
+  <si>
+    <t>space</t>
+  </si>
+  <si>
+    <t>thing != thing</t>
+  </si>
+  <si>
+    <t>here</t>
+  </si>
+  <si>
+    <t>space AND is true</t>
+  </si>
+  <si>
+    <t>thing AND has change</t>
+  </si>
+  <si>
+    <t>action AND before</t>
+  </si>
+  <si>
+    <t>Conj</t>
+  </si>
+  <si>
+    <t>because</t>
+  </si>
+  <si>
+    <t>cause = true</t>
+  </si>
+  <si>
+    <t>if</t>
+  </si>
+  <si>
+    <t>state = true OR state = false</t>
+  </si>
+  <si>
+    <t>mind</t>
+  </si>
+  <si>
+    <t>thing AND has time AND space = false</t>
+  </si>
+  <si>
+    <t>body</t>
+  </si>
+  <si>
+    <t>thing AND has space</t>
+  </si>
+  <si>
+    <t>want</t>
+  </si>
+  <si>
+    <t>mind AND cause action</t>
+  </si>
+  <si>
+    <t>good</t>
+  </si>
+  <si>
+    <t>want = true</t>
+  </si>
+  <si>
+    <t>bad</t>
+  </si>
+  <si>
+    <t>NOT good</t>
+  </si>
+  <si>
+    <t>EX.2</t>
+  </si>
+  <si>
+    <t>Ex.3</t>
+  </si>
+  <si>
+    <t>nothing</t>
+  </si>
+  <si>
+    <t>thing = false</t>
+  </si>
+  <si>
+    <t>equal</t>
+  </si>
+  <si>
+    <t>different</t>
+  </si>
+  <si>
+    <t>there</t>
+  </si>
+  <si>
+    <t>space AND NOT here</t>
+  </si>
+  <si>
+    <t>near</t>
+  </si>
+  <si>
+    <t>space AND here AND some</t>
+  </si>
+  <si>
+    <t>far</t>
+  </si>
+  <si>
+    <t>space AND NOT here AND all</t>
+  </si>
+  <si>
+    <t>begin</t>
+  </si>
+  <si>
+    <t>time AND before = none</t>
+  </si>
+  <si>
+    <t>end</t>
+  </si>
+  <si>
+    <t>time AND after = none</t>
+  </si>
+  <si>
+    <t>forever</t>
+  </si>
+  <si>
+    <t>time AND end = false</t>
+  </si>
+  <si>
+    <t>create</t>
+  </si>
+  <si>
+    <t>cause thing AND before = none</t>
+  </si>
+  <si>
+    <t>destroy</t>
+  </si>
+  <si>
+    <t>cause thing = none</t>
+  </si>
+  <si>
+    <t>move</t>
+  </si>
+  <si>
+    <t>change AND space</t>
+  </si>
+  <si>
+    <t>static</t>
+  </si>
+  <si>
+    <t>NOT move</t>
+  </si>
+  <si>
+    <t>fast</t>
+  </si>
+  <si>
+    <t>move AND NOT time</t>
+  </si>
+  <si>
+    <t>slow</t>
+  </si>
+  <si>
+    <t>move AND time</t>
+  </si>
+  <si>
+    <t>matter</t>
+  </si>
+  <si>
+    <t>thing AND space</t>
+  </si>
+  <si>
+    <t>energy</t>
+  </si>
+  <si>
+    <t>thing AND action AND NOT space</t>
+  </si>
+  <si>
+    <t>light</t>
+  </si>
+  <si>
+    <t>energy AND see</t>
+  </si>
+  <si>
+    <t>dark</t>
+  </si>
+  <si>
+    <t>NOT light</t>
+  </si>
+  <si>
+    <t>hot</t>
+  </si>
+  <si>
+    <t>energy AND feel</t>
+  </si>
+  <si>
+    <t>cold</t>
+  </si>
+  <si>
+    <t>NOT hot</t>
+  </si>
+  <si>
+    <t>water</t>
+  </si>
+  <si>
+    <t>matter AND move</t>
+  </si>
+  <si>
+    <t>earth</t>
+  </si>
+  <si>
+    <t>matter AND static</t>
+  </si>
+  <si>
+    <t>air</t>
+  </si>
+  <si>
+    <t>matter AND NOT see</t>
+  </si>
+  <si>
+    <t>fire</t>
+  </si>
+  <si>
+    <t>matter AND hot AND light</t>
+  </si>
+  <si>
+    <t>big</t>
+  </si>
+  <si>
+    <t>space AND all</t>
+  </si>
+  <si>
+    <t>small</t>
+  </si>
+  <si>
+    <t>space AND some</t>
+  </si>
+  <si>
+    <t>day</t>
+  </si>
+  <si>
+    <t>time AND light</t>
+  </si>
+  <si>
+    <t>night</t>
+  </si>
+  <si>
+    <t>time AND dark</t>
+  </si>
+  <si>
+    <t>sun</t>
+  </si>
+  <si>
+    <t>thing AND cause light AND day</t>
+  </si>
+  <si>
+    <t>moon</t>
+  </si>
+  <si>
+    <t>thing AND cause light AND night</t>
+  </si>
+  <si>
+    <t>star</t>
+  </si>
+  <si>
+    <t>thing AND cause light AND far</t>
+  </si>
+  <si>
+    <t>color</t>
+  </si>
+  <si>
+    <t>state AND light AND see</t>
+  </si>
+  <si>
+    <t>form</t>
+  </si>
+  <si>
+    <t>state AND space AND see</t>
+  </si>
+  <si>
+    <t>life</t>
+  </si>
+  <si>
+    <t>thing AND has change AND has body AND has mind</t>
+  </si>
+  <si>
+    <t>death</t>
+  </si>
+  <si>
+    <t>life AND change = false</t>
+  </si>
+  <si>
+    <t>plant</t>
+  </si>
+  <si>
+    <t>life AND static AND earth</t>
+  </si>
+  <si>
+    <t>animal</t>
+  </si>
+  <si>
+    <t>life AND move</t>
+  </si>
+  <si>
+    <t>human</t>
+  </si>
+  <si>
+    <t>animal AND mind AND word</t>
+  </si>
+  <si>
+    <t>eat</t>
+  </si>
+  <si>
+    <t>animal AND take matter AND cause life</t>
+  </si>
+  <si>
+    <t>sleep</t>
+  </si>
+  <si>
+    <t>life AND static AND mind = false</t>
+  </si>
+  <si>
+    <t>wake</t>
+  </si>
+  <si>
+    <t>life AND mind = true AND after sleep</t>
+  </si>
+  <si>
+    <t>grow</t>
+  </si>
+  <si>
+    <t>change AND big</t>
+  </si>
+  <si>
+    <t>shrink</t>
+  </si>
+  <si>
+    <t>change AND small</t>
+  </si>
+  <si>
+    <t>action AND mind AND NOT space</t>
+  </si>
+  <si>
+    <t>know</t>
+  </si>
+  <si>
+    <t>mind AND state = true</t>
+  </si>
+  <si>
+    <t>mind AND before</t>
+  </si>
+  <si>
+    <t>learn</t>
+  </si>
+  <si>
+    <t>change AND know</t>
+  </si>
+  <si>
+    <t>sense</t>
+  </si>
+  <si>
+    <t>body AND cause mind state</t>
+  </si>
+  <si>
+    <t>sense AND space</t>
+  </si>
+  <si>
+    <t>hear</t>
+  </si>
+  <si>
+    <t>sense AND time</t>
+  </si>
+  <si>
+    <t>feel</t>
+  </si>
+  <si>
+    <t>sense AND body</t>
+  </si>
+  <si>
+    <t>joy</t>
+  </si>
+  <si>
+    <t>mind AND state = good AND now</t>
+  </si>
+  <si>
+    <t>pain</t>
+  </si>
+  <si>
+    <t>body AND state = bad</t>
+  </si>
+  <si>
+    <t>fear</t>
+  </si>
+  <si>
+    <t>mind AND state = bad AND after</t>
+  </si>
+  <si>
+    <t>love</t>
+  </si>
+  <si>
+    <t>want AND good AND person</t>
+  </si>
+  <si>
+    <t>hate</t>
+  </si>
+  <si>
+    <t>want AND bad AND person</t>
+  </si>
+  <si>
+    <t>person</t>
+  </si>
+  <si>
+    <t>life AND mind = true</t>
+  </si>
+  <si>
+    <t>group</t>
+  </si>
+  <si>
+    <t>all person</t>
+  </si>
+  <si>
+    <t>thing AND cause mind state</t>
+  </si>
+  <si>
+    <t>speak</t>
+  </si>
+  <si>
+    <t>action AND cause word</t>
+  </si>
+  <si>
+    <t>friend</t>
+  </si>
+  <si>
+    <t>person AND love</t>
+  </si>
+  <si>
+    <t>enemy</t>
+  </si>
+  <si>
+    <t>person AND hate</t>
+  </si>
+  <si>
+    <t>cause thing AND person</t>
+  </si>
+  <si>
+    <t>take</t>
+  </si>
+  <si>
+    <t>cause thing AND NOT give</t>
+  </si>
+  <si>
+    <t>power</t>
+  </si>
+  <si>
+    <t>cause action = true</t>
+  </si>
+  <si>
+    <t>rule</t>
+  </si>
+  <si>
+    <t>power AND because</t>
+  </si>
+  <si>
+    <t>point</t>
+  </si>
+  <si>
+    <t>space AND NOT big</t>
+  </si>
+  <si>
+    <t>line</t>
+  </si>
+  <si>
+    <t>space AND move</t>
+  </si>
+  <si>
+    <t>circle</t>
+  </si>
+  <si>
+    <t>line AND move AND static</t>
+  </si>
+  <si>
+    <t>number</t>
+  </si>
+  <si>
+    <t>state AND mind AND thing</t>
+  </si>
+  <si>
+    <t>number AND thing</t>
+  </si>
+  <si>
+    <t>two</t>
+  </si>
+  <si>
+    <t>one AND one</t>
+  </si>
+  <si>
+    <t>all number AND NOT one AND NOT none</t>
+  </si>
+  <si>
+    <t>add</t>
+  </si>
+  <si>
+    <t>cause action AND many</t>
+  </si>
+  <si>
+    <t>sub</t>
+  </si>
+  <si>
+    <t>cause action AND none</t>
+  </si>
+  <si>
+    <t>Ex. 4</t>
+  </si>
+  <si>
+    <t>thing = none</t>
+  </si>
+  <si>
+    <t>and</t>
+  </si>
+  <si>
+    <t>true = true</t>
+  </si>
+  <si>
+    <t>or</t>
+  </si>
+  <si>
+    <t>true != false</t>
+  </si>
+  <si>
+    <t>always</t>
+  </si>
+  <si>
+    <t>time AND all</t>
+  </si>
+  <si>
+    <t>never</t>
+  </si>
+  <si>
+    <t>time AND none</t>
+  </si>
+  <si>
+    <t>heavy</t>
+  </si>
+  <si>
+    <t>matter AND much</t>
+  </si>
+  <si>
+    <t>lightweight</t>
+  </si>
+  <si>
+    <t>matter AND NOT heavy</t>
+  </si>
+  <si>
+    <t>hard</t>
+  </si>
+  <si>
+    <t>matter AND NOT change form</t>
+  </si>
+  <si>
+    <t>soft</t>
+  </si>
+  <si>
+    <t>NOT hard</t>
+  </si>
+  <si>
+    <t>matter AND move AND soft</t>
+  </si>
+  <si>
+    <t>matter AND static AND hard</t>
+  </si>
+  <si>
+    <t>matter AND NOT see AND lightweight</t>
+  </si>
+  <si>
+    <t>matter AND hot AND light AND change</t>
+  </si>
+  <si>
+    <t>sky</t>
+  </si>
+  <si>
+    <t>space AND up AND air</t>
+  </si>
+  <si>
+    <t>world</t>
+  </si>
+  <si>
+    <t>all space AND all matter</t>
+  </si>
+  <si>
+    <t>mountain</t>
+  </si>
+  <si>
+    <t>earth AND big AND up</t>
+  </si>
+  <si>
+    <t>valley</t>
+  </si>
+  <si>
+    <t>earth AND down AND near mountain</t>
+  </si>
+  <si>
+    <t>river</t>
+  </si>
+  <si>
+    <t>water AND move AND line</t>
+  </si>
+  <si>
+    <t>ocean</t>
+  </si>
+  <si>
+    <t>water AND big AND static</t>
+  </si>
+  <si>
+    <t>island</t>
+  </si>
+  <si>
+    <t>earth AND near ocean AND all</t>
+  </si>
+  <si>
+    <t>forest</t>
+  </si>
+  <si>
+    <t>earth AND many tree</t>
+  </si>
+  <si>
+    <t>desert</t>
+  </si>
+  <si>
+    <t>earth AND hot AND water = none</t>
+  </si>
+  <si>
+    <t>thing AND has change AND has body</t>
+  </si>
+  <si>
+    <t>blood</t>
+  </si>
+  <si>
+    <t>water AND body AND red</t>
+  </si>
+  <si>
+    <t>bone</t>
+  </si>
+  <si>
+    <t>hard AND body</t>
+  </si>
+  <si>
+    <t>skin</t>
+  </si>
+  <si>
+    <t>soft AND body AND space</t>
+  </si>
+  <si>
+    <t>wood</t>
+  </si>
+  <si>
+    <t>hard AND plant</t>
+  </si>
+  <si>
+    <t>leaf</t>
+  </si>
+  <si>
+    <t>soft AND plant AND green</t>
+  </si>
+  <si>
+    <t>flower</t>
+  </si>
+  <si>
+    <t>soft AND plant AND color</t>
+  </si>
+  <si>
+    <t>seed</t>
+  </si>
+  <si>
+    <t>plant AND before begin</t>
+  </si>
+  <si>
+    <t>tree</t>
+  </si>
+  <si>
+    <t>plant AND big AND wood</t>
+  </si>
+  <si>
+    <t>grass</t>
+  </si>
+  <si>
+    <t>plant AND small AND many</t>
+  </si>
+  <si>
+    <t>red</t>
+  </si>
+  <si>
+    <t>color AND hot</t>
+  </si>
+  <si>
+    <t>blue</t>
+  </si>
+  <si>
+    <t>color AND water</t>
+  </si>
+  <si>
+    <t>green</t>
+  </si>
+  <si>
+    <t>color AND plant</t>
+  </si>
+  <si>
+    <t>yellow</t>
+  </si>
+  <si>
+    <t>color AND sun</t>
+  </si>
+  <si>
+    <t>sense AND light</t>
+  </si>
+  <si>
+    <t>sense AND sound</t>
+  </si>
+  <si>
+    <t>sense AND body AND matter</t>
+  </si>
+  <si>
+    <t>smell</t>
+  </si>
+  <si>
+    <t>sense AND air</t>
+  </si>
+  <si>
+    <t>taste</t>
+  </si>
+  <si>
+    <t>sense AND eat</t>
+  </si>
+  <si>
+    <t>sound</t>
+  </si>
+  <si>
+    <t>energy AND hear</t>
+  </si>
+  <si>
+    <t>loud</t>
+  </si>
+  <si>
+    <t>sound AND big</t>
+  </si>
+  <si>
+    <t>quiet</t>
+  </si>
+  <si>
+    <t>sound AND small</t>
+  </si>
+  <si>
+    <t>drink</t>
+  </si>
+  <si>
+    <t>eat AND water</t>
+  </si>
+  <si>
+    <t>walk</t>
+  </si>
+  <si>
+    <t>move AND animal AND slow</t>
+  </si>
+  <si>
+    <t>run</t>
+  </si>
+  <si>
+    <t>walk AND fast</t>
+  </si>
+  <si>
+    <t>fly</t>
+  </si>
+  <si>
+    <t>move AND air</t>
+  </si>
+  <si>
+    <t>swim</t>
+  </si>
+  <si>
+    <t>move AND water</t>
+  </si>
+  <si>
+    <t>create AND form AND matter</t>
+  </si>
+  <si>
+    <t>break</t>
+  </si>
+  <si>
+    <t>destroy AND form</t>
+  </si>
+  <si>
+    <t>cause thing AND person AND out</t>
+  </si>
+  <si>
+    <t>cause thing AND in AND NOT give</t>
+  </si>
+  <si>
+    <t>push</t>
+  </si>
+  <si>
+    <t>move AND out AND force</t>
+  </si>
+  <si>
+    <t>pull</t>
+  </si>
+  <si>
+    <t>move AND in AND force</t>
+  </si>
+  <si>
+    <t>hold</t>
+  </si>
+  <si>
+    <t>static AND matter AND body</t>
+  </si>
+  <si>
+    <t>drop</t>
+  </si>
+  <si>
+    <t>move AND down AND NOT hold</t>
+  </si>
+  <si>
+    <t>cut</t>
+  </si>
+  <si>
+    <t>break AND line AND tool</t>
+  </si>
+  <si>
+    <t>forget</t>
+  </si>
+  <si>
+    <t>change AND NOT know AND memory</t>
+  </si>
+  <si>
+    <t>need</t>
+  </si>
+  <si>
+    <t>want AND life</t>
+  </si>
+  <si>
+    <t>idea</t>
+  </si>
+  <si>
+    <t>think AND create</t>
+  </si>
+  <si>
+    <t>idea AND true</t>
+  </si>
+  <si>
+    <t>lie</t>
+  </si>
+  <si>
+    <t>idea AND false</t>
+  </si>
+  <si>
+    <t>dream</t>
+  </si>
+  <si>
+    <t>think AND sleep</t>
+  </si>
+  <si>
+    <t>happy</t>
+  </si>
+  <si>
+    <t>joy AND all</t>
+  </si>
+  <si>
+    <t>sad</t>
+  </si>
+  <si>
+    <t>NOT happy AND pain</t>
+  </si>
+  <si>
+    <t>angry</t>
+  </si>
+  <si>
+    <t>hate AND hot AND fast</t>
+  </si>
+  <si>
+    <t>family</t>
+  </si>
+  <si>
+    <t>group AND blood AND love</t>
+  </si>
+  <si>
+    <t>leader</t>
+  </si>
+  <si>
+    <t>person AND rule AND group</t>
+  </si>
+  <si>
+    <t>follower</t>
+  </si>
+  <si>
+    <t>person AND NOT leader AND group</t>
+  </si>
+  <si>
+    <t>city</t>
+  </si>
+  <si>
+    <t>earth AND many person AND many build</t>
+  </si>
+  <si>
+    <t>build AND person AND sleep</t>
+  </si>
+  <si>
+    <t>room</t>
+  </si>
+  <si>
+    <t>space AND in house</t>
+  </si>
+  <si>
+    <t>door</t>
+  </si>
+  <si>
+    <t>wood AND move AND room</t>
+  </si>
+  <si>
+    <t>wall</t>
+  </si>
+  <si>
+    <t>hard AND static AND room</t>
+  </si>
+  <si>
+    <t>road</t>
+  </si>
+  <si>
+    <t>earth AND line AND walk</t>
+  </si>
+  <si>
+    <t>action AND cause word AND sound</t>
+  </si>
+  <si>
+    <t>action AND cause word AND see</t>
+  </si>
+  <si>
+    <t>read</t>
+  </si>
+  <si>
+    <t>see AND word AND know</t>
+  </si>
+  <si>
+    <t>many word AND paper</t>
+  </si>
+  <si>
+    <t>paper</t>
+  </si>
+  <si>
+    <t>matter AND flat AND tree</t>
+  </si>
+  <si>
+    <t>word AND person = true</t>
+  </si>
+  <si>
+    <t>art</t>
+  </si>
+  <si>
+    <t>create AND color OR form AND joy</t>
+  </si>
+  <si>
+    <t>music</t>
+  </si>
+  <si>
+    <t>create AND sound AND joy</t>
+  </si>
+  <si>
+    <t>song</t>
+  </si>
+  <si>
+    <t>music AND word AND speak</t>
+  </si>
+  <si>
+    <t>game</t>
+  </si>
+  <si>
+    <t>action AND rule AND joy</t>
+  </si>
+  <si>
+    <t>play</t>
+  </si>
+  <si>
+    <t>action AND game</t>
+  </si>
+  <si>
+    <t>action AND need AND NOT play</t>
+  </si>
+  <si>
+    <t>money</t>
+  </si>
+  <si>
+    <t>thing AND give AND take AND work</t>
+  </si>
+  <si>
+    <t>trade</t>
+  </si>
+  <si>
+    <t>give AND take AND money</t>
+  </si>
+  <si>
+    <t>rich</t>
+  </si>
+  <si>
+    <t>person AND many money</t>
+  </si>
+  <si>
+    <t>poor</t>
+  </si>
+  <si>
+    <t>person AND money = none</t>
+  </si>
+  <si>
+    <t>cause action = true AND all</t>
+  </si>
+  <si>
+    <t>force</t>
+  </si>
+  <si>
+    <t>energy AND move AND hard</t>
+  </si>
+  <si>
+    <t>power AND word AND because</t>
+  </si>
+  <si>
+    <t>law</t>
+  </si>
+  <si>
+    <t>rule AND city AND all</t>
+  </si>
+  <si>
+    <t>crime</t>
+  </si>
+  <si>
+    <t>action AND NOT law AND bad</t>
+  </si>
+  <si>
+    <t>justice</t>
+  </si>
+  <si>
+    <t>good AND law AND true</t>
+  </si>
+  <si>
+    <t>matter AND hold AND work</t>
+  </si>
+  <si>
+    <t>weapon</t>
+  </si>
+  <si>
+    <t>tool AND cause pain OR death</t>
+  </si>
+  <si>
+    <t>sword</t>
+  </si>
+  <si>
+    <t>weapon AND cut AND metal</t>
+  </si>
+  <si>
+    <t>shield</t>
+  </si>
+  <si>
+    <t>tool AND NOT cut AND hold</t>
+  </si>
+  <si>
+    <t>wheel</t>
+  </si>
+  <si>
+    <t>tool AND circle AND move</t>
+  </si>
+  <si>
+    <t>vehicle</t>
+  </si>
+  <si>
+    <t>tool AND wheel AND move AND person</t>
+  </si>
+  <si>
+    <t>ship</t>
+  </si>
+  <si>
+    <t>vehicle AND water AND big</t>
+  </si>
+  <si>
+    <t>metal</t>
+  </si>
+  <si>
+    <t>matter AND hard AND cold AND earth</t>
+  </si>
+  <si>
+    <t>math</t>
+  </si>
+  <si>
+    <t>know AND number AND rule</t>
+  </si>
+  <si>
+    <t>shape</t>
+  </si>
+  <si>
+    <t>form AND line AND space</t>
+  </si>
+  <si>
+    <t>space AND NOT big AND shape</t>
+  </si>
+  <si>
+    <t>space AND move AND point</t>
+  </si>
+  <si>
+    <t>square</t>
+  </si>
+  <si>
+    <t>shape AND line AND equal AND four</t>
+  </si>
+  <si>
+    <t>triangle</t>
+  </si>
+  <si>
+    <t>shape AND line AND three</t>
+  </si>
+  <si>
+    <t>three</t>
+  </si>
+  <si>
+    <t>two AND one</t>
+  </si>
+  <si>
+    <t>four</t>
+  </si>
+  <si>
+    <t>two AND two</t>
+  </si>
+  <si>
+    <t>much</t>
+  </si>
+  <si>
+    <t>matter AND big</t>
+  </si>
+  <si>
+    <t>up</t>
+  </si>
+  <si>
+    <t>space AND sky</t>
+  </si>
+  <si>
+    <t>down</t>
+  </si>
+  <si>
+    <t>space AND earth</t>
+  </si>
+  <si>
+    <t>in</t>
+  </si>
+  <si>
+    <t>space AND center</t>
+  </si>
+  <si>
+    <t>out</t>
+  </si>
+  <si>
+    <t>space AND NOT in</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="24">
+  <fonts count="25">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -2134,6 +3389,12 @@
       <sz val="12"/>
       <color theme="0"/>
       <name val="Aptos Narrow"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -2404,7 +3665,7 @@
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="112">
+  <cellXfs count="113">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
@@ -2584,29 +3845,60 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="22" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2626,7 +3918,16 @@
     <xf numFmtId="0" fontId="15" fillId="3" borderId="9" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="6" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2641,6 +3942,15 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="6" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2653,57 +3963,11 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="5">
@@ -3373,12 +4637,12 @@
       <c r="D30" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="E30" s="72" t="s">
+      <c r="E30" s="89" t="s">
         <v>127</v>
       </c>
-      <c r="F30" s="72"/>
-      <c r="G30" s="72"/>
-      <c r="H30" s="72"/>
+      <c r="F30" s="89"/>
+      <c r="G30" s="89"/>
+      <c r="H30" s="89"/>
       <c r="I30" s="4" t="s">
         <v>340</v>
       </c>
@@ -3441,12 +4705,12 @@
       <c r="D36" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="E36" s="72" t="s">
+      <c r="E36" s="89" t="s">
         <v>127</v>
       </c>
-      <c r="F36" s="72"/>
-      <c r="G36" s="72"/>
-      <c r="H36" s="72"/>
+      <c r="F36" s="89"/>
+      <c r="G36" s="89"/>
+      <c r="H36" s="89"/>
     </row>
     <row r="37" spans="2:10">
       <c r="B37" s="4"/>
@@ -3994,22 +5258,22 @@
       </c>
     </row>
     <row r="24" spans="3:8" ht="43" customHeight="1">
-      <c r="C24" s="71" t="s">
+      <c r="C24" s="111" t="s">
         <v>511</v>
       </c>
-      <c r="D24" s="71"/>
-      <c r="E24" s="71"/>
-      <c r="F24" s="71"/>
-      <c r="G24" s="71"/>
+      <c r="D24" s="111"/>
+      <c r="E24" s="111"/>
+      <c r="F24" s="111"/>
+      <c r="G24" s="111"/>
     </row>
     <row r="25" spans="3:8" ht="80" customHeight="1">
-      <c r="C25" s="71" t="s">
+      <c r="C25" s="111" t="s">
         <v>512</v>
       </c>
-      <c r="D25" s="71"/>
-      <c r="E25" s="71"/>
-      <c r="F25" s="71"/>
-      <c r="G25" s="71"/>
+      <c r="D25" s="111"/>
+      <c r="E25" s="111"/>
+      <c r="F25" s="111"/>
+      <c r="G25" s="111"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -4039,125 +5303,125 @@
   </cols>
   <sheetData>
     <row r="3" spans="1:22">
-      <c r="A3" s="94" t="s">
+      <c r="A3" s="71" t="s">
         <v>520</v>
       </c>
-      <c r="B3" s="103" t="s">
+      <c r="B3" s="76" t="s">
         <v>220</v>
       </c>
-      <c r="C3" s="95" t="s">
+      <c r="C3" s="81" t="s">
         <v>519</v>
       </c>
-      <c r="D3" s="95"/>
-      <c r="E3" s="96" t="s">
+      <c r="D3" s="81"/>
+      <c r="E3" s="82" t="s">
         <v>191</v>
       </c>
-      <c r="F3" s="96"/>
-      <c r="G3" s="96"/>
-      <c r="H3" s="96"/>
-      <c r="I3" s="96"/>
-      <c r="J3" s="96"/>
-      <c r="K3" s="96"/>
-      <c r="L3" s="99"/>
-      <c r="M3" s="99"/>
-      <c r="N3" s="97"/>
-      <c r="O3" s="97"/>
-      <c r="P3" s="97"/>
-      <c r="Q3" s="97"/>
-      <c r="R3" s="97"/>
-      <c r="S3" s="97"/>
-      <c r="T3" s="97"/>
-      <c r="U3" s="97"/>
-      <c r="V3" s="97"/>
+      <c r="F3" s="82"/>
+      <c r="G3" s="82"/>
+      <c r="H3" s="82"/>
+      <c r="I3" s="82"/>
+      <c r="J3" s="82"/>
+      <c r="K3" s="82"/>
+      <c r="L3" s="72"/>
+      <c r="M3" s="72"/>
+      <c r="N3" s="73"/>
+      <c r="O3" s="73"/>
+      <c r="P3" s="73"/>
+      <c r="Q3" s="73"/>
+      <c r="R3" s="73"/>
+      <c r="S3" s="73"/>
+      <c r="T3" s="73"/>
+      <c r="U3" s="73"/>
+      <c r="V3" s="73"/>
     </row>
     <row r="4" spans="1:22" s="67" customFormat="1">
-      <c r="C4" s="98" t="s">
+      <c r="C4" s="74" t="s">
         <v>140</v>
       </c>
-      <c r="D4" s="98" t="s">
+      <c r="D4" s="74" t="s">
         <v>521</v>
       </c>
-      <c r="E4" s="98" t="s">
+      <c r="E4" s="74" t="s">
         <v>539</v>
       </c>
-      <c r="F4" s="104" t="s">
+      <c r="F4" s="84" t="s">
         <v>140</v>
       </c>
-      <c r="G4" s="104"/>
-      <c r="H4" s="104"/>
-      <c r="I4" s="106" t="s">
+      <c r="G4" s="84"/>
+      <c r="H4" s="84"/>
+      <c r="I4" s="85" t="s">
         <v>521</v>
       </c>
-      <c r="J4" s="106"/>
-      <c r="K4" s="108" t="s">
+      <c r="J4" s="85"/>
+      <c r="K4" s="88" t="s">
         <v>529</v>
       </c>
-      <c r="L4" s="108"/>
-      <c r="M4" s="108"/>
-      <c r="N4" s="110" t="s">
+      <c r="L4" s="88"/>
+      <c r="M4" s="88"/>
+      <c r="N4" s="83" t="s">
         <v>530</v>
       </c>
-      <c r="O4" s="110"/>
-      <c r="P4" s="110"/>
-      <c r="Q4" s="110"/>
-      <c r="R4" s="110"/>
-      <c r="S4" s="110"/>
-      <c r="T4" s="110"/>
-      <c r="U4" s="110"/>
-      <c r="V4" s="110"/>
+      <c r="O4" s="83"/>
+      <c r="P4" s="83"/>
+      <c r="Q4" s="83"/>
+      <c r="R4" s="83"/>
+      <c r="S4" s="83"/>
+      <c r="T4" s="83"/>
+      <c r="U4" s="83"/>
+      <c r="V4" s="83"/>
     </row>
     <row r="5" spans="1:22" s="67" customFormat="1">
-      <c r="C5" s="98"/>
-      <c r="D5" s="98"/>
-      <c r="F5" s="105" t="s">
+      <c r="C5" s="74"/>
+      <c r="D5" s="74"/>
+      <c r="F5" s="77" t="s">
         <v>531</v>
       </c>
-      <c r="G5" s="105" t="s">
+      <c r="G5" s="77" t="s">
         <v>555</v>
       </c>
-      <c r="H5" s="105" t="s">
+      <c r="H5" s="77" t="s">
         <v>140</v>
       </c>
-      <c r="I5" s="107" t="s">
+      <c r="I5" s="78" t="s">
         <v>521</v>
       </c>
-      <c r="J5" s="107" t="s">
+      <c r="J5" s="78" t="s">
         <v>537</v>
       </c>
-      <c r="K5" s="109" t="s">
+      <c r="K5" s="79" t="s">
         <v>531</v>
       </c>
-      <c r="L5" s="109" t="s">
+      <c r="L5" s="79" t="s">
         <v>555</v>
       </c>
-      <c r="M5" s="109" t="s">
+      <c r="M5" s="79" t="s">
         <v>529</v>
       </c>
-      <c r="N5" s="111" t="s">
+      <c r="N5" s="80" t="s">
         <v>528</v>
       </c>
-      <c r="O5" s="111" t="s">
+      <c r="O5" s="80" t="s">
         <v>532</v>
       </c>
-      <c r="P5" s="111" t="s">
+      <c r="P5" s="80" t="s">
         <v>547</v>
       </c>
-      <c r="Q5" s="111" t="s">
+      <c r="Q5" s="80" t="s">
         <v>369</v>
       </c>
-      <c r="R5" s="111" t="s">
+      <c r="R5" s="80" t="s">
         <v>556</v>
       </c>
-      <c r="S5" s="111" t="s">
+      <c r="S5" s="80" t="s">
         <v>557</v>
       </c>
-      <c r="T5" s="111" t="s">
+      <c r="T5" s="80" t="s">
         <v>559</v>
       </c>
-      <c r="U5" s="111" t="s">
+      <c r="U5" s="80" t="s">
         <v>558</v>
       </c>
-      <c r="V5" s="111" t="s">
+      <c r="V5" s="80" t="s">
         <v>190</v>
       </c>
     </row>
@@ -4446,7 +5710,7 @@
       </c>
     </row>
     <row r="11" spans="1:22">
-      <c r="A11" s="100" t="s">
+      <c r="A11" s="86" t="s">
         <v>538</v>
       </c>
       <c r="B11" t="s">
@@ -4458,7 +5722,7 @@
       <c r="D11" t="s">
         <v>518</v>
       </c>
-      <c r="E11" s="101" t="s">
+      <c r="E11" s="87" t="s">
         <v>545</v>
       </c>
       <c r="F11" t="s">
@@ -4514,8 +5778,8 @@
       </c>
     </row>
     <row r="12" spans="1:22">
-      <c r="A12" s="100"/>
-      <c r="B12" s="102" t="s">
+      <c r="A12" s="86"/>
+      <c r="B12" s="75" t="s">
         <v>218</v>
       </c>
       <c r="C12" t="s">
@@ -4524,7 +5788,7 @@
       <c r="D12" t="s">
         <v>518</v>
       </c>
-      <c r="E12" s="101"/>
+      <c r="E12" s="87"/>
       <c r="F12" t="s">
         <v>518</v>
       </c>
@@ -5055,15 +6319,3769 @@
     </row>
   </sheetData>
   <mergeCells count="8">
+    <mergeCell ref="A11:A12"/>
+    <mergeCell ref="E11:E12"/>
+    <mergeCell ref="K4:M4"/>
     <mergeCell ref="C3:D3"/>
     <mergeCell ref="E3:K3"/>
     <mergeCell ref="N4:V4"/>
     <mergeCell ref="F4:H4"/>
     <mergeCell ref="I4:J4"/>
-    <mergeCell ref="A11:A12"/>
-    <mergeCell ref="E11:E12"/>
-    <mergeCell ref="K4:M4"/>
   </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E1C89CA7-ADD8-6749-BD11-855A0279261B}">
+  <dimension ref="B2:D350"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
+  <cols>
+    <col min="2" max="2" width="9.1640625" style="68" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8" style="68" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="61.6640625" style="68" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:4">
+      <c r="B2" s="68" t="s">
+        <v>597</v>
+      </c>
+    </row>
+    <row r="4" spans="2:4">
+      <c r="B4" s="112" t="s">
+        <v>594</v>
+      </c>
+      <c r="C4" s="112" t="s">
+        <v>595</v>
+      </c>
+      <c r="D4" s="112" t="s">
+        <v>596</v>
+      </c>
+    </row>
+    <row r="5" spans="2:4">
+      <c r="B5" s="68" t="s">
+        <v>580</v>
+      </c>
+      <c r="C5" s="68" t="s">
+        <v>581</v>
+      </c>
+      <c r="D5" s="68" t="s">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="6" spans="2:4">
+      <c r="B6" s="68" t="s">
+        <v>583</v>
+      </c>
+      <c r="C6" s="68" t="b">
+        <v>1</v>
+      </c>
+      <c r="D6" s="68" t="s">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="7" spans="2:4">
+      <c r="B7" s="68" t="s">
+        <v>583</v>
+      </c>
+      <c r="C7" s="68" t="b">
+        <v>0</v>
+      </c>
+      <c r="D7" s="68" t="s">
+        <v>584</v>
+      </c>
+    </row>
+    <row r="8" spans="2:4">
+      <c r="B8" s="68" t="s">
+        <v>585</v>
+      </c>
+      <c r="C8" s="68" t="s">
+        <v>308</v>
+      </c>
+      <c r="D8" s="68" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="9" spans="2:4">
+      <c r="B9" s="68" t="s">
+        <v>585</v>
+      </c>
+      <c r="C9" s="68" t="s">
+        <v>587</v>
+      </c>
+      <c r="D9" s="68" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="10" spans="2:4">
+      <c r="B10" s="68" t="s">
+        <v>580</v>
+      </c>
+      <c r="C10" s="68" t="s">
+        <v>589</v>
+      </c>
+      <c r="D10" s="68" t="s">
+        <v>590</v>
+      </c>
+    </row>
+    <row r="11" spans="2:4">
+      <c r="B11" s="68" t="s">
+        <v>591</v>
+      </c>
+      <c r="C11" s="68" t="s">
+        <v>592</v>
+      </c>
+      <c r="D11" s="68" t="s">
+        <v>593</v>
+      </c>
+    </row>
+    <row r="13" spans="2:4">
+      <c r="B13" s="68" t="s">
+        <v>637</v>
+      </c>
+    </row>
+    <row r="15" spans="2:4">
+      <c r="B15" s="112" t="s">
+        <v>594</v>
+      </c>
+      <c r="C15" s="112" t="s">
+        <v>595</v>
+      </c>
+      <c r="D15" s="112" t="s">
+        <v>596</v>
+      </c>
+    </row>
+    <row r="16" spans="2:4">
+      <c r="B16" s="68" t="s">
+        <v>580</v>
+      </c>
+      <c r="C16" s="68" t="s">
+        <v>581</v>
+      </c>
+      <c r="D16" s="68" t="s">
+        <v>598</v>
+      </c>
+    </row>
+    <row r="17" spans="2:4">
+      <c r="B17" s="68" t="s">
+        <v>580</v>
+      </c>
+      <c r="C17" s="68" t="s">
+        <v>589</v>
+      </c>
+      <c r="D17" s="68" t="s">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="18" spans="2:4">
+      <c r="B18" s="68" t="s">
+        <v>583</v>
+      </c>
+      <c r="C18" s="68" t="b">
+        <v>1</v>
+      </c>
+      <c r="D18" s="68" t="s">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="19" spans="2:4">
+      <c r="B19" s="68" t="s">
+        <v>583</v>
+      </c>
+      <c r="C19" s="68" t="b">
+        <v>0</v>
+      </c>
+      <c r="D19" s="68" t="s">
+        <v>584</v>
+      </c>
+    </row>
+    <row r="20" spans="2:4">
+      <c r="B20" s="68" t="s">
+        <v>585</v>
+      </c>
+      <c r="C20" s="68" t="s">
+        <v>579</v>
+      </c>
+      <c r="D20" s="68" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="21" spans="2:4">
+      <c r="B21" s="68" t="s">
+        <v>585</v>
+      </c>
+      <c r="C21" s="68" t="s">
+        <v>601</v>
+      </c>
+      <c r="D21" s="68" t="s">
+        <v>602</v>
+      </c>
+    </row>
+    <row r="22" spans="2:4">
+      <c r="B22" s="68" t="s">
+        <v>583</v>
+      </c>
+      <c r="C22" s="68" t="s">
+        <v>524</v>
+      </c>
+      <c r="D22" s="68" t="s">
+        <v>603</v>
+      </c>
+    </row>
+    <row r="23" spans="2:4">
+      <c r="B23" s="68" t="s">
+        <v>583</v>
+      </c>
+      <c r="C23" s="68" t="s">
+        <v>604</v>
+      </c>
+      <c r="D23" s="68" t="s">
+        <v>605</v>
+      </c>
+    </row>
+    <row r="24" spans="2:4">
+      <c r="B24" s="68" t="s">
+        <v>583</v>
+      </c>
+      <c r="C24" s="68" t="s">
+        <v>606</v>
+      </c>
+      <c r="D24" s="68" t="s">
+        <v>607</v>
+      </c>
+    </row>
+    <row r="25" spans="2:4">
+      <c r="B25" s="68" t="s">
+        <v>585</v>
+      </c>
+      <c r="C25" s="68" t="s">
+        <v>174</v>
+      </c>
+      <c r="D25" s="68" t="s">
+        <v>608</v>
+      </c>
+    </row>
+    <row r="26" spans="2:4">
+      <c r="B26" s="68" t="s">
+        <v>580</v>
+      </c>
+      <c r="C26" s="68" t="s">
+        <v>609</v>
+      </c>
+      <c r="D26" s="68" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="27" spans="2:4">
+      <c r="B27" s="68" t="s">
+        <v>591</v>
+      </c>
+      <c r="C27" s="68" t="s">
+        <v>592</v>
+      </c>
+      <c r="D27" s="68" t="s">
+        <v>611</v>
+      </c>
+    </row>
+    <row r="28" spans="2:4">
+      <c r="B28" s="68" t="s">
+        <v>591</v>
+      </c>
+      <c r="C28" s="68" t="s">
+        <v>612</v>
+      </c>
+      <c r="D28" s="68" t="s">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="29" spans="2:4">
+      <c r="B29" s="68" t="s">
+        <v>591</v>
+      </c>
+      <c r="C29" s="68" t="s">
+        <v>614</v>
+      </c>
+      <c r="D29" s="68" t="s">
+        <v>615</v>
+      </c>
+    </row>
+    <row r="30" spans="2:4">
+      <c r="B30" s="68" t="s">
+        <v>585</v>
+      </c>
+      <c r="C30" s="68" t="s">
+        <v>616</v>
+      </c>
+      <c r="D30" s="68" t="s">
+        <v>617</v>
+      </c>
+    </row>
+    <row r="31" spans="2:4">
+      <c r="B31" s="68" t="s">
+        <v>591</v>
+      </c>
+      <c r="C31" s="68" t="s">
+        <v>618</v>
+      </c>
+      <c r="D31" s="68" t="s">
+        <v>619</v>
+      </c>
+    </row>
+    <row r="32" spans="2:4">
+      <c r="B32" s="68" t="s">
+        <v>585</v>
+      </c>
+      <c r="C32" s="68" t="s">
+        <v>171</v>
+      </c>
+      <c r="D32" s="68" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="33" spans="2:4">
+      <c r="B33" s="68" t="s">
+        <v>580</v>
+      </c>
+      <c r="C33" s="68" t="s">
+        <v>190</v>
+      </c>
+      <c r="D33" s="68" t="s">
+        <v>621</v>
+      </c>
+    </row>
+    <row r="34" spans="2:4">
+      <c r="B34" s="68" t="s">
+        <v>622</v>
+      </c>
+      <c r="C34" s="68" t="s">
+        <v>623</v>
+      </c>
+      <c r="D34" s="68" t="s">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="35" spans="2:4">
+      <c r="B35" s="68" t="s">
+        <v>622</v>
+      </c>
+      <c r="C35" s="68" t="s">
+        <v>625</v>
+      </c>
+      <c r="D35" s="68" t="s">
+        <v>626</v>
+      </c>
+    </row>
+    <row r="36" spans="2:4">
+      <c r="B36" s="68" t="s">
+        <v>585</v>
+      </c>
+      <c r="C36" s="68" t="s">
+        <v>627</v>
+      </c>
+      <c r="D36" s="68" t="s">
+        <v>628</v>
+      </c>
+    </row>
+    <row r="37" spans="2:4">
+      <c r="B37" s="68" t="s">
+        <v>585</v>
+      </c>
+      <c r="C37" s="68" t="s">
+        <v>629</v>
+      </c>
+      <c r="D37" s="68" t="s">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="38" spans="2:4">
+      <c r="B38" s="68" t="s">
+        <v>580</v>
+      </c>
+      <c r="C38" s="68" t="s">
+        <v>631</v>
+      </c>
+      <c r="D38" s="68" t="s">
+        <v>632</v>
+      </c>
+    </row>
+    <row r="39" spans="2:4">
+      <c r="B39" s="68" t="s">
+        <v>583</v>
+      </c>
+      <c r="C39" s="68" t="s">
+        <v>633</v>
+      </c>
+      <c r="D39" s="68" t="s">
+        <v>634</v>
+      </c>
+    </row>
+    <row r="40" spans="2:4">
+      <c r="B40" s="68" t="s">
+        <v>583</v>
+      </c>
+      <c r="C40" s="68" t="s">
+        <v>635</v>
+      </c>
+      <c r="D40" s="68" t="s">
+        <v>636</v>
+      </c>
+    </row>
+    <row r="42" spans="2:4">
+      <c r="B42" s="68" t="s">
+        <v>638</v>
+      </c>
+    </row>
+    <row r="44" spans="2:4">
+      <c r="B44" s="112" t="s">
+        <v>594</v>
+      </c>
+      <c r="C44" s="112" t="s">
+        <v>595</v>
+      </c>
+      <c r="D44" s="112" t="s">
+        <v>596</v>
+      </c>
+    </row>
+    <row r="45" spans="2:4">
+      <c r="B45" s="68" t="s">
+        <v>580</v>
+      </c>
+      <c r="C45" s="68" t="s">
+        <v>581</v>
+      </c>
+      <c r="D45" s="68" t="s">
+        <v>598</v>
+      </c>
+    </row>
+    <row r="46" spans="2:4">
+      <c r="B46" s="68" t="s">
+        <v>580</v>
+      </c>
+      <c r="C46" s="68" t="s">
+        <v>589</v>
+      </c>
+      <c r="D46" s="68" t="s">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="47" spans="2:4">
+      <c r="B47" s="68" t="s">
+        <v>583</v>
+      </c>
+      <c r="C47" s="68" t="b">
+        <v>1</v>
+      </c>
+      <c r="D47" s="68" t="s">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="48" spans="2:4">
+      <c r="B48" s="68" t="s">
+        <v>583</v>
+      </c>
+      <c r="C48" s="68" t="b">
+        <v>0</v>
+      </c>
+      <c r="D48" s="68" t="s">
+        <v>584</v>
+      </c>
+    </row>
+    <row r="49" spans="2:4">
+      <c r="B49" s="68" t="s">
+        <v>585</v>
+      </c>
+      <c r="C49" s="68" t="s">
+        <v>579</v>
+      </c>
+      <c r="D49" s="68" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="50" spans="2:4">
+      <c r="B50" s="68" t="s">
+        <v>585</v>
+      </c>
+      <c r="C50" s="68" t="s">
+        <v>601</v>
+      </c>
+      <c r="D50" s="68" t="s">
+        <v>602</v>
+      </c>
+    </row>
+    <row r="51" spans="2:4">
+      <c r="B51" s="68" t="s">
+        <v>583</v>
+      </c>
+      <c r="C51" s="68" t="s">
+        <v>524</v>
+      </c>
+      <c r="D51" s="68" t="s">
+        <v>603</v>
+      </c>
+    </row>
+    <row r="52" spans="2:4">
+      <c r="B52" s="68" t="s">
+        <v>583</v>
+      </c>
+      <c r="C52" s="68" t="s">
+        <v>604</v>
+      </c>
+      <c r="D52" s="68" t="s">
+        <v>605</v>
+      </c>
+    </row>
+    <row r="53" spans="2:4">
+      <c r="B53" s="68" t="s">
+        <v>583</v>
+      </c>
+      <c r="C53" s="68" t="s">
+        <v>606</v>
+      </c>
+      <c r="D53" s="68" t="s">
+        <v>607</v>
+      </c>
+    </row>
+    <row r="54" spans="2:4">
+      <c r="B54" s="68" t="s">
+        <v>585</v>
+      </c>
+      <c r="C54" s="68" t="s">
+        <v>639</v>
+      </c>
+      <c r="D54" s="68" t="s">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="55" spans="2:4">
+      <c r="B55" s="68" t="s">
+        <v>583</v>
+      </c>
+      <c r="C55" s="68" t="s">
+        <v>641</v>
+      </c>
+      <c r="D55" s="68" t="s">
+        <v>598</v>
+      </c>
+    </row>
+    <row r="56" spans="2:4">
+      <c r="B56" s="68" t="s">
+        <v>583</v>
+      </c>
+      <c r="C56" s="68" t="s">
+        <v>642</v>
+      </c>
+      <c r="D56" s="68" t="s">
+        <v>617</v>
+      </c>
+    </row>
+    <row r="57" spans="2:4">
+      <c r="B57" s="68" t="s">
+        <v>585</v>
+      </c>
+      <c r="C57" s="68" t="s">
+        <v>174</v>
+      </c>
+      <c r="D57" s="68" t="s">
+        <v>608</v>
+      </c>
+    </row>
+    <row r="58" spans="2:4">
+      <c r="B58" s="68" t="s">
+        <v>580</v>
+      </c>
+      <c r="C58" s="68" t="s">
+        <v>609</v>
+      </c>
+      <c r="D58" s="68" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="59" spans="2:4">
+      <c r="B59" s="68" t="s">
+        <v>591</v>
+      </c>
+      <c r="C59" s="68" t="s">
+        <v>592</v>
+      </c>
+      <c r="D59" s="68" t="s">
+        <v>611</v>
+      </c>
+    </row>
+    <row r="60" spans="2:4">
+      <c r="B60" s="68" t="s">
+        <v>591</v>
+      </c>
+      <c r="C60" s="68" t="s">
+        <v>612</v>
+      </c>
+      <c r="D60" s="68" t="s">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="61" spans="2:4">
+      <c r="B61" s="68" t="s">
+        <v>591</v>
+      </c>
+      <c r="C61" s="68" t="s">
+        <v>614</v>
+      </c>
+      <c r="D61" s="68" t="s">
+        <v>615</v>
+      </c>
+    </row>
+    <row r="62" spans="2:4">
+      <c r="B62" s="68" t="s">
+        <v>585</v>
+      </c>
+      <c r="C62" s="68" t="s">
+        <v>616</v>
+      </c>
+      <c r="D62" s="68" t="s">
+        <v>617</v>
+      </c>
+    </row>
+    <row r="63" spans="2:4">
+      <c r="B63" s="68" t="s">
+        <v>591</v>
+      </c>
+      <c r="C63" s="68" t="s">
+        <v>618</v>
+      </c>
+      <c r="D63" s="68" t="s">
+        <v>619</v>
+      </c>
+    </row>
+    <row r="64" spans="2:4">
+      <c r="B64" s="68" t="s">
+        <v>591</v>
+      </c>
+      <c r="C64" s="68" t="s">
+        <v>643</v>
+      </c>
+      <c r="D64" s="68" t="s">
+        <v>644</v>
+      </c>
+    </row>
+    <row r="65" spans="2:4">
+      <c r="B65" s="68" t="s">
+        <v>591</v>
+      </c>
+      <c r="C65" s="68" t="s">
+        <v>645</v>
+      </c>
+      <c r="D65" s="68" t="s">
+        <v>646</v>
+      </c>
+    </row>
+    <row r="66" spans="2:4">
+      <c r="B66" s="68" t="s">
+        <v>591</v>
+      </c>
+      <c r="C66" s="68" t="s">
+        <v>647</v>
+      </c>
+      <c r="D66" s="68" t="s">
+        <v>648</v>
+      </c>
+    </row>
+    <row r="67" spans="2:4">
+      <c r="B67" s="68" t="s">
+        <v>580</v>
+      </c>
+      <c r="C67" s="68" t="s">
+        <v>649</v>
+      </c>
+      <c r="D67" s="68" t="s">
+        <v>650</v>
+      </c>
+    </row>
+    <row r="68" spans="2:4">
+      <c r="B68" s="68" t="s">
+        <v>580</v>
+      </c>
+      <c r="C68" s="68" t="s">
+        <v>651</v>
+      </c>
+      <c r="D68" s="68" t="s">
+        <v>652</v>
+      </c>
+    </row>
+    <row r="69" spans="2:4">
+      <c r="B69" s="68" t="s">
+        <v>591</v>
+      </c>
+      <c r="C69" s="68" t="s">
+        <v>653</v>
+      </c>
+      <c r="D69" s="68" t="s">
+        <v>654</v>
+      </c>
+    </row>
+    <row r="70" spans="2:4">
+      <c r="B70" s="68" t="s">
+        <v>585</v>
+      </c>
+      <c r="C70" s="68" t="s">
+        <v>171</v>
+      </c>
+      <c r="D70" s="68" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="71" spans="2:4">
+      <c r="B71" s="68" t="s">
+        <v>580</v>
+      </c>
+      <c r="C71" s="68" t="s">
+        <v>190</v>
+      </c>
+      <c r="D71" s="68" t="s">
+        <v>621</v>
+      </c>
+    </row>
+    <row r="72" spans="2:4">
+      <c r="B72" s="68" t="s">
+        <v>622</v>
+      </c>
+      <c r="C72" s="68" t="s">
+        <v>623</v>
+      </c>
+      <c r="D72" s="68" t="s">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="73" spans="2:4">
+      <c r="B73" s="68" t="s">
+        <v>622</v>
+      </c>
+      <c r="C73" s="68" t="s">
+        <v>625</v>
+      </c>
+      <c r="D73" s="68" t="s">
+        <v>626</v>
+      </c>
+    </row>
+    <row r="74" spans="2:4">
+      <c r="B74" s="68" t="s">
+        <v>580</v>
+      </c>
+      <c r="C74" s="68" t="s">
+        <v>655</v>
+      </c>
+      <c r="D74" s="68" t="s">
+        <v>656</v>
+      </c>
+    </row>
+    <row r="75" spans="2:4">
+      <c r="B75" s="68" t="s">
+        <v>580</v>
+      </c>
+      <c r="C75" s="68" t="s">
+        <v>657</v>
+      </c>
+      <c r="D75" s="68" t="s">
+        <v>658</v>
+      </c>
+    </row>
+    <row r="76" spans="2:4">
+      <c r="B76" s="68" t="s">
+        <v>580</v>
+      </c>
+      <c r="C76" s="68" t="s">
+        <v>659</v>
+      </c>
+      <c r="D76" s="68" t="s">
+        <v>660</v>
+      </c>
+    </row>
+    <row r="77" spans="2:4">
+      <c r="B77" s="68" t="s">
+        <v>583</v>
+      </c>
+      <c r="C77" s="68" t="s">
+        <v>661</v>
+      </c>
+      <c r="D77" s="68" t="s">
+        <v>662</v>
+      </c>
+    </row>
+    <row r="78" spans="2:4">
+      <c r="B78" s="68" t="s">
+        <v>583</v>
+      </c>
+      <c r="C78" s="68" t="s">
+        <v>663</v>
+      </c>
+      <c r="D78" s="68" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="79" spans="2:4">
+      <c r="B79" s="68" t="s">
+        <v>583</v>
+      </c>
+      <c r="C79" s="68" t="s">
+        <v>665</v>
+      </c>
+      <c r="D79" s="68" t="s">
+        <v>666</v>
+      </c>
+    </row>
+    <row r="80" spans="2:4">
+      <c r="B80" s="68" t="s">
+        <v>585</v>
+      </c>
+      <c r="C80" s="68" t="s">
+        <v>667</v>
+      </c>
+      <c r="D80" s="68" t="s">
+        <v>668</v>
+      </c>
+    </row>
+    <row r="81" spans="2:4">
+      <c r="B81" s="68" t="s">
+        <v>585</v>
+      </c>
+      <c r="C81" s="68" t="s">
+        <v>669</v>
+      </c>
+      <c r="D81" s="68" t="s">
+        <v>670</v>
+      </c>
+    </row>
+    <row r="82" spans="2:4">
+      <c r="B82" s="68" t="s">
+        <v>585</v>
+      </c>
+      <c r="C82" s="68" t="s">
+        <v>671</v>
+      </c>
+      <c r="D82" s="68" t="s">
+        <v>672</v>
+      </c>
+    </row>
+    <row r="83" spans="2:4">
+      <c r="B83" s="68" t="s">
+        <v>585</v>
+      </c>
+      <c r="C83" s="68" t="s">
+        <v>673</v>
+      </c>
+      <c r="D83" s="68" t="s">
+        <v>674</v>
+      </c>
+    </row>
+    <row r="84" spans="2:4">
+      <c r="B84" s="68" t="s">
+        <v>583</v>
+      </c>
+      <c r="C84" s="68" t="s">
+        <v>675</v>
+      </c>
+      <c r="D84" s="68" t="s">
+        <v>676</v>
+      </c>
+    </row>
+    <row r="85" spans="2:4">
+      <c r="B85" s="68" t="s">
+        <v>583</v>
+      </c>
+      <c r="C85" s="68" t="s">
+        <v>677</v>
+      </c>
+      <c r="D85" s="68" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="86" spans="2:4">
+      <c r="B86" s="68" t="s">
+        <v>585</v>
+      </c>
+      <c r="C86" s="68" t="s">
+        <v>679</v>
+      </c>
+      <c r="D86" s="68" t="s">
+        <v>680</v>
+      </c>
+    </row>
+    <row r="87" spans="2:4">
+      <c r="B87" s="68" t="s">
+        <v>585</v>
+      </c>
+      <c r="C87" s="68" t="s">
+        <v>681</v>
+      </c>
+      <c r="D87" s="68" t="s">
+        <v>682</v>
+      </c>
+    </row>
+    <row r="88" spans="2:4">
+      <c r="B88" s="68" t="s">
+        <v>585</v>
+      </c>
+      <c r="C88" s="68" t="s">
+        <v>683</v>
+      </c>
+      <c r="D88" s="68" t="s">
+        <v>684</v>
+      </c>
+    </row>
+    <row r="89" spans="2:4">
+      <c r="B89" s="68" t="s">
+        <v>585</v>
+      </c>
+      <c r="C89" s="68" t="s">
+        <v>685</v>
+      </c>
+      <c r="D89" s="68" t="s">
+        <v>686</v>
+      </c>
+    </row>
+    <row r="90" spans="2:4">
+      <c r="B90" s="68" t="s">
+        <v>583</v>
+      </c>
+      <c r="C90" s="68" t="s">
+        <v>687</v>
+      </c>
+      <c r="D90" s="68" t="s">
+        <v>688</v>
+      </c>
+    </row>
+    <row r="91" spans="2:4">
+      <c r="B91" s="68" t="s">
+        <v>583</v>
+      </c>
+      <c r="C91" s="68" t="s">
+        <v>689</v>
+      </c>
+      <c r="D91" s="68" t="s">
+        <v>690</v>
+      </c>
+    </row>
+    <row r="92" spans="2:4">
+      <c r="B92" s="68" t="s">
+        <v>585</v>
+      </c>
+      <c r="C92" s="68" t="s">
+        <v>691</v>
+      </c>
+      <c r="D92" s="68" t="s">
+        <v>692</v>
+      </c>
+    </row>
+    <row r="93" spans="2:4">
+      <c r="B93" s="68" t="s">
+        <v>585</v>
+      </c>
+      <c r="C93" s="68" t="s">
+        <v>693</v>
+      </c>
+      <c r="D93" s="68" t="s">
+        <v>694</v>
+      </c>
+    </row>
+    <row r="94" spans="2:4">
+      <c r="B94" s="68" t="s">
+        <v>585</v>
+      </c>
+      <c r="C94" s="68" t="s">
+        <v>695</v>
+      </c>
+      <c r="D94" s="68" t="s">
+        <v>696</v>
+      </c>
+    </row>
+    <row r="95" spans="2:4">
+      <c r="B95" s="68" t="s">
+        <v>585</v>
+      </c>
+      <c r="C95" s="68" t="s">
+        <v>697</v>
+      </c>
+      <c r="D95" s="68" t="s">
+        <v>698</v>
+      </c>
+    </row>
+    <row r="96" spans="2:4">
+      <c r="B96" s="68" t="s">
+        <v>585</v>
+      </c>
+      <c r="C96" s="68" t="s">
+        <v>699</v>
+      </c>
+      <c r="D96" s="68" t="s">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="97" spans="2:4">
+      <c r="B97" s="68" t="s">
+        <v>585</v>
+      </c>
+      <c r="C97" s="68" t="s">
+        <v>701</v>
+      </c>
+      <c r="D97" s="68" t="s">
+        <v>702</v>
+      </c>
+    </row>
+    <row r="98" spans="2:4">
+      <c r="B98" s="68" t="s">
+        <v>585</v>
+      </c>
+      <c r="C98" s="68" t="s">
+        <v>703</v>
+      </c>
+      <c r="D98" s="68" t="s">
+        <v>704</v>
+      </c>
+    </row>
+    <row r="99" spans="2:4">
+      <c r="B99" s="68" t="s">
+        <v>585</v>
+      </c>
+      <c r="C99" s="68" t="s">
+        <v>629</v>
+      </c>
+      <c r="D99" s="68" t="s">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="100" spans="2:4">
+      <c r="B100" s="68" t="s">
+        <v>585</v>
+      </c>
+      <c r="C100" s="68" t="s">
+        <v>705</v>
+      </c>
+      <c r="D100" s="68" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="101" spans="2:4">
+      <c r="B101" s="68" t="s">
+        <v>585</v>
+      </c>
+      <c r="C101" s="68" t="s">
+        <v>707</v>
+      </c>
+      <c r="D101" s="68" t="s">
+        <v>708</v>
+      </c>
+    </row>
+    <row r="102" spans="2:4">
+      <c r="B102" s="68" t="s">
+        <v>585</v>
+      </c>
+      <c r="C102" s="68" t="s">
+        <v>709</v>
+      </c>
+      <c r="D102" s="68" t="s">
+        <v>710</v>
+      </c>
+    </row>
+    <row r="103" spans="2:4">
+      <c r="B103" s="68" t="s">
+        <v>585</v>
+      </c>
+      <c r="C103" s="68" t="s">
+        <v>711</v>
+      </c>
+      <c r="D103" s="68" t="s">
+        <v>712</v>
+      </c>
+    </row>
+    <row r="104" spans="2:4">
+      <c r="B104" s="68" t="s">
+        <v>585</v>
+      </c>
+      <c r="C104" s="68" t="s">
+        <v>713</v>
+      </c>
+      <c r="D104" s="68" t="s">
+        <v>714</v>
+      </c>
+    </row>
+    <row r="105" spans="2:4">
+      <c r="B105" s="68" t="s">
+        <v>580</v>
+      </c>
+      <c r="C105" s="68" t="s">
+        <v>715</v>
+      </c>
+      <c r="D105" s="68" t="s">
+        <v>716</v>
+      </c>
+    </row>
+    <row r="106" spans="2:4">
+      <c r="B106" s="68" t="s">
+        <v>580</v>
+      </c>
+      <c r="C106" s="68" t="s">
+        <v>717</v>
+      </c>
+      <c r="D106" s="68" t="s">
+        <v>718</v>
+      </c>
+    </row>
+    <row r="107" spans="2:4">
+      <c r="B107" s="68" t="s">
+        <v>580</v>
+      </c>
+      <c r="C107" s="68" t="s">
+        <v>719</v>
+      </c>
+      <c r="D107" s="68" t="s">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="108" spans="2:4">
+      <c r="B108" s="68" t="s">
+        <v>580</v>
+      </c>
+      <c r="C108" s="68" t="s">
+        <v>721</v>
+      </c>
+      <c r="D108" s="68" t="s">
+        <v>722</v>
+      </c>
+    </row>
+    <row r="109" spans="2:4">
+      <c r="B109" s="68" t="s">
+        <v>580</v>
+      </c>
+      <c r="C109" s="68" t="s">
+        <v>723</v>
+      </c>
+      <c r="D109" s="68" t="s">
+        <v>724</v>
+      </c>
+    </row>
+    <row r="110" spans="2:4">
+      <c r="B110" s="68" t="s">
+        <v>585</v>
+      </c>
+      <c r="C110" s="68" t="s">
+        <v>627</v>
+      </c>
+      <c r="D110" s="68" t="s">
+        <v>628</v>
+      </c>
+    </row>
+    <row r="111" spans="2:4">
+      <c r="B111" s="68" t="s">
+        <v>580</v>
+      </c>
+      <c r="C111" s="68" t="s">
+        <v>470</v>
+      </c>
+      <c r="D111" s="68" t="s">
+        <v>725</v>
+      </c>
+    </row>
+    <row r="112" spans="2:4">
+      <c r="B112" s="68" t="s">
+        <v>580</v>
+      </c>
+      <c r="C112" s="68" t="s">
+        <v>726</v>
+      </c>
+      <c r="D112" s="68" t="s">
+        <v>727</v>
+      </c>
+    </row>
+    <row r="113" spans="2:4">
+      <c r="B113" s="68" t="s">
+        <v>585</v>
+      </c>
+      <c r="C113" s="68" t="s">
+        <v>463</v>
+      </c>
+      <c r="D113" s="68" t="s">
+        <v>728</v>
+      </c>
+    </row>
+    <row r="114" spans="2:4">
+      <c r="B114" s="68" t="s">
+        <v>580</v>
+      </c>
+      <c r="C114" s="68" t="s">
+        <v>729</v>
+      </c>
+      <c r="D114" s="68" t="s">
+        <v>730</v>
+      </c>
+    </row>
+    <row r="115" spans="2:4">
+      <c r="B115" s="68" t="s">
+        <v>580</v>
+      </c>
+      <c r="C115" s="68" t="s">
+        <v>731</v>
+      </c>
+      <c r="D115" s="68" t="s">
+        <v>732</v>
+      </c>
+    </row>
+    <row r="116" spans="2:4">
+      <c r="B116" s="68" t="s">
+        <v>580</v>
+      </c>
+      <c r="C116" s="68" t="s">
+        <v>542</v>
+      </c>
+      <c r="D116" s="68" t="s">
+        <v>733</v>
+      </c>
+    </row>
+    <row r="117" spans="2:4">
+      <c r="B117" s="68" t="s">
+        <v>580</v>
+      </c>
+      <c r="C117" s="68" t="s">
+        <v>734</v>
+      </c>
+      <c r="D117" s="68" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="118" spans="2:4">
+      <c r="B118" s="68" t="s">
+        <v>580</v>
+      </c>
+      <c r="C118" s="68" t="s">
+        <v>736</v>
+      </c>
+      <c r="D118" s="68" t="s">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="119" spans="2:4">
+      <c r="B119" s="68" t="s">
+        <v>580</v>
+      </c>
+      <c r="C119" s="68" t="s">
+        <v>631</v>
+      </c>
+      <c r="D119" s="68" t="s">
+        <v>632</v>
+      </c>
+    </row>
+    <row r="120" spans="2:4">
+      <c r="B120" s="68" t="s">
+        <v>583</v>
+      </c>
+      <c r="C120" s="68" t="s">
+        <v>633</v>
+      </c>
+      <c r="D120" s="68" t="s">
+        <v>634</v>
+      </c>
+    </row>
+    <row r="121" spans="2:4">
+      <c r="B121" s="68" t="s">
+        <v>583</v>
+      </c>
+      <c r="C121" s="68" t="s">
+        <v>635</v>
+      </c>
+      <c r="D121" s="68" t="s">
+        <v>636</v>
+      </c>
+    </row>
+    <row r="122" spans="2:4">
+      <c r="B122" s="68" t="s">
+        <v>585</v>
+      </c>
+      <c r="C122" s="68" t="s">
+        <v>738</v>
+      </c>
+      <c r="D122" s="68" t="s">
+        <v>739</v>
+      </c>
+    </row>
+    <row r="123" spans="2:4">
+      <c r="B123" s="68" t="s">
+        <v>585</v>
+      </c>
+      <c r="C123" s="68" t="s">
+        <v>740</v>
+      </c>
+      <c r="D123" s="68" t="s">
+        <v>741</v>
+      </c>
+    </row>
+    <row r="124" spans="2:4">
+      <c r="B124" s="68" t="s">
+        <v>585</v>
+      </c>
+      <c r="C124" s="68" t="s">
+        <v>742</v>
+      </c>
+      <c r="D124" s="68" t="s">
+        <v>743</v>
+      </c>
+    </row>
+    <row r="125" spans="2:4">
+      <c r="B125" s="68" t="s">
+        <v>585</v>
+      </c>
+      <c r="C125" s="68" t="s">
+        <v>744</v>
+      </c>
+      <c r="D125" s="68" t="s">
+        <v>745</v>
+      </c>
+    </row>
+    <row r="126" spans="2:4">
+      <c r="B126" s="68" t="s">
+        <v>585</v>
+      </c>
+      <c r="C126" s="68" t="s">
+        <v>746</v>
+      </c>
+      <c r="D126" s="68" t="s">
+        <v>747</v>
+      </c>
+    </row>
+    <row r="127" spans="2:4">
+      <c r="B127" s="68" t="s">
+        <v>585</v>
+      </c>
+      <c r="C127" s="68" t="s">
+        <v>748</v>
+      </c>
+      <c r="D127" s="68" t="s">
+        <v>749</v>
+      </c>
+    </row>
+    <row r="128" spans="2:4">
+      <c r="B128" s="68" t="s">
+        <v>585</v>
+      </c>
+      <c r="C128" s="68" t="s">
+        <v>750</v>
+      </c>
+      <c r="D128" s="68" t="s">
+        <v>751</v>
+      </c>
+    </row>
+    <row r="129" spans="2:4">
+      <c r="B129" s="68" t="s">
+        <v>585</v>
+      </c>
+      <c r="C129" s="68" t="s">
+        <v>60</v>
+      </c>
+      <c r="D129" s="68" t="s">
+        <v>752</v>
+      </c>
+    </row>
+    <row r="130" spans="2:4">
+      <c r="B130" s="68" t="s">
+        <v>580</v>
+      </c>
+      <c r="C130" s="68" t="s">
+        <v>753</v>
+      </c>
+      <c r="D130" s="68" t="s">
+        <v>754</v>
+      </c>
+    </row>
+    <row r="131" spans="2:4">
+      <c r="B131" s="68" t="s">
+        <v>585</v>
+      </c>
+      <c r="C131" s="68" t="s">
+        <v>755</v>
+      </c>
+      <c r="D131" s="68" t="s">
+        <v>756</v>
+      </c>
+    </row>
+    <row r="132" spans="2:4">
+      <c r="B132" s="68" t="s">
+        <v>585</v>
+      </c>
+      <c r="C132" s="68" t="s">
+        <v>757</v>
+      </c>
+      <c r="D132" s="68" t="s">
+        <v>758</v>
+      </c>
+    </row>
+    <row r="133" spans="2:4">
+      <c r="B133" s="68" t="s">
+        <v>580</v>
+      </c>
+      <c r="C133" s="68" t="s">
+        <v>535</v>
+      </c>
+      <c r="D133" s="68" t="s">
+        <v>759</v>
+      </c>
+    </row>
+    <row r="134" spans="2:4">
+      <c r="B134" s="68" t="s">
+        <v>580</v>
+      </c>
+      <c r="C134" s="68" t="s">
+        <v>760</v>
+      </c>
+      <c r="D134" s="68" t="s">
+        <v>761</v>
+      </c>
+    </row>
+    <row r="135" spans="2:4">
+      <c r="B135" s="68" t="s">
+        <v>585</v>
+      </c>
+      <c r="C135" s="68" t="s">
+        <v>762</v>
+      </c>
+      <c r="D135" s="68" t="s">
+        <v>763</v>
+      </c>
+    </row>
+    <row r="136" spans="2:4">
+      <c r="B136" s="68" t="s">
+        <v>585</v>
+      </c>
+      <c r="C136" s="68" t="s">
+        <v>764</v>
+      </c>
+      <c r="D136" s="68" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="137" spans="2:4">
+      <c r="B137" s="68" t="s">
+        <v>585</v>
+      </c>
+      <c r="C137" s="68" t="s">
+        <v>766</v>
+      </c>
+      <c r="D137" s="68" t="s">
+        <v>767</v>
+      </c>
+    </row>
+    <row r="138" spans="2:4">
+      <c r="B138" s="68" t="s">
+        <v>585</v>
+      </c>
+      <c r="C138" s="68" t="s">
+        <v>768</v>
+      </c>
+      <c r="D138" s="68" t="s">
+        <v>769</v>
+      </c>
+    </row>
+    <row r="139" spans="2:4">
+      <c r="B139" s="68" t="s">
+        <v>585</v>
+      </c>
+      <c r="C139" s="68" t="s">
+        <v>770</v>
+      </c>
+      <c r="D139" s="68" t="s">
+        <v>771</v>
+      </c>
+    </row>
+    <row r="140" spans="2:4">
+      <c r="B140" s="68" t="s">
+        <v>585</v>
+      </c>
+      <c r="C140" s="68" t="s">
+        <v>772</v>
+      </c>
+      <c r="D140" s="68" t="s">
+        <v>773</v>
+      </c>
+    </row>
+    <row r="141" spans="2:4">
+      <c r="B141" s="68" t="s">
+        <v>585</v>
+      </c>
+      <c r="C141" s="68" t="s">
+        <v>561</v>
+      </c>
+      <c r="D141" s="68" t="s">
+        <v>774</v>
+      </c>
+    </row>
+    <row r="142" spans="2:4">
+      <c r="B142" s="68" t="s">
+        <v>585</v>
+      </c>
+      <c r="C142" s="68" t="s">
+        <v>775</v>
+      </c>
+      <c r="D142" s="68" t="s">
+        <v>776</v>
+      </c>
+    </row>
+    <row r="143" spans="2:4">
+      <c r="B143" s="68" t="s">
+        <v>583</v>
+      </c>
+      <c r="C143" s="68" t="s">
+        <v>554</v>
+      </c>
+      <c r="D143" s="68" t="s">
+        <v>777</v>
+      </c>
+    </row>
+    <row r="144" spans="2:4">
+      <c r="B144" s="68" t="s">
+        <v>580</v>
+      </c>
+      <c r="C144" s="68" t="s">
+        <v>778</v>
+      </c>
+      <c r="D144" s="68" t="s">
+        <v>779</v>
+      </c>
+    </row>
+    <row r="145" spans="2:4">
+      <c r="B145" s="68" t="s">
+        <v>580</v>
+      </c>
+      <c r="C145" s="68" t="s">
+        <v>780</v>
+      </c>
+      <c r="D145" s="68" t="s">
+        <v>781</v>
+      </c>
+    </row>
+    <row r="147" spans="2:4">
+      <c r="B147" s="68" t="s">
+        <v>782</v>
+      </c>
+    </row>
+    <row r="149" spans="2:4">
+      <c r="B149" s="112" t="s">
+        <v>594</v>
+      </c>
+      <c r="C149" s="112" t="s">
+        <v>595</v>
+      </c>
+      <c r="D149" s="112" t="s">
+        <v>596</v>
+      </c>
+    </row>
+    <row r="150" spans="2:4">
+      <c r="B150" s="68" t="s">
+        <v>580</v>
+      </c>
+      <c r="C150" s="68" t="s">
+        <v>581</v>
+      </c>
+      <c r="D150" s="68" t="s">
+        <v>598</v>
+      </c>
+    </row>
+    <row r="151" spans="2:4">
+      <c r="B151" s="68" t="s">
+        <v>580</v>
+      </c>
+      <c r="C151" s="68" t="s">
+        <v>589</v>
+      </c>
+      <c r="D151" s="68" t="s">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="152" spans="2:4">
+      <c r="B152" s="68" t="s">
+        <v>583</v>
+      </c>
+      <c r="C152" s="68" t="b">
+        <v>1</v>
+      </c>
+      <c r="D152" s="68" t="s">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="153" spans="2:4">
+      <c r="B153" s="68" t="s">
+        <v>583</v>
+      </c>
+      <c r="C153" s="68" t="b">
+        <v>0</v>
+      </c>
+      <c r="D153" s="68" t="s">
+        <v>584</v>
+      </c>
+    </row>
+    <row r="154" spans="2:4">
+      <c r="B154" s="68" t="s">
+        <v>585</v>
+      </c>
+      <c r="C154" s="68" t="s">
+        <v>579</v>
+      </c>
+      <c r="D154" s="68" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="155" spans="2:4">
+      <c r="B155" s="68" t="s">
+        <v>585</v>
+      </c>
+      <c r="C155" s="68" t="s">
+        <v>601</v>
+      </c>
+      <c r="D155" s="68" t="s">
+        <v>602</v>
+      </c>
+    </row>
+    <row r="156" spans="2:4">
+      <c r="B156" s="68" t="s">
+        <v>583</v>
+      </c>
+      <c r="C156" s="68" t="s">
+        <v>524</v>
+      </c>
+      <c r="D156" s="68" t="s">
+        <v>603</v>
+      </c>
+    </row>
+    <row r="157" spans="2:4">
+      <c r="B157" s="68" t="s">
+        <v>583</v>
+      </c>
+      <c r="C157" s="68" t="s">
+        <v>604</v>
+      </c>
+      <c r="D157" s="68" t="s">
+        <v>605</v>
+      </c>
+    </row>
+    <row r="158" spans="2:4">
+      <c r="B158" s="68" t="s">
+        <v>583</v>
+      </c>
+      <c r="C158" s="68" t="s">
+        <v>606</v>
+      </c>
+      <c r="D158" s="68" t="s">
+        <v>607</v>
+      </c>
+    </row>
+    <row r="159" spans="2:4">
+      <c r="B159" s="68" t="s">
+        <v>585</v>
+      </c>
+      <c r="C159" s="68" t="s">
+        <v>639</v>
+      </c>
+      <c r="D159" s="68" t="s">
+        <v>783</v>
+      </c>
+    </row>
+    <row r="160" spans="2:4">
+      <c r="B160" s="68" t="s">
+        <v>583</v>
+      </c>
+      <c r="C160" s="68" t="s">
+        <v>641</v>
+      </c>
+      <c r="D160" s="68" t="s">
+        <v>598</v>
+      </c>
+    </row>
+    <row r="161" spans="2:4">
+      <c r="B161" s="68" t="s">
+        <v>583</v>
+      </c>
+      <c r="C161" s="68" t="s">
+        <v>642</v>
+      </c>
+      <c r="D161" s="68" t="s">
+        <v>617</v>
+      </c>
+    </row>
+    <row r="162" spans="2:4">
+      <c r="B162" s="68" t="s">
+        <v>622</v>
+      </c>
+      <c r="C162" s="68" t="s">
+        <v>784</v>
+      </c>
+      <c r="D162" s="68" t="s">
+        <v>785</v>
+      </c>
+    </row>
+    <row r="163" spans="2:4">
+      <c r="B163" s="68" t="s">
+        <v>622</v>
+      </c>
+      <c r="C163" s="68" t="s">
+        <v>786</v>
+      </c>
+      <c r="D163" s="68" t="s">
+        <v>787</v>
+      </c>
+    </row>
+    <row r="164" spans="2:4">
+      <c r="B164" s="68" t="s">
+        <v>585</v>
+      </c>
+      <c r="C164" s="68" t="s">
+        <v>174</v>
+      </c>
+      <c r="D164" s="68" t="s">
+        <v>608</v>
+      </c>
+    </row>
+    <row r="165" spans="2:4">
+      <c r="B165" s="68" t="s">
+        <v>580</v>
+      </c>
+      <c r="C165" s="68" t="s">
+        <v>609</v>
+      </c>
+      <c r="D165" s="68" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="166" spans="2:4">
+      <c r="B166" s="68" t="s">
+        <v>591</v>
+      </c>
+      <c r="C166" s="68" t="s">
+        <v>592</v>
+      </c>
+      <c r="D166" s="68" t="s">
+        <v>611</v>
+      </c>
+    </row>
+    <row r="167" spans="2:4">
+      <c r="B167" s="68" t="s">
+        <v>591</v>
+      </c>
+      <c r="C167" s="68" t="s">
+        <v>612</v>
+      </c>
+      <c r="D167" s="68" t="s">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="168" spans="2:4">
+      <c r="B168" s="68" t="s">
+        <v>591</v>
+      </c>
+      <c r="C168" s="68" t="s">
+        <v>614</v>
+      </c>
+      <c r="D168" s="68" t="s">
+        <v>615</v>
+      </c>
+    </row>
+    <row r="169" spans="2:4">
+      <c r="B169" s="68" t="s">
+        <v>591</v>
+      </c>
+      <c r="C169" s="68" t="s">
+        <v>788</v>
+      </c>
+      <c r="D169" s="68" t="s">
+        <v>789</v>
+      </c>
+    </row>
+    <row r="170" spans="2:4">
+      <c r="B170" s="68" t="s">
+        <v>591</v>
+      </c>
+      <c r="C170" s="68" t="s">
+        <v>790</v>
+      </c>
+      <c r="D170" s="68" t="s">
+        <v>791</v>
+      </c>
+    </row>
+    <row r="171" spans="2:4">
+      <c r="B171" s="68" t="s">
+        <v>585</v>
+      </c>
+      <c r="C171" s="68" t="s">
+        <v>616</v>
+      </c>
+      <c r="D171" s="68" t="s">
+        <v>617</v>
+      </c>
+    </row>
+    <row r="172" spans="2:4">
+      <c r="B172" s="68" t="s">
+        <v>591</v>
+      </c>
+      <c r="C172" s="68" t="s">
+        <v>618</v>
+      </c>
+      <c r="D172" s="68" t="s">
+        <v>619</v>
+      </c>
+    </row>
+    <row r="173" spans="2:4">
+      <c r="B173" s="68" t="s">
+        <v>591</v>
+      </c>
+      <c r="C173" s="68" t="s">
+        <v>643</v>
+      </c>
+      <c r="D173" s="68" t="s">
+        <v>644</v>
+      </c>
+    </row>
+    <row r="174" spans="2:4">
+      <c r="B174" s="68" t="s">
+        <v>591</v>
+      </c>
+      <c r="C174" s="68" t="s">
+        <v>645</v>
+      </c>
+      <c r="D174" s="68" t="s">
+        <v>646</v>
+      </c>
+    </row>
+    <row r="175" spans="2:4">
+      <c r="B175" s="68" t="s">
+        <v>591</v>
+      </c>
+      <c r="C175" s="68" t="s">
+        <v>647</v>
+      </c>
+      <c r="D175" s="68" t="s">
+        <v>648</v>
+      </c>
+    </row>
+    <row r="176" spans="2:4">
+      <c r="B176" s="68" t="s">
+        <v>580</v>
+      </c>
+      <c r="C176" s="68" t="s">
+        <v>649</v>
+      </c>
+      <c r="D176" s="68" t="s">
+        <v>650</v>
+      </c>
+    </row>
+    <row r="177" spans="2:4">
+      <c r="B177" s="68" t="s">
+        <v>580</v>
+      </c>
+      <c r="C177" s="68" t="s">
+        <v>651</v>
+      </c>
+      <c r="D177" s="68" t="s">
+        <v>652</v>
+      </c>
+    </row>
+    <row r="178" spans="2:4">
+      <c r="B178" s="68" t="s">
+        <v>591</v>
+      </c>
+      <c r="C178" s="68" t="s">
+        <v>653</v>
+      </c>
+      <c r="D178" s="68" t="s">
+        <v>654</v>
+      </c>
+    </row>
+    <row r="179" spans="2:4">
+      <c r="B179" s="68" t="s">
+        <v>585</v>
+      </c>
+      <c r="C179" s="68" t="s">
+        <v>171</v>
+      </c>
+      <c r="D179" s="68" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="180" spans="2:4">
+      <c r="B180" s="68" t="s">
+        <v>580</v>
+      </c>
+      <c r="C180" s="68" t="s">
+        <v>190</v>
+      </c>
+      <c r="D180" s="68" t="s">
+        <v>621</v>
+      </c>
+    </row>
+    <row r="181" spans="2:4">
+      <c r="B181" s="68" t="s">
+        <v>622</v>
+      </c>
+      <c r="C181" s="68" t="s">
+        <v>623</v>
+      </c>
+      <c r="D181" s="68" t="s">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="182" spans="2:4">
+      <c r="B182" s="68" t="s">
+        <v>622</v>
+      </c>
+      <c r="C182" s="68" t="s">
+        <v>625</v>
+      </c>
+      <c r="D182" s="68" t="s">
+        <v>626</v>
+      </c>
+    </row>
+    <row r="183" spans="2:4">
+      <c r="B183" s="68" t="s">
+        <v>580</v>
+      </c>
+      <c r="C183" s="68" t="s">
+        <v>655</v>
+      </c>
+      <c r="D183" s="68" t="s">
+        <v>656</v>
+      </c>
+    </row>
+    <row r="184" spans="2:4">
+      <c r="B184" s="68" t="s">
+        <v>580</v>
+      </c>
+      <c r="C184" s="68" t="s">
+        <v>657</v>
+      </c>
+      <c r="D184" s="68" t="s">
+        <v>658</v>
+      </c>
+    </row>
+    <row r="185" spans="2:4">
+      <c r="B185" s="68" t="s">
+        <v>580</v>
+      </c>
+      <c r="C185" s="68" t="s">
+        <v>659</v>
+      </c>
+      <c r="D185" s="68" t="s">
+        <v>660</v>
+      </c>
+    </row>
+    <row r="186" spans="2:4">
+      <c r="B186" s="68" t="s">
+        <v>583</v>
+      </c>
+      <c r="C186" s="68" t="s">
+        <v>661</v>
+      </c>
+      <c r="D186" s="68" t="s">
+        <v>662</v>
+      </c>
+    </row>
+    <row r="187" spans="2:4">
+      <c r="B187" s="68" t="s">
+        <v>583</v>
+      </c>
+      <c r="C187" s="68" t="s">
+        <v>663</v>
+      </c>
+      <c r="D187" s="68" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="188" spans="2:4">
+      <c r="B188" s="68" t="s">
+        <v>583</v>
+      </c>
+      <c r="C188" s="68" t="s">
+        <v>665</v>
+      </c>
+      <c r="D188" s="68" t="s">
+        <v>666</v>
+      </c>
+    </row>
+    <row r="189" spans="2:4">
+      <c r="B189" s="68" t="s">
+        <v>585</v>
+      </c>
+      <c r="C189" s="68" t="s">
+        <v>667</v>
+      </c>
+      <c r="D189" s="68" t="s">
+        <v>668</v>
+      </c>
+    </row>
+    <row r="190" spans="2:4">
+      <c r="B190" s="68" t="s">
+        <v>585</v>
+      </c>
+      <c r="C190" s="68" t="s">
+        <v>669</v>
+      </c>
+      <c r="D190" s="68" t="s">
+        <v>670</v>
+      </c>
+    </row>
+    <row r="191" spans="2:4">
+      <c r="B191" s="68" t="s">
+        <v>585</v>
+      </c>
+      <c r="C191" s="68" t="s">
+        <v>671</v>
+      </c>
+      <c r="D191" s="68" t="s">
+        <v>672</v>
+      </c>
+    </row>
+    <row r="192" spans="2:4">
+      <c r="B192" s="68" t="s">
+        <v>585</v>
+      </c>
+      <c r="C192" s="68" t="s">
+        <v>673</v>
+      </c>
+      <c r="D192" s="68" t="s">
+        <v>674</v>
+      </c>
+    </row>
+    <row r="193" spans="2:4">
+      <c r="B193" s="68" t="s">
+        <v>583</v>
+      </c>
+      <c r="C193" s="68" t="s">
+        <v>675</v>
+      </c>
+      <c r="D193" s="68" t="s">
+        <v>676</v>
+      </c>
+    </row>
+    <row r="194" spans="2:4">
+      <c r="B194" s="68" t="s">
+        <v>583</v>
+      </c>
+      <c r="C194" s="68" t="s">
+        <v>677</v>
+      </c>
+      <c r="D194" s="68" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="195" spans="2:4">
+      <c r="B195" s="68" t="s">
+        <v>583</v>
+      </c>
+      <c r="C195" s="68" t="s">
+        <v>792</v>
+      </c>
+      <c r="D195" s="68" t="s">
+        <v>793</v>
+      </c>
+    </row>
+    <row r="196" spans="2:4">
+      <c r="B196" s="68" t="s">
+        <v>583</v>
+      </c>
+      <c r="C196" s="68" t="s">
+        <v>794</v>
+      </c>
+      <c r="D196" s="68" t="s">
+        <v>795</v>
+      </c>
+    </row>
+    <row r="197" spans="2:4">
+      <c r="B197" s="68" t="s">
+        <v>583</v>
+      </c>
+      <c r="C197" s="68" t="s">
+        <v>796</v>
+      </c>
+      <c r="D197" s="68" t="s">
+        <v>797</v>
+      </c>
+    </row>
+    <row r="198" spans="2:4">
+      <c r="B198" s="68" t="s">
+        <v>583</v>
+      </c>
+      <c r="C198" s="68" t="s">
+        <v>798</v>
+      </c>
+      <c r="D198" s="68" t="s">
+        <v>799</v>
+      </c>
+    </row>
+    <row r="199" spans="2:4">
+      <c r="B199" s="68" t="s">
+        <v>585</v>
+      </c>
+      <c r="C199" s="68" t="s">
+        <v>679</v>
+      </c>
+      <c r="D199" s="68" t="s">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="200" spans="2:4">
+      <c r="B200" s="68" t="s">
+        <v>585</v>
+      </c>
+      <c r="C200" s="68" t="s">
+        <v>681</v>
+      </c>
+      <c r="D200" s="68" t="s">
+        <v>801</v>
+      </c>
+    </row>
+    <row r="201" spans="2:4">
+      <c r="B201" s="68" t="s">
+        <v>585</v>
+      </c>
+      <c r="C201" s="68" t="s">
+        <v>683</v>
+      </c>
+      <c r="D201" s="68" t="s">
+        <v>802</v>
+      </c>
+    </row>
+    <row r="202" spans="2:4">
+      <c r="B202" s="68" t="s">
+        <v>585</v>
+      </c>
+      <c r="C202" s="68" t="s">
+        <v>685</v>
+      </c>
+      <c r="D202" s="68" t="s">
+        <v>803</v>
+      </c>
+    </row>
+    <row r="203" spans="2:4">
+      <c r="B203" s="68" t="s">
+        <v>583</v>
+      </c>
+      <c r="C203" s="68" t="s">
+        <v>687</v>
+      </c>
+      <c r="D203" s="68" t="s">
+        <v>688</v>
+      </c>
+    </row>
+    <row r="204" spans="2:4">
+      <c r="B204" s="68" t="s">
+        <v>583</v>
+      </c>
+      <c r="C204" s="68" t="s">
+        <v>689</v>
+      </c>
+      <c r="D204" s="68" t="s">
+        <v>690</v>
+      </c>
+    </row>
+    <row r="205" spans="2:4">
+      <c r="B205" s="68" t="s">
+        <v>585</v>
+      </c>
+      <c r="C205" s="68" t="s">
+        <v>691</v>
+      </c>
+      <c r="D205" s="68" t="s">
+        <v>692</v>
+      </c>
+    </row>
+    <row r="206" spans="2:4">
+      <c r="B206" s="68" t="s">
+        <v>585</v>
+      </c>
+      <c r="C206" s="68" t="s">
+        <v>693</v>
+      </c>
+      <c r="D206" s="68" t="s">
+        <v>694</v>
+      </c>
+    </row>
+    <row r="207" spans="2:4">
+      <c r="B207" s="68" t="s">
+        <v>585</v>
+      </c>
+      <c r="C207" s="68" t="s">
+        <v>695</v>
+      </c>
+      <c r="D207" s="68" t="s">
+        <v>696</v>
+      </c>
+    </row>
+    <row r="208" spans="2:4">
+      <c r="B208" s="68" t="s">
+        <v>585</v>
+      </c>
+      <c r="C208" s="68" t="s">
+        <v>697</v>
+      </c>
+      <c r="D208" s="68" t="s">
+        <v>698</v>
+      </c>
+    </row>
+    <row r="209" spans="2:4">
+      <c r="B209" s="68" t="s">
+        <v>585</v>
+      </c>
+      <c r="C209" s="68" t="s">
+        <v>699</v>
+      </c>
+      <c r="D209" s="68" t="s">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="210" spans="2:4">
+      <c r="B210" s="68" t="s">
+        <v>585</v>
+      </c>
+      <c r="C210" s="68" t="s">
+        <v>804</v>
+      </c>
+      <c r="D210" s="68" t="s">
+        <v>805</v>
+      </c>
+    </row>
+    <row r="211" spans="2:4">
+      <c r="B211" s="68" t="s">
+        <v>585</v>
+      </c>
+      <c r="C211" s="68" t="s">
+        <v>806</v>
+      </c>
+      <c r="D211" s="68" t="s">
+        <v>807</v>
+      </c>
+    </row>
+    <row r="212" spans="2:4">
+      <c r="B212" s="68" t="s">
+        <v>585</v>
+      </c>
+      <c r="C212" s="68" t="s">
+        <v>808</v>
+      </c>
+      <c r="D212" s="68" t="s">
+        <v>809</v>
+      </c>
+    </row>
+    <row r="213" spans="2:4">
+      <c r="B213" s="68" t="s">
+        <v>585</v>
+      </c>
+      <c r="C213" s="68" t="s">
+        <v>810</v>
+      </c>
+      <c r="D213" s="68" t="s">
+        <v>811</v>
+      </c>
+    </row>
+    <row r="214" spans="2:4">
+      <c r="B214" s="68" t="s">
+        <v>585</v>
+      </c>
+      <c r="C214" s="68" t="s">
+        <v>812</v>
+      </c>
+      <c r="D214" s="68" t="s">
+        <v>813</v>
+      </c>
+    </row>
+    <row r="215" spans="2:4">
+      <c r="B215" s="68" t="s">
+        <v>585</v>
+      </c>
+      <c r="C215" s="68" t="s">
+        <v>814</v>
+      </c>
+      <c r="D215" s="68" t="s">
+        <v>815</v>
+      </c>
+    </row>
+    <row r="216" spans="2:4">
+      <c r="B216" s="68" t="s">
+        <v>585</v>
+      </c>
+      <c r="C216" s="68" t="s">
+        <v>816</v>
+      </c>
+      <c r="D216" s="68" t="s">
+        <v>817</v>
+      </c>
+    </row>
+    <row r="217" spans="2:4">
+      <c r="B217" s="68" t="s">
+        <v>585</v>
+      </c>
+      <c r="C217" s="68" t="s">
+        <v>818</v>
+      </c>
+      <c r="D217" s="68" t="s">
+        <v>819</v>
+      </c>
+    </row>
+    <row r="218" spans="2:4">
+      <c r="B218" s="68" t="s">
+        <v>585</v>
+      </c>
+      <c r="C218" s="68" t="s">
+        <v>820</v>
+      </c>
+      <c r="D218" s="68" t="s">
+        <v>821</v>
+      </c>
+    </row>
+    <row r="219" spans="2:4">
+      <c r="B219" s="68" t="s">
+        <v>585</v>
+      </c>
+      <c r="C219" s="68" t="s">
+        <v>629</v>
+      </c>
+      <c r="D219" s="68" t="s">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="220" spans="2:4">
+      <c r="B220" s="68" t="s">
+        <v>585</v>
+      </c>
+      <c r="C220" s="68" t="s">
+        <v>705</v>
+      </c>
+      <c r="D220" s="68" t="s">
+        <v>822</v>
+      </c>
+    </row>
+    <row r="221" spans="2:4">
+      <c r="B221" s="68" t="s">
+        <v>585</v>
+      </c>
+      <c r="C221" s="68" t="s">
+        <v>707</v>
+      </c>
+      <c r="D221" s="68" t="s">
+        <v>708</v>
+      </c>
+    </row>
+    <row r="222" spans="2:4">
+      <c r="B222" s="68" t="s">
+        <v>585</v>
+      </c>
+      <c r="C222" s="68" t="s">
+        <v>709</v>
+      </c>
+      <c r="D222" s="68" t="s">
+        <v>710</v>
+      </c>
+    </row>
+    <row r="223" spans="2:4">
+      <c r="B223" s="68" t="s">
+        <v>585</v>
+      </c>
+      <c r="C223" s="68" t="s">
+        <v>711</v>
+      </c>
+      <c r="D223" s="68" t="s">
+        <v>712</v>
+      </c>
+    </row>
+    <row r="224" spans="2:4">
+      <c r="B224" s="68" t="s">
+        <v>585</v>
+      </c>
+      <c r="C224" s="68" t="s">
+        <v>713</v>
+      </c>
+      <c r="D224" s="68" t="s">
+        <v>714</v>
+      </c>
+    </row>
+    <row r="225" spans="2:4">
+      <c r="B225" s="68" t="s">
+        <v>585</v>
+      </c>
+      <c r="C225" s="68" t="s">
+        <v>823</v>
+      </c>
+      <c r="D225" s="68" t="s">
+        <v>824</v>
+      </c>
+    </row>
+    <row r="226" spans="2:4">
+      <c r="B226" s="68" t="s">
+        <v>585</v>
+      </c>
+      <c r="C226" s="68" t="s">
+        <v>825</v>
+      </c>
+      <c r="D226" s="68" t="s">
+        <v>826</v>
+      </c>
+    </row>
+    <row r="227" spans="2:4">
+      <c r="B227" s="68" t="s">
+        <v>585</v>
+      </c>
+      <c r="C227" s="68" t="s">
+        <v>827</v>
+      </c>
+      <c r="D227" s="68" t="s">
+        <v>828</v>
+      </c>
+    </row>
+    <row r="228" spans="2:4">
+      <c r="B228" s="68" t="s">
+        <v>585</v>
+      </c>
+      <c r="C228" s="68" t="s">
+        <v>829</v>
+      </c>
+      <c r="D228" s="68" t="s">
+        <v>830</v>
+      </c>
+    </row>
+    <row r="229" spans="2:4">
+      <c r="B229" s="68" t="s">
+        <v>585</v>
+      </c>
+      <c r="C229" s="68" t="s">
+        <v>831</v>
+      </c>
+      <c r="D229" s="68" t="s">
+        <v>832</v>
+      </c>
+    </row>
+    <row r="230" spans="2:4">
+      <c r="B230" s="68" t="s">
+        <v>585</v>
+      </c>
+      <c r="C230" s="68" t="s">
+        <v>833</v>
+      </c>
+      <c r="D230" s="68" t="s">
+        <v>834</v>
+      </c>
+    </row>
+    <row r="231" spans="2:4">
+      <c r="B231" s="68" t="s">
+        <v>585</v>
+      </c>
+      <c r="C231" s="68" t="s">
+        <v>835</v>
+      </c>
+      <c r="D231" s="68" t="s">
+        <v>836</v>
+      </c>
+    </row>
+    <row r="232" spans="2:4">
+      <c r="B232" s="68" t="s">
+        <v>585</v>
+      </c>
+      <c r="C232" s="68" t="s">
+        <v>837</v>
+      </c>
+      <c r="D232" s="68" t="s">
+        <v>838</v>
+      </c>
+    </row>
+    <row r="233" spans="2:4">
+      <c r="B233" s="68" t="s">
+        <v>585</v>
+      </c>
+      <c r="C233" s="68" t="s">
+        <v>839</v>
+      </c>
+      <c r="D233" s="68" t="s">
+        <v>840</v>
+      </c>
+    </row>
+    <row r="234" spans="2:4">
+      <c r="B234" s="68" t="s">
+        <v>585</v>
+      </c>
+      <c r="C234" s="68" t="s">
+        <v>701</v>
+      </c>
+      <c r="D234" s="68" t="s">
+        <v>702</v>
+      </c>
+    </row>
+    <row r="235" spans="2:4">
+      <c r="B235" s="68" t="s">
+        <v>585</v>
+      </c>
+      <c r="C235" s="68" t="s">
+        <v>841</v>
+      </c>
+      <c r="D235" s="68" t="s">
+        <v>842</v>
+      </c>
+    </row>
+    <row r="236" spans="2:4">
+      <c r="B236" s="68" t="s">
+        <v>585</v>
+      </c>
+      <c r="C236" s="68" t="s">
+        <v>843</v>
+      </c>
+      <c r="D236" s="68" t="s">
+        <v>844</v>
+      </c>
+    </row>
+    <row r="237" spans="2:4">
+      <c r="B237" s="68" t="s">
+        <v>585</v>
+      </c>
+      <c r="C237" s="68" t="s">
+        <v>845</v>
+      </c>
+      <c r="D237" s="68" t="s">
+        <v>846</v>
+      </c>
+    </row>
+    <row r="238" spans="2:4">
+      <c r="B238" s="68" t="s">
+        <v>585</v>
+      </c>
+      <c r="C238" s="68" t="s">
+        <v>847</v>
+      </c>
+      <c r="D238" s="68" t="s">
+        <v>848</v>
+      </c>
+    </row>
+    <row r="239" spans="2:4">
+      <c r="B239" s="68" t="s">
+        <v>580</v>
+      </c>
+      <c r="C239" s="68" t="s">
+        <v>731</v>
+      </c>
+      <c r="D239" s="68" t="s">
+        <v>732</v>
+      </c>
+    </row>
+    <row r="240" spans="2:4">
+      <c r="B240" s="68" t="s">
+        <v>580</v>
+      </c>
+      <c r="C240" s="68" t="s">
+        <v>542</v>
+      </c>
+      <c r="D240" s="68" t="s">
+        <v>849</v>
+      </c>
+    </row>
+    <row r="241" spans="2:4">
+      <c r="B241" s="68" t="s">
+        <v>580</v>
+      </c>
+      <c r="C241" s="68" t="s">
+        <v>734</v>
+      </c>
+      <c r="D241" s="68" t="s">
+        <v>850</v>
+      </c>
+    </row>
+    <row r="242" spans="2:4">
+      <c r="B242" s="68" t="s">
+        <v>580</v>
+      </c>
+      <c r="C242" s="68" t="s">
+        <v>736</v>
+      </c>
+      <c r="D242" s="68" t="s">
+        <v>851</v>
+      </c>
+    </row>
+    <row r="243" spans="2:4">
+      <c r="B243" s="68" t="s">
+        <v>580</v>
+      </c>
+      <c r="C243" s="68" t="s">
+        <v>852</v>
+      </c>
+      <c r="D243" s="68" t="s">
+        <v>853</v>
+      </c>
+    </row>
+    <row r="244" spans="2:4">
+      <c r="B244" s="68" t="s">
+        <v>580</v>
+      </c>
+      <c r="C244" s="68" t="s">
+        <v>854</v>
+      </c>
+      <c r="D244" s="68" t="s">
+        <v>855</v>
+      </c>
+    </row>
+    <row r="245" spans="2:4">
+      <c r="B245" s="68" t="s">
+        <v>585</v>
+      </c>
+      <c r="C245" s="68" t="s">
+        <v>856</v>
+      </c>
+      <c r="D245" s="68" t="s">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="246" spans="2:4">
+      <c r="B246" s="68" t="s">
+        <v>583</v>
+      </c>
+      <c r="C246" s="68" t="s">
+        <v>858</v>
+      </c>
+      <c r="D246" s="68" t="s">
+        <v>859</v>
+      </c>
+    </row>
+    <row r="247" spans="2:4">
+      <c r="B247" s="68" t="s">
+        <v>583</v>
+      </c>
+      <c r="C247" s="68" t="s">
+        <v>860</v>
+      </c>
+      <c r="D247" s="68" t="s">
+        <v>861</v>
+      </c>
+    </row>
+    <row r="248" spans="2:4">
+      <c r="B248" s="68" t="s">
+        <v>580</v>
+      </c>
+      <c r="C248" s="68" t="s">
+        <v>715</v>
+      </c>
+      <c r="D248" s="68" t="s">
+        <v>716</v>
+      </c>
+    </row>
+    <row r="249" spans="2:4">
+      <c r="B249" s="68" t="s">
+        <v>580</v>
+      </c>
+      <c r="C249" s="68" t="s">
+        <v>862</v>
+      </c>
+      <c r="D249" s="68" t="s">
+        <v>863</v>
+      </c>
+    </row>
+    <row r="250" spans="2:4">
+      <c r="B250" s="68" t="s">
+        <v>580</v>
+      </c>
+      <c r="C250" s="68" t="s">
+        <v>717</v>
+      </c>
+      <c r="D250" s="68" t="s">
+        <v>718</v>
+      </c>
+    </row>
+    <row r="251" spans="2:4">
+      <c r="B251" s="68" t="s">
+        <v>580</v>
+      </c>
+      <c r="C251" s="68" t="s">
+        <v>719</v>
+      </c>
+      <c r="D251" s="68" t="s">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="252" spans="2:4">
+      <c r="B252" s="68" t="s">
+        <v>580</v>
+      </c>
+      <c r="C252" s="68" t="s">
+        <v>721</v>
+      </c>
+      <c r="D252" s="68" t="s">
+        <v>722</v>
+      </c>
+    </row>
+    <row r="253" spans="2:4">
+      <c r="B253" s="68" t="s">
+        <v>580</v>
+      </c>
+      <c r="C253" s="68" t="s">
+        <v>723</v>
+      </c>
+      <c r="D253" s="68" t="s">
+        <v>724</v>
+      </c>
+    </row>
+    <row r="254" spans="2:4">
+      <c r="B254" s="68" t="s">
+        <v>580</v>
+      </c>
+      <c r="C254" s="68" t="s">
+        <v>864</v>
+      </c>
+      <c r="D254" s="68" t="s">
+        <v>865</v>
+      </c>
+    </row>
+    <row r="255" spans="2:4">
+      <c r="B255" s="68" t="s">
+        <v>580</v>
+      </c>
+      <c r="C255" s="68" t="s">
+        <v>866</v>
+      </c>
+      <c r="D255" s="68" t="s">
+        <v>867</v>
+      </c>
+    </row>
+    <row r="256" spans="2:4">
+      <c r="B256" s="68" t="s">
+        <v>580</v>
+      </c>
+      <c r="C256" s="68" t="s">
+        <v>868</v>
+      </c>
+      <c r="D256" s="68" t="s">
+        <v>869</v>
+      </c>
+    </row>
+    <row r="257" spans="2:4">
+      <c r="B257" s="68" t="s">
+        <v>580</v>
+      </c>
+      <c r="C257" s="68" t="s">
+        <v>870</v>
+      </c>
+      <c r="D257" s="68" t="s">
+        <v>871</v>
+      </c>
+    </row>
+    <row r="258" spans="2:4">
+      <c r="B258" s="68" t="s">
+        <v>580</v>
+      </c>
+      <c r="C258" s="68" t="s">
+        <v>576</v>
+      </c>
+      <c r="D258" s="68" t="s">
+        <v>872</v>
+      </c>
+    </row>
+    <row r="259" spans="2:4">
+      <c r="B259" s="68" t="s">
+        <v>580</v>
+      </c>
+      <c r="C259" s="68" t="s">
+        <v>873</v>
+      </c>
+      <c r="D259" s="68" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="260" spans="2:4">
+      <c r="B260" s="68" t="s">
+        <v>580</v>
+      </c>
+      <c r="C260" s="68" t="s">
+        <v>535</v>
+      </c>
+      <c r="D260" s="68" t="s">
+        <v>875</v>
+      </c>
+    </row>
+    <row r="261" spans="2:4">
+      <c r="B261" s="68" t="s">
+        <v>580</v>
+      </c>
+      <c r="C261" s="68" t="s">
+        <v>760</v>
+      </c>
+      <c r="D261" s="68" t="s">
+        <v>876</v>
+      </c>
+    </row>
+    <row r="262" spans="2:4">
+      <c r="B262" s="68" t="s">
+        <v>580</v>
+      </c>
+      <c r="C262" s="68" t="s">
+        <v>877</v>
+      </c>
+      <c r="D262" s="68" t="s">
+        <v>878</v>
+      </c>
+    </row>
+    <row r="263" spans="2:4">
+      <c r="B263" s="68" t="s">
+        <v>580</v>
+      </c>
+      <c r="C263" s="68" t="s">
+        <v>879</v>
+      </c>
+      <c r="D263" s="68" t="s">
+        <v>880</v>
+      </c>
+    </row>
+    <row r="264" spans="2:4">
+      <c r="B264" s="68" t="s">
+        <v>580</v>
+      </c>
+      <c r="C264" s="68" t="s">
+        <v>881</v>
+      </c>
+      <c r="D264" s="68" t="s">
+        <v>882</v>
+      </c>
+    </row>
+    <row r="265" spans="2:4">
+      <c r="B265" s="68" t="s">
+        <v>580</v>
+      </c>
+      <c r="C265" s="68" t="s">
+        <v>883</v>
+      </c>
+      <c r="D265" s="68" t="s">
+        <v>884</v>
+      </c>
+    </row>
+    <row r="266" spans="2:4">
+      <c r="B266" s="68" t="s">
+        <v>580</v>
+      </c>
+      <c r="C266" s="68" t="s">
+        <v>885</v>
+      </c>
+      <c r="D266" s="68" t="s">
+        <v>886</v>
+      </c>
+    </row>
+    <row r="267" spans="2:4">
+      <c r="B267" s="68" t="s">
+        <v>585</v>
+      </c>
+      <c r="C267" s="68" t="s">
+        <v>627</v>
+      </c>
+      <c r="D267" s="68" t="s">
+        <v>628</v>
+      </c>
+    </row>
+    <row r="268" spans="2:4">
+      <c r="B268" s="68" t="s">
+        <v>580</v>
+      </c>
+      <c r="C268" s="68" t="s">
+        <v>470</v>
+      </c>
+      <c r="D268" s="68" t="s">
+        <v>725</v>
+      </c>
+    </row>
+    <row r="269" spans="2:4">
+      <c r="B269" s="68" t="s">
+        <v>580</v>
+      </c>
+      <c r="C269" s="68" t="s">
+        <v>726</v>
+      </c>
+      <c r="D269" s="68" t="s">
+        <v>727</v>
+      </c>
+    </row>
+    <row r="270" spans="2:4">
+      <c r="B270" s="68" t="s">
+        <v>585</v>
+      </c>
+      <c r="C270" s="68" t="s">
+        <v>463</v>
+      </c>
+      <c r="D270" s="68" t="s">
+        <v>728</v>
+      </c>
+    </row>
+    <row r="271" spans="2:4">
+      <c r="B271" s="68" t="s">
+        <v>580</v>
+      </c>
+      <c r="C271" s="68" t="s">
+        <v>729</v>
+      </c>
+      <c r="D271" s="68" t="s">
+        <v>730</v>
+      </c>
+    </row>
+    <row r="272" spans="2:4">
+      <c r="B272" s="68" t="s">
+        <v>580</v>
+      </c>
+      <c r="C272" s="68" t="s">
+        <v>887</v>
+      </c>
+      <c r="D272" s="68" t="s">
+        <v>888</v>
+      </c>
+    </row>
+    <row r="273" spans="2:4">
+      <c r="B273" s="68" t="s">
+        <v>580</v>
+      </c>
+      <c r="C273" s="68" t="s">
+        <v>631</v>
+      </c>
+      <c r="D273" s="68" t="s">
+        <v>632</v>
+      </c>
+    </row>
+    <row r="274" spans="2:4">
+      <c r="B274" s="68" t="s">
+        <v>580</v>
+      </c>
+      <c r="C274" s="68" t="s">
+        <v>889</v>
+      </c>
+      <c r="D274" s="68" t="s">
+        <v>890</v>
+      </c>
+    </row>
+    <row r="275" spans="2:4">
+      <c r="B275" s="68" t="s">
+        <v>583</v>
+      </c>
+      <c r="C275" s="68" t="s">
+        <v>633</v>
+      </c>
+      <c r="D275" s="68" t="s">
+        <v>634</v>
+      </c>
+    </row>
+    <row r="276" spans="2:4">
+      <c r="B276" s="68" t="s">
+        <v>583</v>
+      </c>
+      <c r="C276" s="68" t="s">
+        <v>635</v>
+      </c>
+      <c r="D276" s="68" t="s">
+        <v>636</v>
+      </c>
+    </row>
+    <row r="277" spans="2:4">
+      <c r="B277" s="68" t="s">
+        <v>585</v>
+      </c>
+      <c r="C277" s="68" t="s">
+        <v>738</v>
+      </c>
+      <c r="D277" s="68" t="s">
+        <v>739</v>
+      </c>
+    </row>
+    <row r="278" spans="2:4">
+      <c r="B278" s="68" t="s">
+        <v>585</v>
+      </c>
+      <c r="C278" s="68" t="s">
+        <v>740</v>
+      </c>
+      <c r="D278" s="68" t="s">
+        <v>741</v>
+      </c>
+    </row>
+    <row r="279" spans="2:4">
+      <c r="B279" s="68" t="s">
+        <v>585</v>
+      </c>
+      <c r="C279" s="68" t="s">
+        <v>742</v>
+      </c>
+      <c r="D279" s="68" t="s">
+        <v>743</v>
+      </c>
+    </row>
+    <row r="280" spans="2:4">
+      <c r="B280" s="68" t="s">
+        <v>585</v>
+      </c>
+      <c r="C280" s="68" t="s">
+        <v>744</v>
+      </c>
+      <c r="D280" s="68" t="s">
+        <v>745</v>
+      </c>
+    </row>
+    <row r="281" spans="2:4">
+      <c r="B281" s="68" t="s">
+        <v>585</v>
+      </c>
+      <c r="C281" s="68" t="s">
+        <v>746</v>
+      </c>
+      <c r="D281" s="68" t="s">
+        <v>747</v>
+      </c>
+    </row>
+    <row r="282" spans="2:4">
+      <c r="B282" s="68" t="s">
+        <v>585</v>
+      </c>
+      <c r="C282" s="68" t="s">
+        <v>891</v>
+      </c>
+      <c r="D282" s="68" t="s">
+        <v>892</v>
+      </c>
+    </row>
+    <row r="283" spans="2:4">
+      <c r="B283" s="68" t="s">
+        <v>585</v>
+      </c>
+      <c r="C283" s="68" t="s">
+        <v>215</v>
+      </c>
+      <c r="D283" s="68" t="s">
+        <v>893</v>
+      </c>
+    </row>
+    <row r="284" spans="2:4">
+      <c r="B284" s="68" t="s">
+        <v>585</v>
+      </c>
+      <c r="C284" s="68" t="s">
+        <v>894</v>
+      </c>
+      <c r="D284" s="68" t="s">
+        <v>895</v>
+      </c>
+    </row>
+    <row r="285" spans="2:4">
+      <c r="B285" s="68" t="s">
+        <v>585</v>
+      </c>
+      <c r="C285" s="68" t="s">
+        <v>896</v>
+      </c>
+      <c r="D285" s="68" t="s">
+        <v>897</v>
+      </c>
+    </row>
+    <row r="286" spans="2:4">
+      <c r="B286" s="68" t="s">
+        <v>583</v>
+      </c>
+      <c r="C286" s="68" t="s">
+        <v>898</v>
+      </c>
+      <c r="D286" s="68" t="s">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="287" spans="2:4">
+      <c r="B287" s="68" t="s">
+        <v>583</v>
+      </c>
+      <c r="C287" s="68" t="s">
+        <v>900</v>
+      </c>
+      <c r="D287" s="68" t="s">
+        <v>901</v>
+      </c>
+    </row>
+    <row r="288" spans="2:4">
+      <c r="B288" s="68" t="s">
+        <v>583</v>
+      </c>
+      <c r="C288" s="68" t="s">
+        <v>902</v>
+      </c>
+      <c r="D288" s="68" t="s">
+        <v>903</v>
+      </c>
+    </row>
+    <row r="289" spans="2:4">
+      <c r="B289" s="68" t="s">
+        <v>585</v>
+      </c>
+      <c r="C289" s="68" t="s">
+        <v>748</v>
+      </c>
+      <c r="D289" s="68" t="s">
+        <v>749</v>
+      </c>
+    </row>
+    <row r="290" spans="2:4">
+      <c r="B290" s="68" t="s">
+        <v>585</v>
+      </c>
+      <c r="C290" s="68" t="s">
+        <v>750</v>
+      </c>
+      <c r="D290" s="68" t="s">
+        <v>751</v>
+      </c>
+    </row>
+    <row r="291" spans="2:4">
+      <c r="B291" s="68" t="s">
+        <v>585</v>
+      </c>
+      <c r="C291" s="68" t="s">
+        <v>904</v>
+      </c>
+      <c r="D291" s="68" t="s">
+        <v>905</v>
+      </c>
+    </row>
+    <row r="292" spans="2:4">
+      <c r="B292" s="68" t="s">
+        <v>585</v>
+      </c>
+      <c r="C292" s="68" t="s">
+        <v>755</v>
+      </c>
+      <c r="D292" s="68" t="s">
+        <v>756</v>
+      </c>
+    </row>
+    <row r="293" spans="2:4">
+      <c r="B293" s="68" t="s">
+        <v>585</v>
+      </c>
+      <c r="C293" s="68" t="s">
+        <v>757</v>
+      </c>
+      <c r="D293" s="68" t="s">
+        <v>758</v>
+      </c>
+    </row>
+    <row r="294" spans="2:4">
+      <c r="B294" s="68" t="s">
+        <v>585</v>
+      </c>
+      <c r="C294" s="68" t="s">
+        <v>906</v>
+      </c>
+      <c r="D294" s="68" t="s">
+        <v>907</v>
+      </c>
+    </row>
+    <row r="295" spans="2:4">
+      <c r="B295" s="68" t="s">
+        <v>585</v>
+      </c>
+      <c r="C295" s="68" t="s">
+        <v>908</v>
+      </c>
+      <c r="D295" s="68" t="s">
+        <v>909</v>
+      </c>
+    </row>
+    <row r="296" spans="2:4">
+      <c r="B296" s="68" t="s">
+        <v>585</v>
+      </c>
+      <c r="C296" s="68" t="s">
+        <v>910</v>
+      </c>
+      <c r="D296" s="68" t="s">
+        <v>911</v>
+      </c>
+    </row>
+    <row r="297" spans="2:4">
+      <c r="B297" s="68" t="s">
+        <v>585</v>
+      </c>
+      <c r="C297" s="68" t="s">
+        <v>573</v>
+      </c>
+      <c r="D297" s="68" t="s">
+        <v>912</v>
+      </c>
+    </row>
+    <row r="298" spans="2:4">
+      <c r="B298" s="68" t="s">
+        <v>585</v>
+      </c>
+      <c r="C298" s="68" t="s">
+        <v>913</v>
+      </c>
+      <c r="D298" s="68" t="s">
+        <v>914</v>
+      </c>
+    </row>
+    <row r="299" spans="2:4">
+      <c r="B299" s="68" t="s">
+        <v>585</v>
+      </c>
+      <c r="C299" s="68" t="s">
+        <v>915</v>
+      </c>
+      <c r="D299" s="68" t="s">
+        <v>916</v>
+      </c>
+    </row>
+    <row r="300" spans="2:4">
+      <c r="B300" s="68" t="s">
+        <v>585</v>
+      </c>
+      <c r="C300" s="68" t="s">
+        <v>917</v>
+      </c>
+      <c r="D300" s="68" t="s">
+        <v>918</v>
+      </c>
+    </row>
+    <row r="301" spans="2:4">
+      <c r="B301" s="68" t="s">
+        <v>585</v>
+      </c>
+      <c r="C301" s="68" t="s">
+        <v>919</v>
+      </c>
+      <c r="D301" s="68" t="s">
+        <v>920</v>
+      </c>
+    </row>
+    <row r="302" spans="2:4">
+      <c r="B302" s="68" t="s">
+        <v>585</v>
+      </c>
+      <c r="C302" s="68" t="s">
+        <v>60</v>
+      </c>
+      <c r="D302" s="68" t="s">
+        <v>752</v>
+      </c>
+    </row>
+    <row r="303" spans="2:4">
+      <c r="B303" s="68" t="s">
+        <v>580</v>
+      </c>
+      <c r="C303" s="68" t="s">
+        <v>753</v>
+      </c>
+      <c r="D303" s="68" t="s">
+        <v>921</v>
+      </c>
+    </row>
+    <row r="304" spans="2:4">
+      <c r="B304" s="68" t="s">
+        <v>580</v>
+      </c>
+      <c r="C304" s="68" t="s">
+        <v>567</v>
+      </c>
+      <c r="D304" s="68" t="s">
+        <v>922</v>
+      </c>
+    </row>
+    <row r="305" spans="2:4">
+      <c r="B305" s="68" t="s">
+        <v>580</v>
+      </c>
+      <c r="C305" s="68" t="s">
+        <v>923</v>
+      </c>
+      <c r="D305" s="68" t="s">
+        <v>924</v>
+      </c>
+    </row>
+    <row r="306" spans="2:4">
+      <c r="B306" s="68" t="s">
+        <v>585</v>
+      </c>
+      <c r="C306" s="68" t="s">
+        <v>562</v>
+      </c>
+      <c r="D306" s="68" t="s">
+        <v>925</v>
+      </c>
+    </row>
+    <row r="307" spans="2:4">
+      <c r="B307" s="68" t="s">
+        <v>585</v>
+      </c>
+      <c r="C307" s="68" t="s">
+        <v>926</v>
+      </c>
+      <c r="D307" s="68" t="s">
+        <v>927</v>
+      </c>
+    </row>
+    <row r="308" spans="2:4">
+      <c r="B308" s="68" t="s">
+        <v>585</v>
+      </c>
+      <c r="C308" s="68" t="s">
+        <v>264</v>
+      </c>
+      <c r="D308" s="68" t="s">
+        <v>928</v>
+      </c>
+    </row>
+    <row r="309" spans="2:4">
+      <c r="B309" s="68" t="s">
+        <v>585</v>
+      </c>
+      <c r="C309" s="68" t="s">
+        <v>929</v>
+      </c>
+      <c r="D309" s="68" t="s">
+        <v>930</v>
+      </c>
+    </row>
+    <row r="310" spans="2:4">
+      <c r="B310" s="68" t="s">
+        <v>585</v>
+      </c>
+      <c r="C310" s="68" t="s">
+        <v>931</v>
+      </c>
+      <c r="D310" s="68" t="s">
+        <v>932</v>
+      </c>
+    </row>
+    <row r="311" spans="2:4">
+      <c r="B311" s="68" t="s">
+        <v>585</v>
+      </c>
+      <c r="C311" s="68" t="s">
+        <v>933</v>
+      </c>
+      <c r="D311" s="68" t="s">
+        <v>934</v>
+      </c>
+    </row>
+    <row r="312" spans="2:4">
+      <c r="B312" s="68" t="s">
+        <v>585</v>
+      </c>
+      <c r="C312" s="68" t="s">
+        <v>935</v>
+      </c>
+      <c r="D312" s="68" t="s">
+        <v>936</v>
+      </c>
+    </row>
+    <row r="313" spans="2:4">
+      <c r="B313" s="68" t="s">
+        <v>580</v>
+      </c>
+      <c r="C313" s="68" t="s">
+        <v>937</v>
+      </c>
+      <c r="D313" s="68" t="s">
+        <v>938</v>
+      </c>
+    </row>
+    <row r="314" spans="2:4">
+      <c r="B314" s="68" t="s">
+        <v>580</v>
+      </c>
+      <c r="C314" s="68" t="s">
+        <v>550</v>
+      </c>
+      <c r="D314" s="68" t="s">
+        <v>939</v>
+      </c>
+    </row>
+    <row r="315" spans="2:4">
+      <c r="B315" s="68" t="s">
+        <v>585</v>
+      </c>
+      <c r="C315" s="68" t="s">
+        <v>940</v>
+      </c>
+      <c r="D315" s="68" t="s">
+        <v>941</v>
+      </c>
+    </row>
+    <row r="316" spans="2:4">
+      <c r="B316" s="68" t="s">
+        <v>585</v>
+      </c>
+      <c r="C316" s="68" t="s">
+        <v>942</v>
+      </c>
+      <c r="D316" s="68" t="s">
+        <v>943</v>
+      </c>
+    </row>
+    <row r="317" spans="2:4">
+      <c r="B317" s="68" t="s">
+        <v>583</v>
+      </c>
+      <c r="C317" s="68" t="s">
+        <v>944</v>
+      </c>
+      <c r="D317" s="68" t="s">
+        <v>945</v>
+      </c>
+    </row>
+    <row r="318" spans="2:4">
+      <c r="B318" s="68" t="s">
+        <v>583</v>
+      </c>
+      <c r="C318" s="68" t="s">
+        <v>946</v>
+      </c>
+      <c r="D318" s="68" t="s">
+        <v>947</v>
+      </c>
+    </row>
+    <row r="319" spans="2:4">
+      <c r="B319" s="68" t="s">
+        <v>585</v>
+      </c>
+      <c r="C319" s="68" t="s">
+        <v>762</v>
+      </c>
+      <c r="D319" s="68" t="s">
+        <v>948</v>
+      </c>
+    </row>
+    <row r="320" spans="2:4">
+      <c r="B320" s="68" t="s">
+        <v>585</v>
+      </c>
+      <c r="C320" s="68" t="s">
+        <v>949</v>
+      </c>
+      <c r="D320" s="68" t="s">
+        <v>950</v>
+      </c>
+    </row>
+    <row r="321" spans="2:4">
+      <c r="B321" s="68" t="s">
+        <v>585</v>
+      </c>
+      <c r="C321" s="68" t="s">
+        <v>764</v>
+      </c>
+      <c r="D321" s="68" t="s">
+        <v>951</v>
+      </c>
+    </row>
+    <row r="322" spans="2:4">
+      <c r="B322" s="68" t="s">
+        <v>585</v>
+      </c>
+      <c r="C322" s="68" t="s">
+        <v>952</v>
+      </c>
+      <c r="D322" s="68" t="s">
+        <v>953</v>
+      </c>
+    </row>
+    <row r="323" spans="2:4">
+      <c r="B323" s="68" t="s">
+        <v>585</v>
+      </c>
+      <c r="C323" s="68" t="s">
+        <v>954</v>
+      </c>
+      <c r="D323" s="68" t="s">
+        <v>955</v>
+      </c>
+    </row>
+    <row r="324" spans="2:4">
+      <c r="B324" s="68" t="s">
+        <v>585</v>
+      </c>
+      <c r="C324" s="68" t="s">
+        <v>956</v>
+      </c>
+      <c r="D324" s="68" t="s">
+        <v>957</v>
+      </c>
+    </row>
+    <row r="325" spans="2:4">
+      <c r="B325" s="68" t="s">
+        <v>585</v>
+      </c>
+      <c r="C325" s="68" t="s">
+        <v>557</v>
+      </c>
+      <c r="D325" s="68" t="s">
+        <v>958</v>
+      </c>
+    </row>
+    <row r="326" spans="2:4">
+      <c r="B326" s="68" t="s">
+        <v>585</v>
+      </c>
+      <c r="C326" s="68" t="s">
+        <v>959</v>
+      </c>
+      <c r="D326" s="68" t="s">
+        <v>960</v>
+      </c>
+    </row>
+    <row r="327" spans="2:4">
+      <c r="B327" s="68" t="s">
+        <v>585</v>
+      </c>
+      <c r="C327" s="68" t="s">
+        <v>961</v>
+      </c>
+      <c r="D327" s="68" t="s">
+        <v>962</v>
+      </c>
+    </row>
+    <row r="328" spans="2:4">
+      <c r="B328" s="68" t="s">
+        <v>585</v>
+      </c>
+      <c r="C328" s="68" t="s">
+        <v>963</v>
+      </c>
+      <c r="D328" s="68" t="s">
+        <v>964</v>
+      </c>
+    </row>
+    <row r="329" spans="2:4">
+      <c r="B329" s="68" t="s">
+        <v>585</v>
+      </c>
+      <c r="C329" s="68" t="s">
+        <v>965</v>
+      </c>
+      <c r="D329" s="68" t="s">
+        <v>966</v>
+      </c>
+    </row>
+    <row r="330" spans="2:4">
+      <c r="B330" s="68" t="s">
+        <v>585</v>
+      </c>
+      <c r="C330" s="68" t="s">
+        <v>967</v>
+      </c>
+      <c r="D330" s="68" t="s">
+        <v>968</v>
+      </c>
+    </row>
+    <row r="331" spans="2:4">
+      <c r="B331" s="68" t="s">
+        <v>585</v>
+      </c>
+      <c r="C331" s="68" t="s">
+        <v>969</v>
+      </c>
+      <c r="D331" s="68" t="s">
+        <v>970</v>
+      </c>
+    </row>
+    <row r="332" spans="2:4">
+      <c r="B332" s="68" t="s">
+        <v>585</v>
+      </c>
+      <c r="C332" s="68" t="s">
+        <v>971</v>
+      </c>
+      <c r="D332" s="68" t="s">
+        <v>972</v>
+      </c>
+    </row>
+    <row r="333" spans="2:4">
+      <c r="B333" s="68" t="s">
+        <v>585</v>
+      </c>
+      <c r="C333" s="68" t="s">
+        <v>772</v>
+      </c>
+      <c r="D333" s="68" t="s">
+        <v>773</v>
+      </c>
+    </row>
+    <row r="334" spans="2:4">
+      <c r="B334" s="68" t="s">
+        <v>585</v>
+      </c>
+      <c r="C334" s="68" t="s">
+        <v>973</v>
+      </c>
+      <c r="D334" s="68" t="s">
+        <v>974</v>
+      </c>
+    </row>
+    <row r="335" spans="2:4">
+      <c r="B335" s="68" t="s">
+        <v>585</v>
+      </c>
+      <c r="C335" s="68" t="s">
+        <v>975</v>
+      </c>
+      <c r="D335" s="68" t="s">
+        <v>976</v>
+      </c>
+    </row>
+    <row r="336" spans="2:4">
+      <c r="B336" s="68" t="s">
+        <v>585</v>
+      </c>
+      <c r="C336" s="68" t="s">
+        <v>766</v>
+      </c>
+      <c r="D336" s="68" t="s">
+        <v>977</v>
+      </c>
+    </row>
+    <row r="337" spans="2:4">
+      <c r="B337" s="68" t="s">
+        <v>585</v>
+      </c>
+      <c r="C337" s="68" t="s">
+        <v>768</v>
+      </c>
+      <c r="D337" s="68" t="s">
+        <v>978</v>
+      </c>
+    </row>
+    <row r="338" spans="2:4">
+      <c r="B338" s="68" t="s">
+        <v>585</v>
+      </c>
+      <c r="C338" s="68" t="s">
+        <v>770</v>
+      </c>
+      <c r="D338" s="68" t="s">
+        <v>771</v>
+      </c>
+    </row>
+    <row r="339" spans="2:4">
+      <c r="B339" s="68" t="s">
+        <v>585</v>
+      </c>
+      <c r="C339" s="68" t="s">
+        <v>979</v>
+      </c>
+      <c r="D339" s="68" t="s">
+        <v>980</v>
+      </c>
+    </row>
+    <row r="340" spans="2:4">
+      <c r="B340" s="68" t="s">
+        <v>585</v>
+      </c>
+      <c r="C340" s="68" t="s">
+        <v>981</v>
+      </c>
+      <c r="D340" s="68" t="s">
+        <v>982</v>
+      </c>
+    </row>
+    <row r="341" spans="2:4">
+      <c r="B341" s="68" t="s">
+        <v>585</v>
+      </c>
+      <c r="C341" s="68" t="s">
+        <v>561</v>
+      </c>
+      <c r="D341" s="68" t="s">
+        <v>774</v>
+      </c>
+    </row>
+    <row r="342" spans="2:4">
+      <c r="B342" s="68" t="s">
+        <v>585</v>
+      </c>
+      <c r="C342" s="68" t="s">
+        <v>775</v>
+      </c>
+      <c r="D342" s="68" t="s">
+        <v>776</v>
+      </c>
+    </row>
+    <row r="343" spans="2:4">
+      <c r="B343" s="68" t="s">
+        <v>585</v>
+      </c>
+      <c r="C343" s="68" t="s">
+        <v>983</v>
+      </c>
+      <c r="D343" s="68" t="s">
+        <v>984</v>
+      </c>
+    </row>
+    <row r="344" spans="2:4">
+      <c r="B344" s="68" t="s">
+        <v>585</v>
+      </c>
+      <c r="C344" s="68" t="s">
+        <v>985</v>
+      </c>
+      <c r="D344" s="68" t="s">
+        <v>986</v>
+      </c>
+    </row>
+    <row r="345" spans="2:4">
+      <c r="B345" s="68" t="s">
+        <v>583</v>
+      </c>
+      <c r="C345" s="68" t="s">
+        <v>554</v>
+      </c>
+      <c r="D345" s="68" t="s">
+        <v>777</v>
+      </c>
+    </row>
+    <row r="346" spans="2:4">
+      <c r="B346" s="68" t="s">
+        <v>583</v>
+      </c>
+      <c r="C346" s="68" t="s">
+        <v>987</v>
+      </c>
+      <c r="D346" s="68" t="s">
+        <v>988</v>
+      </c>
+    </row>
+    <row r="347" spans="2:4">
+      <c r="B347" s="68" t="s">
+        <v>591</v>
+      </c>
+      <c r="C347" s="68" t="s">
+        <v>989</v>
+      </c>
+      <c r="D347" s="68" t="s">
+        <v>990</v>
+      </c>
+    </row>
+    <row r="348" spans="2:4">
+      <c r="B348" s="68" t="s">
+        <v>591</v>
+      </c>
+      <c r="C348" s="68" t="s">
+        <v>991</v>
+      </c>
+      <c r="D348" s="68" t="s">
+        <v>992</v>
+      </c>
+    </row>
+    <row r="349" spans="2:4">
+      <c r="B349" s="68" t="s">
+        <v>591</v>
+      </c>
+      <c r="C349" s="68" t="s">
+        <v>993</v>
+      </c>
+      <c r="D349" s="68" t="s">
+        <v>994</v>
+      </c>
+    </row>
+    <row r="350" spans="2:4">
+      <c r="B350" s="68" t="s">
+        <v>591</v>
+      </c>
+      <c r="C350" s="68" t="s">
+        <v>995</v>
+      </c>
+      <c r="D350" s="68" t="s">
+        <v>996</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="24" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -5535,22 +10553,22 @@
       <c r="R5" s="19"/>
     </row>
     <row r="6" spans="3:21">
-      <c r="C6" s="75" t="s">
+      <c r="C6" s="96" t="s">
         <v>343</v>
       </c>
-      <c r="D6" s="76"/>
-      <c r="E6" s="76"/>
-      <c r="F6" s="76"/>
-      <c r="G6" s="76"/>
-      <c r="H6" s="76"/>
-      <c r="I6" s="76"/>
-      <c r="J6" s="76"/>
-      <c r="K6" s="76"/>
-      <c r="L6" s="76"/>
-      <c r="M6" s="76"/>
-      <c r="N6" s="76"/>
-      <c r="O6" s="76"/>
-      <c r="P6" s="77"/>
+      <c r="D6" s="97"/>
+      <c r="E6" s="97"/>
+      <c r="F6" s="97"/>
+      <c r="G6" s="97"/>
+      <c r="H6" s="97"/>
+      <c r="I6" s="97"/>
+      <c r="J6" s="97"/>
+      <c r="K6" s="97"/>
+      <c r="L6" s="97"/>
+      <c r="M6" s="97"/>
+      <c r="N6" s="97"/>
+      <c r="O6" s="97"/>
+      <c r="P6" s="98"/>
       <c r="Q6" s="22"/>
       <c r="R6" s="22" t="s">
         <v>218</v>
@@ -5558,24 +10576,24 @@
       <c r="U6" s="2"/>
     </row>
     <row r="7" spans="3:21">
-      <c r="C7" s="79" t="s">
+      <c r="C7" s="90" t="s">
         <v>227</v>
       </c>
-      <c r="D7" s="80"/>
-      <c r="E7" s="80"/>
-      <c r="F7" s="80"/>
-      <c r="G7" s="80"/>
-      <c r="H7" s="80"/>
-      <c r="I7" s="81"/>
-      <c r="J7" s="79" t="s">
+      <c r="D7" s="91"/>
+      <c r="E7" s="91"/>
+      <c r="F7" s="91"/>
+      <c r="G7" s="91"/>
+      <c r="H7" s="91"/>
+      <c r="I7" s="92"/>
+      <c r="J7" s="90" t="s">
         <v>230</v>
       </c>
-      <c r="K7" s="80"/>
-      <c r="L7" s="80"/>
-      <c r="M7" s="80"/>
-      <c r="N7" s="80"/>
-      <c r="O7" s="80"/>
-      <c r="P7" s="81"/>
+      <c r="K7" s="91"/>
+      <c r="L7" s="91"/>
+      <c r="M7" s="91"/>
+      <c r="N7" s="91"/>
+      <c r="O7" s="91"/>
+      <c r="P7" s="92"/>
       <c r="Q7" s="19"/>
       <c r="R7" s="19"/>
       <c r="U7" s="2"/>
@@ -5628,28 +10646,28 @@
       <c r="U8" s="2"/>
     </row>
     <row r="9" spans="3:21">
-      <c r="C9" s="86" t="s">
+      <c r="C9" s="100" t="s">
         <v>234</v>
       </c>
-      <c r="D9" s="75" t="b">
-        <v>1</v>
-      </c>
-      <c r="E9" s="76"/>
-      <c r="F9" s="76"/>
-      <c r="G9" s="76"/>
-      <c r="H9" s="76"/>
-      <c r="I9" s="77"/>
-      <c r="J9" s="86" t="s">
+      <c r="D9" s="96" t="b">
+        <v>1</v>
+      </c>
+      <c r="E9" s="97"/>
+      <c r="F9" s="97"/>
+      <c r="G9" s="97"/>
+      <c r="H9" s="97"/>
+      <c r="I9" s="98"/>
+      <c r="J9" s="100" t="s">
         <v>218</v>
       </c>
-      <c r="K9" s="74" t="b">
-        <v>1</v>
-      </c>
-      <c r="L9" s="74"/>
-      <c r="M9" s="74"/>
-      <c r="N9" s="74"/>
-      <c r="O9" s="74"/>
-      <c r="P9" s="74"/>
+      <c r="K9" s="99" t="b">
+        <v>1</v>
+      </c>
+      <c r="L9" s="99"/>
+      <c r="M9" s="99"/>
+      <c r="N9" s="99"/>
+      <c r="O9" s="99"/>
+      <c r="P9" s="99"/>
       <c r="Q9" s="24" t="b">
         <v>1</v>
       </c>
@@ -5665,24 +10683,24 @@
       </c>
     </row>
     <row r="10" spans="3:21">
-      <c r="C10" s="87"/>
-      <c r="D10" s="82" t="b">
-        <v>1</v>
-      </c>
-      <c r="E10" s="83"/>
-      <c r="F10" s="83"/>
-      <c r="G10" s="83"/>
-      <c r="H10" s="83"/>
-      <c r="I10" s="84"/>
-      <c r="J10" s="87"/>
-      <c r="K10" s="85" t="b">
+      <c r="C10" s="101"/>
+      <c r="D10" s="93" t="b">
+        <v>1</v>
+      </c>
+      <c r="E10" s="94"/>
+      <c r="F10" s="94"/>
+      <c r="G10" s="94"/>
+      <c r="H10" s="94"/>
+      <c r="I10" s="95"/>
+      <c r="J10" s="101"/>
+      <c r="K10" s="104" t="b">
         <v>0</v>
       </c>
-      <c r="L10" s="85"/>
-      <c r="M10" s="85"/>
-      <c r="N10" s="85"/>
-      <c r="O10" s="85"/>
-      <c r="P10" s="85"/>
+      <c r="L10" s="104"/>
+      <c r="M10" s="104"/>
+      <c r="N10" s="104"/>
+      <c r="O10" s="104"/>
+      <c r="P10" s="104"/>
       <c r="Q10" s="26" t="b">
         <v>0</v>
       </c>
@@ -5698,24 +10716,24 @@
       </c>
     </row>
     <row r="11" spans="3:21">
-      <c r="C11" s="87"/>
-      <c r="D11" s="75" t="b">
+      <c r="C11" s="101"/>
+      <c r="D11" s="96" t="b">
         <v>0</v>
       </c>
-      <c r="E11" s="76"/>
-      <c r="F11" s="76"/>
-      <c r="G11" s="76"/>
-      <c r="H11" s="76"/>
-      <c r="I11" s="77"/>
-      <c r="J11" s="87"/>
-      <c r="K11" s="74" t="b">
-        <v>1</v>
-      </c>
-      <c r="L11" s="74"/>
-      <c r="M11" s="74"/>
-      <c r="N11" s="74"/>
-      <c r="O11" s="74"/>
-      <c r="P11" s="74"/>
+      <c r="E11" s="97"/>
+      <c r="F11" s="97"/>
+      <c r="G11" s="97"/>
+      <c r="H11" s="97"/>
+      <c r="I11" s="98"/>
+      <c r="J11" s="101"/>
+      <c r="K11" s="99" t="b">
+        <v>1</v>
+      </c>
+      <c r="L11" s="99"/>
+      <c r="M11" s="99"/>
+      <c r="N11" s="99"/>
+      <c r="O11" s="99"/>
+      <c r="P11" s="99"/>
       <c r="Q11" s="24" t="b">
         <v>1</v>
       </c>
@@ -5731,24 +10749,24 @@
       </c>
     </row>
     <row r="12" spans="3:21">
-      <c r="C12" s="88"/>
-      <c r="D12" s="75" t="b">
+      <c r="C12" s="102"/>
+      <c r="D12" s="96" t="b">
         <v>0</v>
       </c>
-      <c r="E12" s="76"/>
-      <c r="F12" s="76"/>
-      <c r="G12" s="76"/>
-      <c r="H12" s="76"/>
-      <c r="I12" s="77"/>
-      <c r="J12" s="88"/>
-      <c r="K12" s="74" t="b">
+      <c r="E12" s="97"/>
+      <c r="F12" s="97"/>
+      <c r="G12" s="97"/>
+      <c r="H12" s="97"/>
+      <c r="I12" s="98"/>
+      <c r="J12" s="102"/>
+      <c r="K12" s="99" t="b">
         <v>0</v>
       </c>
-      <c r="L12" s="74"/>
-      <c r="M12" s="74"/>
-      <c r="N12" s="74"/>
-      <c r="O12" s="74"/>
-      <c r="P12" s="74"/>
+      <c r="L12" s="99"/>
+      <c r="M12" s="99"/>
+      <c r="N12" s="99"/>
+      <c r="O12" s="99"/>
+      <c r="P12" s="99"/>
       <c r="Q12" s="24" t="b">
         <v>1</v>
       </c>
@@ -5769,22 +10787,22 @@
       <c r="U13" s="2"/>
     </row>
     <row r="14" spans="3:21">
-      <c r="C14" s="75" t="s">
+      <c r="C14" s="96" t="s">
         <v>344</v>
       </c>
-      <c r="D14" s="76"/>
-      <c r="E14" s="76"/>
-      <c r="F14" s="76"/>
-      <c r="G14" s="76"/>
-      <c r="H14" s="76"/>
-      <c r="I14" s="76"/>
-      <c r="J14" s="76"/>
-      <c r="K14" s="76"/>
-      <c r="L14" s="76"/>
-      <c r="M14" s="76"/>
-      <c r="N14" s="76"/>
-      <c r="O14" s="76"/>
-      <c r="P14" s="77"/>
+      <c r="D14" s="97"/>
+      <c r="E14" s="97"/>
+      <c r="F14" s="97"/>
+      <c r="G14" s="97"/>
+      <c r="H14" s="97"/>
+      <c r="I14" s="97"/>
+      <c r="J14" s="97"/>
+      <c r="K14" s="97"/>
+      <c r="L14" s="97"/>
+      <c r="M14" s="97"/>
+      <c r="N14" s="97"/>
+      <c r="O14" s="97"/>
+      <c r="P14" s="98"/>
       <c r="Q14" s="19"/>
       <c r="R14" s="22" t="s">
         <v>219</v>
@@ -5792,24 +10810,24 @@
       <c r="U14" s="2"/>
     </row>
     <row r="15" spans="3:21">
-      <c r="C15" s="79" t="s">
+      <c r="C15" s="90" t="s">
         <v>228</v>
       </c>
-      <c r="D15" s="80"/>
-      <c r="E15" s="80"/>
-      <c r="F15" s="80"/>
-      <c r="G15" s="80"/>
-      <c r="H15" s="80"/>
-      <c r="I15" s="81"/>
-      <c r="J15" s="79" t="s">
+      <c r="D15" s="91"/>
+      <c r="E15" s="91"/>
+      <c r="F15" s="91"/>
+      <c r="G15" s="91"/>
+      <c r="H15" s="91"/>
+      <c r="I15" s="92"/>
+      <c r="J15" s="90" t="s">
         <v>230</v>
       </c>
-      <c r="K15" s="80"/>
-      <c r="L15" s="80"/>
-      <c r="M15" s="80"/>
-      <c r="N15" s="80"/>
-      <c r="O15" s="80"/>
-      <c r="P15" s="81"/>
+      <c r="K15" s="91"/>
+      <c r="L15" s="91"/>
+      <c r="M15" s="91"/>
+      <c r="N15" s="91"/>
+      <c r="O15" s="91"/>
+      <c r="P15" s="92"/>
       <c r="Q15" s="19"/>
       <c r="R15" s="19"/>
       <c r="U15" s="2"/>
@@ -5862,28 +10880,28 @@
       <c r="U16" s="2"/>
     </row>
     <row r="17" spans="3:21">
-      <c r="C17" s="86" t="s">
+      <c r="C17" s="100" t="s">
         <v>234</v>
       </c>
-      <c r="D17" s="75" t="b">
-        <v>1</v>
-      </c>
-      <c r="E17" s="76"/>
-      <c r="F17" s="76"/>
-      <c r="G17" s="76"/>
-      <c r="H17" s="76"/>
-      <c r="I17" s="77"/>
-      <c r="J17" s="86" t="s">
+      <c r="D17" s="96" t="b">
+        <v>1</v>
+      </c>
+      <c r="E17" s="97"/>
+      <c r="F17" s="97"/>
+      <c r="G17" s="97"/>
+      <c r="H17" s="97"/>
+      <c r="I17" s="98"/>
+      <c r="J17" s="100" t="s">
         <v>219</v>
       </c>
-      <c r="K17" s="74" t="b">
-        <v>1</v>
-      </c>
-      <c r="L17" s="74"/>
-      <c r="M17" s="74"/>
-      <c r="N17" s="74"/>
-      <c r="O17" s="74"/>
-      <c r="P17" s="74"/>
+      <c r="K17" s="99" t="b">
+        <v>1</v>
+      </c>
+      <c r="L17" s="99"/>
+      <c r="M17" s="99"/>
+      <c r="N17" s="99"/>
+      <c r="O17" s="99"/>
+      <c r="P17" s="99"/>
       <c r="Q17" s="24" t="b">
         <v>1</v>
       </c>
@@ -5891,24 +10909,24 @@
       <c r="U17" s="2"/>
     </row>
     <row r="18" spans="3:21">
-      <c r="C18" s="87"/>
-      <c r="D18" s="75" t="b">
-        <v>1</v>
-      </c>
-      <c r="E18" s="76"/>
-      <c r="F18" s="76"/>
-      <c r="G18" s="76"/>
-      <c r="H18" s="76"/>
-      <c r="I18" s="77"/>
-      <c r="J18" s="87"/>
-      <c r="K18" s="74" t="b">
+      <c r="C18" s="101"/>
+      <c r="D18" s="96" t="b">
+        <v>1</v>
+      </c>
+      <c r="E18" s="97"/>
+      <c r="F18" s="97"/>
+      <c r="G18" s="97"/>
+      <c r="H18" s="97"/>
+      <c r="I18" s="98"/>
+      <c r="J18" s="101"/>
+      <c r="K18" s="99" t="b">
         <v>0</v>
       </c>
-      <c r="L18" s="74"/>
-      <c r="M18" s="74"/>
-      <c r="N18" s="74"/>
-      <c r="O18" s="74"/>
-      <c r="P18" s="74"/>
+      <c r="L18" s="99"/>
+      <c r="M18" s="99"/>
+      <c r="N18" s="99"/>
+      <c r="O18" s="99"/>
+      <c r="P18" s="99"/>
       <c r="Q18" s="24" t="b">
         <v>1</v>
       </c>
@@ -5916,24 +10934,24 @@
       <c r="U18" s="2"/>
     </row>
     <row r="19" spans="3:21">
-      <c r="C19" s="87"/>
-      <c r="D19" s="82" t="b">
+      <c r="C19" s="101"/>
+      <c r="D19" s="93" t="b">
         <v>0</v>
       </c>
-      <c r="E19" s="83"/>
-      <c r="F19" s="83"/>
-      <c r="G19" s="83"/>
-      <c r="H19" s="83"/>
-      <c r="I19" s="84"/>
-      <c r="J19" s="87"/>
-      <c r="K19" s="85" t="b">
-        <v>1</v>
-      </c>
-      <c r="L19" s="85"/>
-      <c r="M19" s="85"/>
-      <c r="N19" s="85"/>
-      <c r="O19" s="85"/>
-      <c r="P19" s="85"/>
+      <c r="E19" s="94"/>
+      <c r="F19" s="94"/>
+      <c r="G19" s="94"/>
+      <c r="H19" s="94"/>
+      <c r="I19" s="95"/>
+      <c r="J19" s="101"/>
+      <c r="K19" s="104" t="b">
+        <v>1</v>
+      </c>
+      <c r="L19" s="104"/>
+      <c r="M19" s="104"/>
+      <c r="N19" s="104"/>
+      <c r="O19" s="104"/>
+      <c r="P19" s="104"/>
       <c r="Q19" s="26" t="b">
         <v>0</v>
       </c>
@@ -5941,24 +10959,24 @@
       <c r="U19" s="2"/>
     </row>
     <row r="20" spans="3:21">
-      <c r="C20" s="88"/>
-      <c r="D20" s="75" t="b">
+      <c r="C20" s="102"/>
+      <c r="D20" s="96" t="b">
         <v>0</v>
       </c>
-      <c r="E20" s="76"/>
-      <c r="F20" s="76"/>
-      <c r="G20" s="76"/>
-      <c r="H20" s="76"/>
-      <c r="I20" s="77"/>
-      <c r="J20" s="88"/>
-      <c r="K20" s="74" t="b">
+      <c r="E20" s="97"/>
+      <c r="F20" s="97"/>
+      <c r="G20" s="97"/>
+      <c r="H20" s="97"/>
+      <c r="I20" s="98"/>
+      <c r="J20" s="102"/>
+      <c r="K20" s="99" t="b">
         <v>0</v>
       </c>
-      <c r="L20" s="74"/>
-      <c r="M20" s="74"/>
-      <c r="N20" s="74"/>
-      <c r="O20" s="74"/>
-      <c r="P20" s="74"/>
+      <c r="L20" s="99"/>
+      <c r="M20" s="99"/>
+      <c r="N20" s="99"/>
+      <c r="O20" s="99"/>
+      <c r="P20" s="99"/>
       <c r="Q20" s="27" t="b">
         <v>1</v>
       </c>
@@ -5969,46 +10987,46 @@
       <c r="R21" s="19"/>
     </row>
     <row r="22" spans="3:21">
-      <c r="C22" s="75" t="s">
+      <c r="C22" s="96" t="s">
         <v>345</v>
       </c>
-      <c r="D22" s="76"/>
-      <c r="E22" s="76"/>
-      <c r="F22" s="76"/>
-      <c r="G22" s="76"/>
-      <c r="H22" s="76"/>
-      <c r="I22" s="76"/>
-      <c r="J22" s="76"/>
-      <c r="K22" s="76"/>
-      <c r="L22" s="76"/>
-      <c r="M22" s="76"/>
-      <c r="N22" s="76"/>
-      <c r="O22" s="76"/>
-      <c r="P22" s="77"/>
+      <c r="D22" s="97"/>
+      <c r="E22" s="97"/>
+      <c r="F22" s="97"/>
+      <c r="G22" s="97"/>
+      <c r="H22" s="97"/>
+      <c r="I22" s="97"/>
+      <c r="J22" s="97"/>
+      <c r="K22" s="97"/>
+      <c r="L22" s="97"/>
+      <c r="M22" s="97"/>
+      <c r="N22" s="97"/>
+      <c r="O22" s="97"/>
+      <c r="P22" s="98"/>
       <c r="Q22" s="19"/>
       <c r="R22" s="22" t="s">
         <v>217</v>
       </c>
     </row>
     <row r="23" spans="3:21">
-      <c r="C23" s="79" t="s">
+      <c r="C23" s="90" t="s">
         <v>229</v>
       </c>
-      <c r="D23" s="80"/>
-      <c r="E23" s="80"/>
-      <c r="F23" s="80"/>
-      <c r="G23" s="80"/>
-      <c r="H23" s="80"/>
-      <c r="I23" s="81"/>
-      <c r="J23" s="79" t="s">
+      <c r="D23" s="91"/>
+      <c r="E23" s="91"/>
+      <c r="F23" s="91"/>
+      <c r="G23" s="91"/>
+      <c r="H23" s="91"/>
+      <c r="I23" s="92"/>
+      <c r="J23" s="90" t="s">
         <v>231</v>
       </c>
-      <c r="K23" s="80"/>
-      <c r="L23" s="80"/>
-      <c r="M23" s="80"/>
-      <c r="N23" s="80"/>
-      <c r="O23" s="80"/>
-      <c r="P23" s="81"/>
+      <c r="K23" s="91"/>
+      <c r="L23" s="91"/>
+      <c r="M23" s="91"/>
+      <c r="N23" s="91"/>
+      <c r="O23" s="91"/>
+      <c r="P23" s="92"/>
       <c r="Q23" s="19"/>
       <c r="R23" s="19"/>
     </row>
@@ -6059,100 +11077,100 @@
       <c r="R24" s="19"/>
     </row>
     <row r="25" spans="3:21">
-      <c r="C25" s="86" t="s">
+      <c r="C25" s="100" t="s">
         <v>234</v>
       </c>
-      <c r="D25" s="75" t="b">
-        <v>1</v>
-      </c>
-      <c r="E25" s="76"/>
-      <c r="F25" s="76"/>
-      <c r="G25" s="76"/>
-      <c r="H25" s="76"/>
-      <c r="I25" s="77"/>
-      <c r="J25" s="89" t="s">
+      <c r="D25" s="96" t="b">
+        <v>1</v>
+      </c>
+      <c r="E25" s="97"/>
+      <c r="F25" s="97"/>
+      <c r="G25" s="97"/>
+      <c r="H25" s="97"/>
+      <c r="I25" s="98"/>
+      <c r="J25" s="103" t="s">
         <v>233</v>
       </c>
-      <c r="K25" s="74" t="b">
-        <v>1</v>
-      </c>
-      <c r="L25" s="74"/>
-      <c r="M25" s="74"/>
-      <c r="N25" s="74"/>
-      <c r="O25" s="74"/>
-      <c r="P25" s="74"/>
+      <c r="K25" s="99" t="b">
+        <v>1</v>
+      </c>
+      <c r="L25" s="99"/>
+      <c r="M25" s="99"/>
+      <c r="N25" s="99"/>
+      <c r="O25" s="99"/>
+      <c r="P25" s="99"/>
       <c r="Q25" s="24" t="b">
         <v>1</v>
       </c>
       <c r="R25" s="19"/>
     </row>
     <row r="26" spans="3:21">
-      <c r="C26" s="87"/>
-      <c r="D26" s="82" t="b">
-        <v>1</v>
-      </c>
-      <c r="E26" s="83"/>
-      <c r="F26" s="83"/>
-      <c r="G26" s="83"/>
-      <c r="H26" s="83"/>
-      <c r="I26" s="84"/>
-      <c r="J26" s="87"/>
-      <c r="K26" s="85" t="b">
+      <c r="C26" s="101"/>
+      <c r="D26" s="93" t="b">
+        <v>1</v>
+      </c>
+      <c r="E26" s="94"/>
+      <c r="F26" s="94"/>
+      <c r="G26" s="94"/>
+      <c r="H26" s="94"/>
+      <c r="I26" s="95"/>
+      <c r="J26" s="101"/>
+      <c r="K26" s="104" t="b">
         <v>0</v>
       </c>
-      <c r="L26" s="85"/>
-      <c r="M26" s="85"/>
-      <c r="N26" s="85"/>
-      <c r="O26" s="85"/>
-      <c r="P26" s="85"/>
+      <c r="L26" s="104"/>
+      <c r="M26" s="104"/>
+      <c r="N26" s="104"/>
+      <c r="O26" s="104"/>
+      <c r="P26" s="104"/>
       <c r="Q26" s="26" t="b">
         <v>0</v>
       </c>
       <c r="R26" s="19"/>
     </row>
     <row r="27" spans="3:21">
-      <c r="C27" s="87"/>
-      <c r="D27" s="82" t="b">
+      <c r="C27" s="101"/>
+      <c r="D27" s="93" t="b">
         <v>0</v>
       </c>
-      <c r="E27" s="83"/>
-      <c r="F27" s="83"/>
-      <c r="G27" s="83"/>
-      <c r="H27" s="83"/>
-      <c r="I27" s="84"/>
-      <c r="J27" s="87"/>
-      <c r="K27" s="85" t="b">
-        <v>1</v>
-      </c>
-      <c r="L27" s="85"/>
-      <c r="M27" s="85"/>
-      <c r="N27" s="85"/>
-      <c r="O27" s="85"/>
-      <c r="P27" s="85"/>
+      <c r="E27" s="94"/>
+      <c r="F27" s="94"/>
+      <c r="G27" s="94"/>
+      <c r="H27" s="94"/>
+      <c r="I27" s="95"/>
+      <c r="J27" s="101"/>
+      <c r="K27" s="104" t="b">
+        <v>1</v>
+      </c>
+      <c r="L27" s="104"/>
+      <c r="M27" s="104"/>
+      <c r="N27" s="104"/>
+      <c r="O27" s="104"/>
+      <c r="P27" s="104"/>
       <c r="Q27" s="28" t="b">
         <v>0</v>
       </c>
       <c r="R27" s="19"/>
     </row>
     <row r="28" spans="3:21">
-      <c r="C28" s="88"/>
-      <c r="D28" s="75" t="b">
+      <c r="C28" s="102"/>
+      <c r="D28" s="96" t="b">
         <v>0</v>
       </c>
-      <c r="E28" s="76"/>
-      <c r="F28" s="76"/>
-      <c r="G28" s="76"/>
-      <c r="H28" s="76"/>
-      <c r="I28" s="77"/>
-      <c r="J28" s="88"/>
-      <c r="K28" s="74" t="b">
+      <c r="E28" s="97"/>
+      <c r="F28" s="97"/>
+      <c r="G28" s="97"/>
+      <c r="H28" s="97"/>
+      <c r="I28" s="98"/>
+      <c r="J28" s="102"/>
+      <c r="K28" s="99" t="b">
         <v>0</v>
       </c>
-      <c r="L28" s="74"/>
-      <c r="M28" s="74"/>
-      <c r="N28" s="74"/>
-      <c r="O28" s="74"/>
-      <c r="P28" s="74"/>
+      <c r="L28" s="99"/>
+      <c r="M28" s="99"/>
+      <c r="N28" s="99"/>
+      <c r="O28" s="99"/>
+      <c r="P28" s="99"/>
       <c r="Q28" s="27" t="b">
         <v>1</v>
       </c>
@@ -6162,46 +11180,46 @@
       <c r="R29" s="19"/>
     </row>
     <row r="30" spans="3:21">
-      <c r="C30" s="75" t="s">
+      <c r="C30" s="96" t="s">
         <v>346</v>
       </c>
-      <c r="D30" s="76"/>
-      <c r="E30" s="76"/>
-      <c r="F30" s="76"/>
-      <c r="G30" s="76"/>
-      <c r="H30" s="76"/>
-      <c r="I30" s="76"/>
-      <c r="J30" s="76"/>
-      <c r="K30" s="76"/>
-      <c r="L30" s="76"/>
-      <c r="M30" s="76"/>
-      <c r="N30" s="76"/>
-      <c r="O30" s="76"/>
-      <c r="P30" s="77"/>
+      <c r="D30" s="97"/>
+      <c r="E30" s="97"/>
+      <c r="F30" s="97"/>
+      <c r="G30" s="97"/>
+      <c r="H30" s="97"/>
+      <c r="I30" s="97"/>
+      <c r="J30" s="97"/>
+      <c r="K30" s="97"/>
+      <c r="L30" s="97"/>
+      <c r="M30" s="97"/>
+      <c r="N30" s="97"/>
+      <c r="O30" s="97"/>
+      <c r="P30" s="98"/>
       <c r="Q30" s="19"/>
       <c r="R30" s="22" t="s">
         <v>220</v>
       </c>
     </row>
     <row r="31" spans="3:21">
-      <c r="C31" s="79" t="s">
+      <c r="C31" s="90" t="s">
         <v>237</v>
       </c>
-      <c r="D31" s="80"/>
-      <c r="E31" s="80"/>
-      <c r="F31" s="80"/>
-      <c r="G31" s="80"/>
-      <c r="H31" s="80"/>
-      <c r="I31" s="81"/>
-      <c r="J31" s="79" t="s">
+      <c r="D31" s="91"/>
+      <c r="E31" s="91"/>
+      <c r="F31" s="91"/>
+      <c r="G31" s="91"/>
+      <c r="H31" s="91"/>
+      <c r="I31" s="92"/>
+      <c r="J31" s="90" t="s">
         <v>238</v>
       </c>
-      <c r="K31" s="80"/>
-      <c r="L31" s="80"/>
-      <c r="M31" s="80"/>
-      <c r="N31" s="80"/>
-      <c r="O31" s="80"/>
-      <c r="P31" s="81"/>
+      <c r="K31" s="91"/>
+      <c r="L31" s="91"/>
+      <c r="M31" s="91"/>
+      <c r="N31" s="91"/>
+      <c r="O31" s="91"/>
+      <c r="P31" s="92"/>
       <c r="Q31" s="19"/>
       <c r="R31" s="19"/>
     </row>
@@ -6255,25 +11273,25 @@
       <c r="C33" s="24" t="s">
         <v>236</v>
       </c>
-      <c r="D33" s="75" t="s">
+      <c r="D33" s="96" t="s">
         <v>216</v>
       </c>
-      <c r="E33" s="76"/>
-      <c r="F33" s="76"/>
-      <c r="G33" s="76"/>
-      <c r="H33" s="76"/>
-      <c r="I33" s="77"/>
+      <c r="E33" s="97"/>
+      <c r="F33" s="97"/>
+      <c r="G33" s="97"/>
+      <c r="H33" s="97"/>
+      <c r="I33" s="98"/>
       <c r="J33" s="24" t="s">
         <v>235</v>
       </c>
-      <c r="K33" s="74" t="s">
+      <c r="K33" s="99" t="s">
         <v>221</v>
       </c>
-      <c r="L33" s="74"/>
-      <c r="M33" s="74"/>
-      <c r="N33" s="74"/>
-      <c r="O33" s="74"/>
-      <c r="P33" s="74"/>
+      <c r="L33" s="99"/>
+      <c r="M33" s="99"/>
+      <c r="N33" s="99"/>
+      <c r="O33" s="99"/>
+      <c r="P33" s="99"/>
       <c r="Q33" s="24" t="s">
         <v>239</v>
       </c>
@@ -6287,19 +11305,19 @@
     <row r="36" spans="3:21" ht="26">
       <c r="C36" s="20"/>
       <c r="D36" s="20"/>
-      <c r="F36" s="78" t="s">
+      <c r="F36" s="106" t="s">
         <v>253</v>
       </c>
-      <c r="G36" s="78"/>
-      <c r="H36" s="78"/>
-      <c r="I36" s="78"/>
-      <c r="J36" s="78"/>
-      <c r="K36" s="78"/>
-      <c r="L36" s="78"/>
-      <c r="M36" s="78"/>
-      <c r="N36" s="78"/>
-      <c r="O36" s="78"/>
-      <c r="P36" s="78"/>
+      <c r="G36" s="106"/>
+      <c r="H36" s="106"/>
+      <c r="I36" s="106"/>
+      <c r="J36" s="106"/>
+      <c r="K36" s="106"/>
+      <c r="L36" s="106"/>
+      <c r="M36" s="106"/>
+      <c r="N36" s="106"/>
+      <c r="O36" s="106"/>
+      <c r="P36" s="106"/>
     </row>
     <row r="37" spans="3:21">
       <c r="C37" s="30" t="s">
@@ -6595,18 +11613,18 @@
       </c>
     </row>
     <row r="65" spans="3:12">
-      <c r="C65" s="73" t="s">
+      <c r="C65" s="105" t="s">
         <v>286</v>
       </c>
-      <c r="D65" s="73"/>
-      <c r="E65" s="73"/>
-      <c r="F65" s="73"/>
-      <c r="G65" s="73"/>
-      <c r="H65" s="73"/>
-      <c r="I65" s="73"/>
-      <c r="J65" s="73"/>
-      <c r="K65" s="73"/>
-      <c r="L65" s="73"/>
+      <c r="D65" s="105"/>
+      <c r="E65" s="105"/>
+      <c r="F65" s="105"/>
+      <c r="G65" s="105"/>
+      <c r="H65" s="105"/>
+      <c r="I65" s="105"/>
+      <c r="J65" s="105"/>
+      <c r="K65" s="105"/>
+      <c r="L65" s="105"/>
     </row>
     <row r="66" spans="3:12">
       <c r="C66" s="19" t="b">
@@ -6764,18 +11782,18 @@
       <c r="G70" s="19"/>
     </row>
     <row r="71" spans="3:12">
-      <c r="C71" s="73" t="s">
+      <c r="C71" s="105" t="s">
         <v>287</v>
       </c>
-      <c r="D71" s="73"/>
-      <c r="E71" s="73"/>
-      <c r="F71" s="73"/>
-      <c r="G71" s="73"/>
-      <c r="H71" s="73"/>
-      <c r="I71" s="73"/>
-      <c r="J71" s="73"/>
-      <c r="K71" s="73"/>
-      <c r="L71" s="73"/>
+      <c r="D71" s="105"/>
+      <c r="E71" s="105"/>
+      <c r="F71" s="105"/>
+      <c r="G71" s="105"/>
+      <c r="H71" s="105"/>
+      <c r="I71" s="105"/>
+      <c r="J71" s="105"/>
+      <c r="K71" s="105"/>
+      <c r="L71" s="105"/>
     </row>
     <row r="72" spans="3:12">
       <c r="C72" s="19">
@@ -7098,18 +12116,18 @@
       </c>
     </row>
     <row r="81" spans="3:12">
-      <c r="C81" s="73" t="s">
+      <c r="C81" s="105" t="s">
         <v>298</v>
       </c>
-      <c r="D81" s="73"/>
-      <c r="E81" s="73"/>
-      <c r="F81" s="73"/>
-      <c r="G81" s="73"/>
-      <c r="H81" s="73"/>
-      <c r="I81" s="73"/>
-      <c r="J81" s="73"/>
-      <c r="K81" s="73"/>
-      <c r="L81" s="73"/>
+      <c r="D81" s="105"/>
+      <c r="E81" s="105"/>
+      <c r="F81" s="105"/>
+      <c r="G81" s="105"/>
+      <c r="H81" s="105"/>
+      <c r="I81" s="105"/>
+      <c r="J81" s="105"/>
+      <c r="K81" s="105"/>
+      <c r="L81" s="105"/>
     </row>
     <row r="82" spans="3:12">
       <c r="C82" s="19">
@@ -7623,6 +12641,38 @@
     </row>
   </sheetData>
   <mergeCells count="48">
+    <mergeCell ref="C81:L81"/>
+    <mergeCell ref="C65:L65"/>
+    <mergeCell ref="C71:L71"/>
+    <mergeCell ref="K33:P33"/>
+    <mergeCell ref="D33:I33"/>
+    <mergeCell ref="F36:P36"/>
+    <mergeCell ref="C7:I7"/>
+    <mergeCell ref="D12:I12"/>
+    <mergeCell ref="D11:I11"/>
+    <mergeCell ref="D10:I10"/>
+    <mergeCell ref="D9:I9"/>
+    <mergeCell ref="C22:P22"/>
+    <mergeCell ref="K9:P9"/>
+    <mergeCell ref="K10:P10"/>
+    <mergeCell ref="K11:P11"/>
+    <mergeCell ref="K12:P12"/>
+    <mergeCell ref="C6:P6"/>
+    <mergeCell ref="J9:J12"/>
+    <mergeCell ref="J25:J28"/>
+    <mergeCell ref="J17:J20"/>
+    <mergeCell ref="D25:I25"/>
+    <mergeCell ref="C9:C12"/>
+    <mergeCell ref="C17:C20"/>
+    <mergeCell ref="C25:C28"/>
+    <mergeCell ref="K25:P25"/>
+    <mergeCell ref="K26:P26"/>
+    <mergeCell ref="K27:P27"/>
+    <mergeCell ref="K28:P28"/>
+    <mergeCell ref="C14:P14"/>
+    <mergeCell ref="K17:P17"/>
+    <mergeCell ref="K18:P18"/>
+    <mergeCell ref="K19:P19"/>
     <mergeCell ref="J31:P31"/>
     <mergeCell ref="J23:P23"/>
     <mergeCell ref="J7:P7"/>
@@ -7639,38 +12689,6 @@
     <mergeCell ref="C23:I23"/>
     <mergeCell ref="C31:I31"/>
     <mergeCell ref="C30:P30"/>
-    <mergeCell ref="C6:P6"/>
-    <mergeCell ref="J9:J12"/>
-    <mergeCell ref="J25:J28"/>
-    <mergeCell ref="J17:J20"/>
-    <mergeCell ref="D25:I25"/>
-    <mergeCell ref="C9:C12"/>
-    <mergeCell ref="C17:C20"/>
-    <mergeCell ref="C25:C28"/>
-    <mergeCell ref="K25:P25"/>
-    <mergeCell ref="K26:P26"/>
-    <mergeCell ref="K27:P27"/>
-    <mergeCell ref="K28:P28"/>
-    <mergeCell ref="C14:P14"/>
-    <mergeCell ref="K17:P17"/>
-    <mergeCell ref="K18:P18"/>
-    <mergeCell ref="K19:P19"/>
-    <mergeCell ref="C22:P22"/>
-    <mergeCell ref="K9:P9"/>
-    <mergeCell ref="K10:P10"/>
-    <mergeCell ref="K11:P11"/>
-    <mergeCell ref="K12:P12"/>
-    <mergeCell ref="C7:I7"/>
-    <mergeCell ref="D12:I12"/>
-    <mergeCell ref="D11:I11"/>
-    <mergeCell ref="D10:I10"/>
-    <mergeCell ref="D9:I9"/>
-    <mergeCell ref="C81:L81"/>
-    <mergeCell ref="C65:L65"/>
-    <mergeCell ref="C71:L71"/>
-    <mergeCell ref="K33:P33"/>
-    <mergeCell ref="D33:I33"/>
-    <mergeCell ref="F36:P36"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -7764,62 +12782,62 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:33">
-      <c r="B2" s="90" t="s">
+      <c r="B2" s="107" t="s">
         <v>68</v>
       </c>
-      <c r="C2" s="90"/>
-      <c r="D2" s="90"/>
-      <c r="E2" s="90"/>
+      <c r="C2" s="107"/>
+      <c r="D2" s="107"/>
+      <c r="E2" s="107"/>
     </row>
     <row r="3" spans="2:33">
-      <c r="B3" s="90"/>
-      <c r="C3" s="90"/>
-      <c r="D3" s="90"/>
-      <c r="E3" s="90"/>
+      <c r="B3" s="107"/>
+      <c r="C3" s="107"/>
+      <c r="D3" s="107"/>
+      <c r="E3" s="107"/>
       <c r="M3" s="31"/>
     </row>
     <row r="4" spans="2:33">
-      <c r="B4" s="90"/>
-      <c r="C4" s="90"/>
-      <c r="D4" s="90"/>
-      <c r="E4" s="90"/>
+      <c r="B4" s="107"/>
+      <c r="C4" s="107"/>
+      <c r="D4" s="107"/>
+      <c r="E4" s="107"/>
     </row>
     <row r="5" spans="2:33">
-      <c r="B5" s="90"/>
-      <c r="C5" s="90"/>
-      <c r="D5" s="90"/>
-      <c r="E5" s="90"/>
+      <c r="B5" s="107"/>
+      <c r="C5" s="107"/>
+      <c r="D5" s="107"/>
+      <c r="E5" s="107"/>
     </row>
     <row r="6" spans="2:33">
-      <c r="B6" s="90"/>
-      <c r="C6" s="90"/>
-      <c r="D6" s="90"/>
-      <c r="E6" s="90"/>
-      <c r="O6" s="90" t="s">
+      <c r="B6" s="107"/>
+      <c r="C6" s="107"/>
+      <c r="D6" s="107"/>
+      <c r="E6" s="107"/>
+      <c r="O6" s="107" t="s">
         <v>33</v>
       </c>
-      <c r="P6" s="90"/>
-      <c r="Q6" s="90"/>
-      <c r="R6" s="90"/>
+      <c r="P6" s="107"/>
+      <c r="Q6" s="107"/>
+      <c r="R6" s="107"/>
     </row>
     <row r="7" spans="2:33">
-      <c r="O7" s="90"/>
-      <c r="P7" s="90"/>
-      <c r="Q7" s="90"/>
-      <c r="R7" s="90"/>
+      <c r="O7" s="107"/>
+      <c r="P7" s="107"/>
+      <c r="Q7" s="107"/>
+      <c r="R7" s="107"/>
     </row>
     <row r="8" spans="2:33">
-      <c r="C8" s="91" t="s">
+      <c r="C8" s="108" t="s">
         <v>8</v>
       </c>
-      <c r="D8" s="91"/>
-      <c r="E8" s="91"/>
-      <c r="F8" s="91"/>
-      <c r="G8" s="91"/>
-      <c r="O8" s="90"/>
-      <c r="P8" s="90"/>
-      <c r="Q8" s="90"/>
-      <c r="R8" s="90"/>
+      <c r="D8" s="108"/>
+      <c r="E8" s="108"/>
+      <c r="F8" s="108"/>
+      <c r="G8" s="108"/>
+      <c r="O8" s="107"/>
+      <c r="P8" s="107"/>
+      <c r="Q8" s="107"/>
+      <c r="R8" s="107"/>
     </row>
     <row r="9" spans="2:33">
       <c r="B9" s="33" t="s">
@@ -7850,10 +12868,10 @@
         <v>6</v>
       </c>
       <c r="L9" s="31"/>
-      <c r="O9" s="90"/>
-      <c r="P9" s="90"/>
-      <c r="Q9" s="90"/>
-      <c r="R9" s="90"/>
+      <c r="O9" s="107"/>
+      <c r="P9" s="107"/>
+      <c r="Q9" s="107"/>
+      <c r="R9" s="107"/>
     </row>
     <row r="10" spans="2:33">
       <c r="B10" s="31" t="s">
@@ -7883,10 +12901,10 @@
       <c r="J10" s="2">
         <v>0</v>
       </c>
-      <c r="O10" s="90"/>
-      <c r="P10" s="90"/>
-      <c r="Q10" s="90"/>
-      <c r="R10" s="90"/>
+      <c r="O10" s="107"/>
+      <c r="P10" s="107"/>
+      <c r="Q10" s="107"/>
+      <c r="R10" s="107"/>
     </row>
     <row r="11" spans="2:33">
       <c r="B11" s="31" t="s">
@@ -8755,12 +13773,12 @@
       </c>
     </row>
     <row r="25" spans="2:33">
-      <c r="B25" s="90" t="s">
+      <c r="B25" s="107" t="s">
         <v>69</v>
       </c>
-      <c r="C25" s="90"/>
-      <c r="D25" s="90"/>
-      <c r="E25" s="90"/>
+      <c r="C25" s="107"/>
+      <c r="D25" s="107"/>
+      <c r="E25" s="107"/>
       <c r="O25" s="2" t="s">
         <v>23</v>
       </c>
@@ -8829,10 +13847,10 @@
       </c>
     </row>
     <row r="26" spans="2:33" ht="16" customHeight="1">
-      <c r="B26" s="90"/>
-      <c r="C26" s="90"/>
-      <c r="D26" s="90"/>
-      <c r="E26" s="90"/>
+      <c r="B26" s="107"/>
+      <c r="C26" s="107"/>
+      <c r="D26" s="107"/>
+      <c r="E26" s="107"/>
       <c r="N26" s="34" t="s">
         <v>23</v>
       </c>
@@ -8903,10 +13921,10 @@
       </c>
     </row>
     <row r="27" spans="2:33" ht="16" customHeight="1">
-      <c r="B27" s="90"/>
-      <c r="C27" s="90"/>
-      <c r="D27" s="90"/>
-      <c r="E27" s="90"/>
+      <c r="B27" s="107"/>
+      <c r="C27" s="107"/>
+      <c r="D27" s="107"/>
+      <c r="E27" s="107"/>
       <c r="N27" s="34" t="s">
         <v>24</v>
       </c>
@@ -8977,10 +13995,10 @@
       </c>
     </row>
     <row r="28" spans="2:33" ht="16" customHeight="1">
-      <c r="B28" s="90"/>
-      <c r="C28" s="90"/>
-      <c r="D28" s="90"/>
-      <c r="E28" s="90"/>
+      <c r="B28" s="107"/>
+      <c r="C28" s="107"/>
+      <c r="D28" s="107"/>
+      <c r="E28" s="107"/>
       <c r="N28" s="34" t="s">
         <v>25</v>
       </c>
@@ -9051,10 +14069,10 @@
       </c>
     </row>
     <row r="29" spans="2:33" ht="16" customHeight="1">
-      <c r="B29" s="90"/>
-      <c r="C29" s="90"/>
-      <c r="D29" s="90"/>
-      <c r="E29" s="90"/>
+      <c r="B29" s="107"/>
+      <c r="C29" s="107"/>
+      <c r="D29" s="107"/>
+      <c r="E29" s="107"/>
       <c r="N29" s="34" t="s">
         <v>27</v>
       </c>
@@ -10538,7 +15556,7 @@
       <c r="M18" s="6"/>
     </row>
     <row r="19" spans="1:15" ht="39" customHeight="1">
-      <c r="A19" s="92">
+      <c r="A19" s="109">
         <v>2</v>
       </c>
       <c r="B19" s="6" t="s">
@@ -10582,7 +15600,7 @@
       </c>
     </row>
     <row r="20" spans="1:15" ht="39" customHeight="1">
-      <c r="A20" s="92"/>
+      <c r="A20" s="109"/>
       <c r="B20" s="6" t="s">
         <v>98</v>
       </c>
@@ -10801,12 +15819,12 @@
       <c r="F29" s="6"/>
       <c r="G29" s="6"/>
       <c r="H29" s="6"/>
-      <c r="I29" s="93" t="s">
+      <c r="I29" s="110" t="s">
         <v>418</v>
       </c>
-      <c r="J29" s="93"/>
-      <c r="K29" s="93"/>
-      <c r="L29" s="93"/>
+      <c r="J29" s="110"/>
+      <c r="K29" s="110"/>
+      <c r="L29" s="110"/>
     </row>
     <row r="30" spans="1:15" ht="39" customHeight="1">
       <c r="A30" s="6"/>
@@ -11171,12 +16189,12 @@
       <c r="F47" s="6"/>
       <c r="G47" s="6"/>
       <c r="H47" s="6"/>
-      <c r="I47" s="93" t="s">
+      <c r="I47" s="110" t="s">
         <v>419</v>
       </c>
-      <c r="J47" s="93"/>
-      <c r="K47" s="93"/>
-      <c r="L47" s="93"/>
+      <c r="J47" s="110"/>
+      <c r="K47" s="110"/>
+      <c r="L47" s="110"/>
       <c r="M47" s="6"/>
       <c r="N47" s="6"/>
     </row>
